--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -779,7 +779,7 @@
         <v>0.2661312665695027</v>
       </c>
       <c r="E3" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F3" t="n">
         <v>-0.4806241943182994</v>
@@ -849,7 +849,7 @@
         <v>1.177403793656137</v>
       </c>
       <c r="E4" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F4" t="n">
         <v>1.624666086477427</v>
@@ -919,7 +919,7 @@
         <v>-0.5722394583502011</v>
       </c>
       <c r="E5" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F5" t="n">
         <v>1.786611492692483</v>
@@ -997,7 +997,7 @@
         <v>1.104501991489206</v>
       </c>
       <c r="E6" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F6" t="n">
         <v>1.786611492692483</v>
@@ -1075,7 +1075,7 @@
         <v>1.541912804490791</v>
       </c>
       <c r="E7" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F7" t="n">
         <v>0.3695891883107441</v>
@@ -1145,7 +1145,7 @@
         <v>-0.754493963767528</v>
       </c>
       <c r="E8" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F8" t="n">
         <v>-0.1972197334419516</v>
@@ -1215,7 +1215,7 @@
         <v>-1.191904776769113</v>
       </c>
       <c r="E9" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F9" t="n">
         <v>-0.1972197334419516</v>
@@ -1285,7 +1285,7 @@
         <v>-0.6451412605171318</v>
       </c>
       <c r="E10" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F10" t="n">
         <v>-1.627737488341612</v>
@@ -1457,7 +1457,7 @@
         <v>-0.09837774426515113</v>
       </c>
       <c r="E12" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F12" t="n">
         <v>-0.3591651396570075</v>
@@ -1601,7 +1601,7 @@
         <v>0.1567785633191066</v>
       </c>
       <c r="E14" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F14" t="n">
         <v>1.003875362653046</v>
@@ -1675,7 +1675,7 @@
         <v>-1.301257480019509</v>
       </c>
       <c r="E15" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F15" t="n">
         <v>0.3695891883107441</v>
@@ -1749,7 +1749,7 @@
         <v>0.6306402774041565</v>
       </c>
       <c r="E16" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F16" t="n">
         <v>-1.438801181090714</v>
@@ -1921,7 +1921,7 @@
         <v>0.5212875741537604</v>
       </c>
       <c r="E18" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F18" t="n">
         <v>-0.9934513139993099</v>
@@ -1999,7 +1999,7 @@
         <v>-1.337708381102974</v>
       </c>
       <c r="E19" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F19" t="n">
         <v>-0.9934513139993099</v>
@@ -2069,7 +2069,7 @@
         <v>0.9586983871553449</v>
       </c>
       <c r="E20" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3591651396570075</v>
@@ -2139,7 +2139,7 @@
         <v>-0.4264358540163395</v>
       </c>
       <c r="E21" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F21" t="n">
         <v>1.003875362653046</v>
@@ -2311,7 +2311,7 @@
         <v>-0.3899849529328742</v>
       </c>
       <c r="E23" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F23" t="n">
         <v>1.260288922493552</v>
@@ -2381,7 +2381,7 @@
         <v>1.068051090405741</v>
       </c>
       <c r="E24" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F24" t="n">
         <v>0.7609572533304625</v>
@@ -2455,7 +2455,7 @@
         <v>1.323207397989999</v>
       </c>
       <c r="E25" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F25" t="n">
         <v>0.9498935605813611</v>
@@ -2525,7 +2525,7 @@
         <v>-1.483511985436836</v>
       </c>
       <c r="E26" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F26" t="n">
         <v>1.543693383369899</v>
@@ -2599,7 +2599,7 @@
         <v>-0.9731993702683203</v>
       </c>
       <c r="E27" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F27" t="n">
         <v>1.543693383369899</v>
@@ -2669,7 +2669,7 @@
         <v>-1.155453875685647</v>
       </c>
       <c r="E28" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F28" t="n">
         <v>-0.3726605901749289</v>
@@ -2743,7 +2743,7 @@
         <v>1.031600189322276</v>
       </c>
       <c r="E29" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F29" t="n">
         <v>-0.8719922593380179</v>
@@ -2817,7 +2817,7 @@
         <v>-0.6086903594336665</v>
       </c>
       <c r="E30" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F30" t="n">
         <v>-0.1162470303344236</v>
@@ -2985,7 +2985,7 @@
         <v>0.7035420795710873</v>
       </c>
       <c r="E32" t="n">
-        <v>1.997601832234098</v>
+        <v>2.007019749859912</v>
       </c>
       <c r="F32" t="n">
         <v>-0.8719922593380179</v>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV32"/>
+  <dimension ref="A1:AV42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,23 +668,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.09332559573457906</v>
+        <v>1.754229965240363</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.046101172435251</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.468191854065507</v>
+        <v>-1.119728901910384</v>
       </c>
       <c r="F2" t="n">
-        <v>1.260288922493552</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G2" t="n">
         <v>2.532501625081374</v>
@@ -692,12 +692,8 @@
       <c r="H2" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I2" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.574342265380581</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -717,48 +713,36 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.8455523018335774</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2.447643452342835</v>
-      </c>
+        <v>0.4789626758927192</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-1.252955061685929</v>
+        <v>-1.177170690608487</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.029172219982066</v>
+        <v>-0.717609485188304</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>-1.383011493221171</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.6287902387221393</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>-0.5346190325260441</v>
+        <v>-0.2270051852725903</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-1.062031876845381</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.7585517458221516</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-0.7953548134718232</v>
+        <v>-0.8837296714616912</v>
       </c>
       <c r="AT2" t="n">
-        <v>-2.146130072729493</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-2.317802445329099</v>
-      </c>
+        <v>-1.872967535640399</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -766,34 +750,42 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.643079247984667</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3369270691499964</v>
+        <v>-0.5741962211938105</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2661312665695027</v>
+        <v>-0.4264358540163395</v>
       </c>
       <c r="E3" t="n">
-        <v>2.007019749859912</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4806241943182994</v>
+        <v>1.003875362653046</v>
       </c>
       <c r="G3" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H3" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4739900584237479</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.53483257912834</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -810,25 +802,49 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AC3" t="n">
+        <v>-0.6531795056844704</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.5786819836228141</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.5930609615795495</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.005600572526204695</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AI3" t="n">
+        <v>-0.2157867828524556</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-0.6236185998769401</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.9617288327673579</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-0.002201891143915388</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.1119875023548895</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.104171432533474</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.1473885058533249</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-0.717352023709632</v>
+      </c>
       <c r="AV3" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -836,34 +852,42 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>1.197432398919147</v>
+        <v>1.172123418631819</v>
       </c>
       <c r="D4" t="n">
-        <v>1.177403793656137</v>
+        <v>1.031600189322276</v>
       </c>
       <c r="E4" t="n">
-        <v>2.007019749859912</v>
+        <v>0.5849141883619763</v>
       </c>
       <c r="F4" t="n">
-        <v>1.624666086477427</v>
+        <v>-0.8719922593380179</v>
       </c>
       <c r="G4" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H4" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-3.778503172489181</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-6.342670026269265</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-1.770209776903699</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2.450095682585971</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -880,25 +904,49 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>0.08444104377769497</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.116140775092676</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.044754998112522</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-2.354846727233604</v>
+      </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>-2.460462653122692</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.7915474029517493</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.4072904364339175</v>
+      </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>-2.524890747829075</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1.174096606129149</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-3.817673089310177</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-1.223944825092253</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-1.363740211353516</v>
+      </c>
       <c r="AV4" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -906,41 +954,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.232229708664338</v>
+        <v>1.04557851719518</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5722394583502011</v>
+        <v>-1.046101172435251</v>
       </c>
       <c r="E5" t="n">
-        <v>2.007019749859912</v>
+        <v>-0.1779371393289693</v>
       </c>
       <c r="F5" t="n">
-        <v>1.786611492692483</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G5" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H5" t="n">
-        <v>4.806475834200292</v>
+        <v>-0.2080526428291888</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4710084373346808</v>
+        <v>4.253984041457463</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4264364253577941</v>
+        <v>2.679586215120728</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.004405008704159</v>
+        <v>2.058814064093999</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4576315517288156</v>
+        <v>2.531064644556918</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -958,25 +1006,49 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>0.3087354116068392</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4626918635274809</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.467199215796534</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.490365219539204</v>
+      </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>1.277226216546615</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.747057294910456</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.05987146165808682</v>
+      </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>1.103925282415576</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.5157505198823642</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.840340581630462</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.9689675622847957</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.6287172596363076</v>
+      </c>
       <c r="AV5" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -984,41 +1056,41 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C6" t="n">
-        <v>1.716266494809371</v>
+        <v>0.5647078917359482</v>
       </c>
       <c r="D6" t="n">
-        <v>1.104501991489206</v>
+        <v>-0.5722394583502011</v>
       </c>
       <c r="E6" t="n">
-        <v>2.007019749859912</v>
+        <v>0.6885112822459319</v>
       </c>
       <c r="F6" t="n">
         <v>1.786611492692483</v>
       </c>
       <c r="G6" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H6" t="n">
-        <v>4.806475834200292</v>
+        <v>-0.2080526428291888</v>
       </c>
       <c r="I6" t="n">
         <v>0.001490810544533536</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6089044548017132</v>
+        <v>0.01728109471056615</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5272045276949199</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5386005136997623</v>
+        <v>-0.4576315517288156</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1036,25 +1108,49 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-0.4127047478004194</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3300104735691543</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.6798366876576222</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.06535804181488621</v>
+      </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>0.1818506827600168</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.296886165775132</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1933328453984799</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>0.5019364907656042</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.4584802518020718</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.2739443472181795</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.7106338835243743</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.2820892282056113</v>
+      </c>
       <c r="AV6" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1062,34 +1158,42 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C7" t="n">
-        <v>1.323977300355787</v>
+        <v>-0.7007411226304503</v>
       </c>
       <c r="D7" t="n">
-        <v>1.541912804490791</v>
+        <v>1.323207397989999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.007019749859912</v>
+        <v>0.5849141883619763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3695891883107441</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G7" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H7" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1.951979649871683</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1106,25 +1210,49 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
+      <c r="AC7" t="n">
+        <v>-0.3478580755913458</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.07688993299171179</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.378388106185871</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.05005507963723335</v>
+      </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>-0.1663715591243329</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.6535203018191504</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.3507192944202439</v>
+      </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-0.05121786633857534</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.7487774521423054</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-0.1148054590266503</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.1234305822017316</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.3464184416879177</v>
+      </c>
       <c r="AV7" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1132,34 +1260,42 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C8" t="n">
-        <v>0.741870753747244</v>
+        <v>-0.4223423394698427</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.754493963767528</v>
+        <v>-1.082552073518716</v>
       </c>
       <c r="E8" t="n">
-        <v>2.007019749859912</v>
+        <v>0.06692871894219841</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1972197334419516</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G8" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H8" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7102396823633551</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.348433654915647</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.29300929589446</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.032948611842629</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1176,25 +1312,49 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>-0.6643527460639634</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.146905698379529</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.576353889471287</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.66947047503543</v>
+      </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>2.521627090590644</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.2270395147699882</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.6733075254182112</v>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>1.458201858683644</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-1.955151231850747</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.833759535754603</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1.974161787614887</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.723894821307765</v>
+      </c>
       <c r="AV8" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1202,34 +1362,42 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C9" t="n">
-        <v>1.804847925815019</v>
+        <v>0.6026713621669401</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.191904776769113</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E9" t="n">
-        <v>2.007019749859912</v>
+        <v>1.583213456698276</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1972197334419516</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G9" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H9" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2377404344841407</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.313871465494515</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.036716546414051</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1246,60 +1414,92 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>0.07818838982512208</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.4651964249483694</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.4268811252426229</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3271010516586157</v>
+      </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AI9" t="n">
+        <v>-0.2603360930184994</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.5556601863719236</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.7957318824180887</v>
+      </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>0.3899259104133622</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.745575481013643</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.09898932387625416</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.2128517888301623</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.1088416459519538</v>
+      </c>
       <c r="AV9" t="n">
-        <v>-0.1883756946268106</v>
+        <v>5.308540478011726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C10" t="n">
-        <v>1.437867711648763</v>
+        <v>0.678598303028924</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6451412605171318</v>
+        <v>-1.337708381102974</v>
       </c>
       <c r="E10" t="n">
-        <v>2.007019749859912</v>
+        <v>-0.4604746681033937</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.627737488341612</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G10" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H10" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5386005136997623</v>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1316,25 +1516,49 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>-0.3632102606226308</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.512170073120326</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.239966560635817</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.8867897653901261</v>
+      </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+      <c r="AI10" t="n">
+        <v>0.7094779100080542</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0.4496450613040627</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.1295935093719613</v>
+      </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>1.332121878044046</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.8750392009236018</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.7201108806802404</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.692319885077666</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.694650130483942</v>
+      </c>
       <c r="AV10" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1342,41 +1566,41 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.4729603000444986</v>
+        <v>-1.156302767802354</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.410610183269905</v>
+        <v>-1.374159282186439</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09518247181964085</v>
+        <v>-0.5829075972389774</v>
       </c>
       <c r="F11" t="n">
-        <v>1.570684284405742</v>
+        <v>0.7609572533304625</v>
       </c>
       <c r="G11" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H11" t="n">
-        <v>4.806475834200292</v>
+        <v>-0.2080526428291888</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.179757309153502</v>
+        <v>-2.597255052791145</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.018059785448941</v>
+        <v>-2.792929865722383</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2386002405046198</v>
+        <v>-2.536014545103239</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4576315517288156</v>
+        <v>-1.453863617157394</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1395,27 +1619,27 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
-        <v>-0.2574838419377251</v>
+        <v>0.002363364394671634</v>
       </c>
       <c r="AD11" t="n">
-        <v>-1.207810663264663</v>
+        <v>-1.446583299336549</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.5368080399575579</v>
+        <v>-1.63288239336717</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.5895666947753213</v>
+        <v>-1.260110393731166</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="n">
-        <v>-0.1503557522000063</v>
+        <v>-2.307113012912748</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.3989675015189203</v>
+        <v>-0.2998647179390167</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1636491408876873</v>
+        <v>0.8170647780412248</v>
       </c>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -1423,19 +1647,19 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
-        <v>-0.1305770642727867</v>
+        <v>-0.9545641351112686</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.408274397561845</v>
+        <v>-0.2689165353008325</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.09856729195274005</v>
+        <v>-5.65510040110348</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0.8554169196741922</v>
+        <v>-1.454996298176964</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.6784496238687691</v>
+        <v>-1.518264741494152</v>
       </c>
       <c r="AV11" t="n">
         <v>-0.1883756946268106</v>
@@ -1444,23 +1668,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2610001282880125</v>
+        <v>-0.09332559573457906</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09837774426515113</v>
+        <v>-1.046101172435251</v>
       </c>
       <c r="E12" t="n">
-        <v>2.007019749859912</v>
+        <v>1.526705950943391</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3591651396570075</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G12" t="n">
         <v>2.532501625081374</v>
@@ -1468,8 +1692,12 @@
       <c r="H12" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1488,25 +1716,49 @@
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>0.723656315969245</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-2.401283840856593</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.351276367085269</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.07538279859793</v>
+      </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>-1.40402583510261</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.5102707655693648</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.3743027098070484</v>
+      </c>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-0.9856724220139117</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.6750738871787255</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0.8407601367067606</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-2.119619449439449</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-2.384457714045919</v>
+      </c>
       <c r="AV12" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1514,20 +1766,20 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1344552268513727</v>
+        <v>-1.232229708664338</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.082552073518716</v>
+        <v>-0.5722394583502011</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1214296335740845</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F13" t="n">
         <v>1.786611492692483</v>
@@ -1542,10 +1794,14 @@
         <v>-0.4710084373346808</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1651869347333529</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+        <v>-0.4264364253577941</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1588,23 +1844,23 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1091462465640447</v>
+        <v>0.3369270691499964</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1567785633191066</v>
+        <v>0.2661312665695027</v>
       </c>
       <c r="E14" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F14" t="n">
-        <v>1.003875362653046</v>
+        <v>-1.087919467624759</v>
       </c>
       <c r="G14" t="n">
         <v>2.532501625081374</v>
@@ -1612,12 +1868,8 @@
       <c r="H14" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I14" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.574342265380581</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1662,23 +1914,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5267444213049562</v>
+        <v>1.197432398919147</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.301257480019509</v>
+        <v>1.177403793656137</v>
       </c>
       <c r="E15" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3695891883107441</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G15" t="n">
         <v>2.532501625081374</v>
@@ -1686,12 +1938,8 @@
       <c r="H15" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I15" t="n">
-        <v>-0.4710084373346808</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.1651869347333529</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1736,23 +1984,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08383726627671673</v>
+        <v>0.741870753747244</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6306402774041565</v>
+        <v>-0.754493963767528</v>
       </c>
       <c r="E16" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.438801181090714</v>
+        <v>1.935061448389618</v>
       </c>
       <c r="G16" t="n">
         <v>2.532501625081374</v>
@@ -1806,42 +2054,34 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.358774610100978</v>
+        <v>1.323977300355787</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9222474860718796</v>
+        <v>1.541912804490791</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.468191854065507</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3726605901749289</v>
+        <v>-0.7775241057125686</v>
       </c>
       <c r="G17" t="n">
-        <v>4.256064548547412</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H17" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.781484793578249</v>
-      </c>
-      <c r="J17" t="n">
-        <v>4.010738775325809</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.058814064093999</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.032948611842629</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
@@ -1858,49 +2098,25 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="n">
-        <v>-0.6046397244207872</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.185528293335922</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.000671248197561</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.236534809994035</v>
-      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="n">
-        <v>2.023383215046395</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0.2742514443983327</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>-0.3223804881868177</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="n">
-        <v>0.9492107555832001</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.7271026980668596</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>5.726817186723991</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.261424701179745</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.257081257060226</v>
-      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1908,23 +2124,23 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C18" t="n">
-        <v>1.235395869350139</v>
+        <v>1.716266494809371</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5212875741537604</v>
+        <v>1.104501991489206</v>
       </c>
       <c r="E18" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-0.9259740614097032</v>
       </c>
       <c r="G18" t="n">
         <v>2.532501625081374</v>
@@ -1933,16 +2149,16 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2347588133950737</v>
+        <v>0.001490810544533536</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4609986147789265</v>
+        <v>0.6089044548017132</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.004405008704159</v>
+        <v>0.5272045276949199</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9557475844431046</v>
+        <v>0.5386005136997623</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -1986,23 +2202,23 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7545252438909079</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.337708381102974</v>
+        <v>-1.191904776769113</v>
       </c>
       <c r="E19" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-1.087919467624759</v>
       </c>
       <c r="G19" t="n">
         <v>2.532501625081374</v>
@@ -2056,23 +2272,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C20" t="n">
-        <v>1.804847925815019</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9586983871553449</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E20" t="n">
-        <v>2.007019749859912</v>
+        <v>0.09518247181964085</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3591651396570075</v>
+        <v>-1.627737488341612</v>
       </c>
       <c r="G20" t="n">
         <v>2.532501625081374</v>
@@ -2080,10 +2296,18 @@
       <c r="H20" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>-1.179757309153502</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-1.018059785448941</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.2386002405046198</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -2100,25 +2324,49 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
+      <c r="AC20" t="n">
+        <v>-0.1507635441013704</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.230651184088951</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.5865816963899743</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.5855412026895986</v>
+      </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>-0.1421803044613464</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.2592967811914368</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.1098269685987385</v>
+      </c>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>-0.1334298458978723</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.481030588123307</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>-0.1210574773221581</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-0.9213311473271634</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-0.6260105407728102</v>
+      </c>
       <c r="AV20" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2126,23 +2374,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9443425960458677</v>
+        <v>1.437867711648763</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4264358540163395</v>
+        <v>-0.6451412605171318</v>
       </c>
       <c r="E21" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F21" t="n">
-        <v>1.003875362653046</v>
+        <v>-1.627737488341612</v>
       </c>
       <c r="G21" t="n">
         <v>2.532501625081374</v>
@@ -2196,23 +2444,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C22" t="n">
-        <v>-1.14364827765869</v>
+        <v>0.2610001282880125</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6670911784876219</v>
+        <v>-0.09837774426515113</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9993025638977986</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9498935605813611</v>
+        <v>-0.9259740614097032</v>
       </c>
       <c r="G22" t="n">
         <v>2.532501625081374</v>
@@ -2220,18 +2468,10 @@
       <c r="H22" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I22" t="n">
-        <v>-0.2347588133950737</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.01728109471056615</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -2248,49 +2488,25 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="n">
-        <v>0.3875367961142823</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>-1.509756752109526</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>-1.69054836818864</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>-1.101313955924437</v>
-      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="n">
-        <v>-0.7258008289145049</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.01256923397797134</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>-0.2008114170056553</v>
-      </c>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
       <c r="AM22" t="inlineStr"/>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="n">
-        <v>-1.254832368340777</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>-0.9662846218324346</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>-0.8549355163277714</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>-1.772725364297222</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>-2.090889567610786</v>
-      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
       <c r="AV22" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2298,23 +2514,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.8019770437797622</v>
+        <v>0.1091462465640447</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3899849529328742</v>
+        <v>0.1567785633191066</v>
       </c>
       <c r="E23" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F23" t="n">
-        <v>1.260288922493552</v>
+        <v>-0.7775241057125686</v>
       </c>
       <c r="G23" t="n">
         <v>2.532501625081374</v>
@@ -2322,8 +2538,12 @@
       <c r="H23" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -2368,23 +2588,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1.607676405679417</v>
       </c>
       <c r="C24" t="n">
-        <v>1.121505458057164</v>
+        <v>0.1344552268513727</v>
       </c>
       <c r="D24" t="n">
-        <v>1.068051090405741</v>
+        <v>-1.082552073518716</v>
       </c>
       <c r="E24" t="n">
-        <v>2.007019749859912</v>
+        <v>1.423108857059435</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7609572533304625</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G24" t="n">
         <v>2.532501625081374</v>
@@ -2393,10 +2613,10 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9435076852138952</v>
+        <v>-0.4710084373346808</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7222481054033678</v>
+        <v>0.1651869347333529</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -2442,23 +2662,23 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.194561516883891</v>
+        <v>0.08383726627671673</v>
       </c>
       <c r="D25" t="n">
-        <v>1.323207397989999</v>
+        <v>0.6306402774041565</v>
       </c>
       <c r="E25" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9498935605813611</v>
+        <v>-1.438801181090714</v>
       </c>
       <c r="G25" t="n">
         <v>2.532501625081374</v>
@@ -2512,23 +2732,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2198704971712189</v>
+        <v>0.5267444213049562</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.483511985436836</v>
+        <v>-1.301257480019509</v>
       </c>
       <c r="E26" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F26" t="n">
-        <v>1.543693383369899</v>
+        <v>1.935061448389618</v>
       </c>
       <c r="G26" t="n">
         <v>2.532501625081374</v>
@@ -2537,10 +2757,10 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.707258061274288</v>
+        <v>-0.4710084373346808</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1306247453122206</v>
+        <v>0.1651869347333529</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -2586,34 +2806,42 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2989635987190045</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9731993702683203</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E27" t="n">
-        <v>2.007019749859912</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F27" t="n">
-        <v>1.543693383369899</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G27" t="n">
-        <v>2.532501625081374</v>
+        <v>4.256064548547412</v>
       </c>
       <c r="H27" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>3.781484793578249</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.010738775325809</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.058814064093999</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2.032948611842629</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2630,25 +2858,49 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
+      <c r="AC27" t="n">
+        <v>-0.6511238405732754</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.177956939159982</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.922177505230173</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.305436783739022</v>
+      </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>1.936162242306585</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.3450153206147231</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.3949512647078243</v>
+      </c>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
+      <c r="AQ27" t="n">
+        <v>0.9454402959528412</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.7133681774783123</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.83248428806029</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.239416968149064</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.259839768476614</v>
+      </c>
       <c r="AV27" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2656,23 +2908,23 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C28" t="n">
-        <v>1.602376083516395</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.155453875685647</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E28" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3726605901749289</v>
+        <v>-0.3591651396570075</v>
       </c>
       <c r="G28" t="n">
         <v>2.532501625081374</v>
@@ -2680,12 +2932,8 @@
       <c r="H28" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I28" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-0.4264364253577941</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2730,23 +2978,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C29" t="n">
-        <v>1.450522201792427</v>
+        <v>0.7545252438909079</v>
       </c>
       <c r="D29" t="n">
-        <v>1.031600189322276</v>
+        <v>-1.337708381102974</v>
       </c>
       <c r="E29" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.8719922593380179</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G29" t="n">
         <v>2.532501625081374</v>
@@ -2754,12 +3002,8 @@
       <c r="H29" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I29" t="n">
-        <v>-0.707258061274288</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-0.2785305853350074</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2804,23 +3048,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4128540100119804</v>
+        <v>1.235395869350139</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6086903594336665</v>
+        <v>0.5212875741537604</v>
       </c>
       <c r="E30" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1162470303344236</v>
+        <v>1.908070547353775</v>
       </c>
       <c r="G30" t="n">
         <v>2.532501625081374</v>
@@ -2828,10 +3072,18 @@
       <c r="H30" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.4609986147789265</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.9557475844431046</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2874,23 +3126,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2325249873148829</v>
+        <v>1.121505458057164</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6815921616005972</v>
+        <v>1.068051090405741</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1214296335740845</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F31" t="n">
-        <v>1.624666086477427</v>
+        <v>-1.276855774875658</v>
       </c>
       <c r="G31" t="n">
         <v>2.532501625081374</v>
@@ -2902,7 +3154,7 @@
         <v>-0.9435076852138952</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.574342265380581</v>
+        <v>-0.7222481054033678</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2922,73 +3174,49 @@
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="n">
-        <v>-0.875453107318633</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>-2.178252975683592</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>-1.962803158575299</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>-1.318078721308519</v>
-      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="n">
-        <v>-0.5551805107969936</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.260868206617462</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>-0.6733971379630761</v>
-      </c>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="inlineStr"/>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="n">
-        <v>-1.023368041032661</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.2866869599239795</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>-0.6882651275083299</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>-1.894469010631035</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>-1.780719862066613</v>
-      </c>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="n">
-        <v>5.308540478011726</v>
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C32" t="n">
-        <v>1.058233007338844</v>
+        <v>-0.194561516883891</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7035420795710873</v>
+        <v>1.323207397989999</v>
       </c>
       <c r="E32" t="n">
-        <v>2.007019749859912</v>
+        <v>2.044691420363169</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8719922593380179</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G32" t="n">
         <v>2.532501625081374</v>
@@ -2996,12 +3224,8 @@
       <c r="H32" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I32" t="n">
-        <v>-0.707258061274288</v>
-      </c>
-      <c r="J32" t="n">
-        <v>-0.1306247453122206</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -3043,6 +3267,782 @@
         <v>-0.1883756946268106</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.2198704971712189</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-1.483511985436836</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.02177887670897437</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.1306247453122206</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.9443425960458677</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.4264358540163395</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.003875362653046</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.14364827765869</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.6670911784876219</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9993025638977986</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.9498935605813611</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="n">
+        <v>0.4461113399775876</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-1.524762239756724</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>-1.638281620181021</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>-1.050311109373125</v>
+      </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="n">
+        <v>-0.7628951317308241</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>-0.09626131107792331</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-0.1422446830399108</v>
+      </c>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="n">
+        <v>-1.27661724620507</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>-1.03481080131474</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>-0.7700652620771546</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>-1.7252342179863</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>-2.110314085501147</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.8019770437797622</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.3899849529328742</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.260288922493552</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.2989635987190045</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.9731993702683203</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.935061448389618</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.602376083516395</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-1.155453875685647</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-0.3726605901749289</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-0.4264364253577941</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.450522201792427</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.031600189322276</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.1025937983224562</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.8719922593380179</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.2325249873148829</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.6815921616005972</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.1214296335740845</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.624666086477427</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.574342265380581</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="n">
+        <v>-0.8447939548066603</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-2.192270339726984</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>-1.955806121344441</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>-1.330490655239496</v>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="n">
+        <v>-0.5536103179206151</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.235383801553074</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>-0.7773359721053614</v>
+      </c>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="n">
+        <v>-1.031537370231771</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.2598898397375366</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>-0.6794410950955772</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>-1.906322242899729</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>-1.787568249784367</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>5.308540478011726</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.607676405679417</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.4128540100119804</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-0.6086903594336665</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.1162470303344236</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.058233007338844</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7035420795710873</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.044691420363169</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.8719922593380179</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.532501625081374</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.707258061274288</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.1306247453122206</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV42"/>
+  <dimension ref="A1:AV33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,34 +668,42 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W67CmLPh</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C2" t="n">
-        <v>1.754229965240363</v>
+        <v>-1.156302767802354</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9222474860718796</v>
+        <v>-1.374159282186439</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.119728901910384</v>
+        <v>-0.5829075972389774</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3726605901749289</v>
+        <v>0.7609572533304625</v>
       </c>
       <c r="G2" t="n">
-        <v>2.532501625081374</v>
+        <v>-0.9146242218507028</v>
       </c>
       <c r="H2" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-2.597255052791145</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-2.792929865722383</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-2.536014545103239</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1.453863617157394</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -713,36 +721,48 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>0.4789626758927192</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>0.002363364394671634</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.446583299336549</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-1.177170690608487</v>
+        <v>-1.63288239336717</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.717609485188304</v>
+        <v>-1.260110393731166</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>-2.307113012912748</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-0.2998647179390167</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-0.2270051852725903</v>
+        <v>0.8170647780412248</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>-0.9545641351112686</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.2689165353008325</v>
+      </c>
       <c r="AS2" t="n">
-        <v>-0.8837296714616912</v>
+        <v>-5.65510040110348</v>
       </c>
       <c r="AT2" t="n">
-        <v>-1.872967535640399</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>-1.454996298176964</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-1.518264741494152</v>
+      </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -750,42 +770,38 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.5741962211938105</v>
+        <v>-0.09332559573457906</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4264358540163395</v>
+        <v>-1.046101172435251</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1214296335740845</v>
+        <v>1.526705950943391</v>
       </c>
       <c r="F3" t="n">
-        <v>1.003875362653046</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2080526428291888</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4739900584237479</v>
+        <v>-0.9435076852138952</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1651869347333529</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.5272045276949199</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.53483257912834</v>
-      </c>
+        <v>-0.574342265380581</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -803,27 +819,27 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-0.6531795056844704</v>
+        <v>0.723656315969245</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.5786819836228141</v>
+        <v>-2.401283840856593</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.5930609615795495</v>
+        <v>-1.351276367085269</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.005600572526204695</v>
+        <v>-1.07538279859793</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-0.2157867828524556</v>
+        <v>-1.40402583510261</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.6236185998769401</v>
+        <v>0.5102707655693648</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.9617288327673579</v>
+        <v>-0.3743027098070484</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
@@ -831,19 +847,19 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-0.002201891143915388</v>
+        <v>-0.9856724220139117</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1119875023548895</v>
+        <v>0.6750738871787255</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.104171432533474</v>
+        <v>-0.8407601367067606</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1473885058533249</v>
+        <v>-2.119619449439449</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.717352023709632</v>
+        <v>-2.384457714045919</v>
       </c>
       <c r="AV3" t="n">
         <v>-0.1883756946268106</v>
@@ -852,42 +868,34 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>1.172123418631819</v>
+        <v>1.197432398919147</v>
       </c>
       <c r="D4" t="n">
-        <v>1.031600189322276</v>
+        <v>1.177403793656137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5849141883619763</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8719922593380179</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2080526428291888</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-3.778503172489181</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-6.342670026269265</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-1.770209776903699</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-2.450095682585971</v>
-      </c>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -904,49 +912,25 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>0.08444104377769497</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>-1.116140775092676</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-1.044754998112522</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-2.354846727233604</v>
-      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="n">
-        <v>-2.460462653122692</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.7915474029517493</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.4072904364339175</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>-2.524890747829075</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-1.174096606129149</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-3.817673089310177</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-1.223944825092253</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-1.363740211353516</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -954,41 +938,41 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>1.04557851719518</v>
+        <v>-1.232229708664338</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.046101172435251</v>
+        <v>-0.5722394583502011</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1779371393289693</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F5" t="n">
-        <v>1.260288922493552</v>
+        <v>1.786611492692483</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2080526428291888</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I5" t="n">
-        <v>4.253984041457463</v>
+        <v>-0.4710084373346808</v>
       </c>
       <c r="J5" t="n">
-        <v>2.679586215120728</v>
+        <v>-0.4264364253577941</v>
       </c>
       <c r="K5" t="n">
-        <v>2.058814064093999</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L5" t="n">
-        <v>2.531064644556918</v>
+        <v>-0.4576315517288156</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1006,49 +990,25 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
-        <v>0.3087354116068392</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.4626918635274809</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.467199215796534</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.490365219539204</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>1.277226216546615</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.747057294910456</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-0.05987146165808682</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>1.103925282415576</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.5157505198823642</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.840340581630462</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0.9689675622847957</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.6287172596363076</v>
-      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1056,42 +1016,34 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5647078917359482</v>
+        <v>0.3369270691499964</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5722394583502011</v>
+        <v>0.2661312665695027</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6885112822459319</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F6" t="n">
-        <v>1.786611492692483</v>
+        <v>-1.087919467624759</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2080526428291888</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.001490810544533536</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.01728109471056615</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1108,49 +1060,25 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>-0.4127047478004194</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.3300104735691543</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.6798366876576222</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.06535804181488621</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="n">
-        <v>0.1818506827600168</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.296886165775132</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-0.1933328453984799</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>0.5019364907656042</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0.4584802518020718</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.2739443472181795</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.7106338835243743</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.2820892282056113</v>
-      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1158,41 +1086,41 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.7007411226304503</v>
+        <v>1.716266494809371</v>
       </c>
       <c r="D7" t="n">
-        <v>1.323207397989999</v>
+        <v>1.104501991489206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5849141883619763</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9498935605813611</v>
+        <v>-0.9259740614097032</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2080526428291888</v>
+        <v>4.806475834200292</v>
       </c>
       <c r="I7" t="n">
         <v>0.001490810544533536</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2785305853350074</v>
+        <v>0.6089044548017132</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.004405008704159</v>
+        <v>0.5272045276949199</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.951979649871683</v>
+        <v>0.5386005136997623</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1210,49 +1138,25 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
-        <v>-0.3478580755913458</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.07688993299171179</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.378388106185871</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.05005507963723335</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="n">
-        <v>-0.1663715591243329</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.6535203018191504</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.3507192944202439</v>
-      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>-0.05121786633857534</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-0.7487774521423054</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>-0.1148054590266503</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.1234305822017316</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-0.3464184416879177</v>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1260,42 +1164,34 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4223423394698427</v>
+        <v>0.741870753747244</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.082552073518716</v>
+        <v>-0.754493963767528</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06692871894219841</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F8" t="n">
-        <v>1.786611492692483</v>
+        <v>1.935061448389618</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2080526428291888</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.7102396823633551</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.348433654915647</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.29300929589446</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.032948611842629</v>
-      </c>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1312,49 +1208,25 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="n">
-        <v>-0.6643527460639634</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.146905698379529</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.576353889471287</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.66947047503543</v>
-      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="n">
-        <v>2.521627090590644</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.2270395147699882</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.6733075254182112</v>
-      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>1.458201858683644</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-1.955151231850747</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.833759535754603</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.974161787614887</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.723894821307765</v>
-      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1362,42 +1234,34 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6026713621669401</v>
+        <v>1.323977300355787</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9222474860718796</v>
+        <v>1.541912804490791</v>
       </c>
       <c r="E9" t="n">
-        <v>1.583213456698276</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3726605901749289</v>
+        <v>-0.7775241057125686</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2080526428291888</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.2377404344841407</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1.313871465494515</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5272045276949199</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.036716546414051</v>
-      </c>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1414,92 +1278,60 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="n">
-        <v>0.07818838982512208</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.4651964249483694</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.4268811252426229</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.3271010516586157</v>
-      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>-0.2603360930184994</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.5556601863719236</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.7957318824180887</v>
-      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>0.3899259104133622</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.745575481013643</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.09898932387625416</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.2128517888301623</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-0.1088416459519538</v>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>5.308540478011726</v>
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C10" t="n">
-        <v>0.678598303028924</v>
+        <v>0.2610001282880125</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.337708381102974</v>
+        <v>-0.09837774426515113</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4604746681033937</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-0.9259740614097032</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2080526428291888</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.2347588133950737</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.1651869347333529</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.5272045276949199</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5386005136997623</v>
-      </c>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -1516,49 +1348,25 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="n">
-        <v>-0.3632102606226308</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.512170073120326</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.239966560635817</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.8867897653901261</v>
-      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="n">
-        <v>0.7094779100080542</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-0.4496450613040627</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-0.1295935093719613</v>
-      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>1.332121878044046</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.8750392009236018</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.7201108806802404</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.692319885077666</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.694650130483942</v>
-      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1566,42 +1374,34 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.156302767802354</v>
+        <v>1.437867711648763</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.374159282186439</v>
+        <v>-0.6451412605171318</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5829075972389774</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7609572533304625</v>
+        <v>-1.627737488341612</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9146242218507028</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2080526428291888</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-2.597255052791145</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-2.792929865722383</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-2.536014545103239</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.453863617157394</v>
-      </c>
+        <v>4.806475834200292</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1618,49 +1418,25 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="n">
-        <v>0.002363364394671634</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-1.446583299336549</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-1.63288239336717</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>-1.260110393731166</v>
-      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="n">
-        <v>-2.307113012912748</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.2998647179390167</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.8170647780412248</v>
-      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
-        <v>-0.9545641351112686</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>-0.2689165353008325</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>-5.65510040110348</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>-1.454996298176964</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-1.518264741494152</v>
-      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1668,23 +1444,23 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.09332559573457906</v>
+        <v>0.1091462465640447</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.046101172435251</v>
+        <v>0.1567785633191066</v>
       </c>
       <c r="E12" t="n">
-        <v>1.526705950943391</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F12" t="n">
-        <v>1.260288922493552</v>
+        <v>-0.7775241057125686</v>
       </c>
       <c r="G12" t="n">
         <v>2.532501625081374</v>
@@ -1716,49 +1492,25 @@
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="n">
-        <v>0.723656315969245</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-2.401283840856593</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-1.351276367085269</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-1.07538279859793</v>
-      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="n">
-        <v>-1.40402583510261</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.5102707655693648</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-0.3743027098070484</v>
-      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="n">
-        <v>-0.9856724220139117</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.6750738871787255</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>-0.8407601367067606</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>-2.119619449439449</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-2.384457714045919</v>
-      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1766,20 +1518,20 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.572273563374167</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.232229708664338</v>
+        <v>0.1344552268513727</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.5722394583502011</v>
+        <v>-1.082552073518716</v>
       </c>
       <c r="E13" t="n">
-        <v>2.044691420363169</v>
+        <v>1.423108857059435</v>
       </c>
       <c r="F13" t="n">
         <v>1.786611492692483</v>
@@ -1794,14 +1546,10 @@
         <v>-0.4710084373346808</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4264364253577941</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1844,20 +1592,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1.678482090289918</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3369270691499964</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2661312665695027</v>
+        <v>-1.191904776769113</v>
       </c>
       <c r="E14" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F14" t="n">
         <v>-1.087919467624759</v>
@@ -1914,23 +1662,23 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C15" t="n">
-        <v>1.197432398919147</v>
+        <v>-0.4729603000444986</v>
       </c>
       <c r="D15" t="n">
-        <v>1.177403793656137</v>
+        <v>-1.410610183269905</v>
       </c>
       <c r="E15" t="n">
-        <v>2.044691420363169</v>
+        <v>0.09518247181964085</v>
       </c>
       <c r="F15" t="n">
-        <v>1.624666086477427</v>
+        <v>-1.627737488341612</v>
       </c>
       <c r="G15" t="n">
         <v>2.532501625081374</v>
@@ -1938,10 +1686,18 @@
       <c r="H15" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>-1.179757309153502</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.018059785448941</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.2386002405046198</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -1958,25 +1714,49 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>-0.1507635441013704</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.230651184088951</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.5865816963899743</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.5855412026895986</v>
+      </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>-0.1421803044613464</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.2592967811914368</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.1098269685987385</v>
+      </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>-0.1334298458978723</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.481030588123307</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.1210574773221581</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.9213311473271634</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.6260105407728102</v>
+      </c>
       <c r="AV15" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -1984,23 +1764,23 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C16" t="n">
-        <v>0.741870753747244</v>
+        <v>0.08383726627671673</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.754493963767528</v>
+        <v>0.6306402774041565</v>
       </c>
       <c r="E16" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F16" t="n">
-        <v>1.935061448389618</v>
+        <v>-1.438801181090714</v>
       </c>
       <c r="G16" t="n">
         <v>2.532501625081374</v>
@@ -2054,23 +1834,23 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1.678482090289918</v>
       </c>
       <c r="C17" t="n">
-        <v>1.323977300355787</v>
+        <v>0.5267444213049562</v>
       </c>
       <c r="D17" t="n">
-        <v>1.541912804490791</v>
+        <v>-1.301257480019509</v>
       </c>
       <c r="E17" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7775241057125686</v>
+        <v>1.935061448389618</v>
       </c>
       <c r="G17" t="n">
         <v>2.532501625081374</v>
@@ -2078,8 +1858,12 @@
       <c r="H17" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>-0.4710084373346808</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.1651869347333529</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -2124,41 +1908,41 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C18" t="n">
-        <v>1.716266494809371</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D18" t="n">
-        <v>1.104501991489206</v>
+        <v>0.9222474860718796</v>
       </c>
       <c r="E18" t="n">
-        <v>2.044691420363169</v>
+        <v>-1.468191854065507</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9259740614097032</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G18" t="n">
-        <v>2.532501625081374</v>
+        <v>4.256064548547412</v>
       </c>
       <c r="H18" t="n">
         <v>4.806475834200292</v>
       </c>
       <c r="I18" t="n">
-        <v>0.001490810544533536</v>
+        <v>3.781484793578249</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6089044548017132</v>
+        <v>4.010738775325809</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5272045276949199</v>
+        <v>2.058814064093999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5386005136997623</v>
+        <v>2.032948611842629</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2176,25 +1960,49 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>-0.6511238405732754</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.177956939159982</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.922177505230173</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.305436783739022</v>
+      </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>1.936162242306585</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.3450153206147231</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.3949512647078243</v>
+      </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>0.9454402959528412</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0.7133681774783123</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.83248428806029</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.239416968149064</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.259839768476614</v>
+      </c>
       <c r="AV18" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2202,23 +2010,23 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1.678482090289918</v>
       </c>
       <c r="C19" t="n">
-        <v>1.804847925815019</v>
+        <v>1.235395869350139</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.191904776769113</v>
+        <v>0.5212875741537604</v>
       </c>
       <c r="E19" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.087919467624759</v>
+        <v>1.908070547353775</v>
       </c>
       <c r="G19" t="n">
         <v>2.532501625081374</v>
@@ -2226,10 +2034,18 @@
       <c r="H19" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.4609986147789265</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.9557475844431046</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -2272,23 +2088,23 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.4729603000444986</v>
+        <v>1.804847925815019</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.410610183269905</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09518247181964085</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.627737488341612</v>
+        <v>-0.3591651396570075</v>
       </c>
       <c r="G20" t="n">
         <v>2.532501625081374</v>
@@ -2296,18 +2112,10 @@
       <c r="H20" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I20" t="n">
-        <v>-1.179757309153502</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-1.018059785448941</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-0.2386002405046198</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -2324,49 +2132,25 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="n">
-        <v>-0.1507635441013704</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-1.230651184088951</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-0.5865816963899743</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>-0.5855412026895986</v>
-      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="n">
-        <v>-0.1421803044613464</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>-0.2592967811914368</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0.1098269685987385</v>
-      </c>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="n">
-        <v>-0.1334298458978723</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.481030588123307</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>-0.1210574773221581</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>-0.9213311473271634</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>-0.6260105407728102</v>
-      </c>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2374,23 +2158,23 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.678482090289918</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C21" t="n">
-        <v>1.437867711648763</v>
+        <v>0.7545252438909079</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6451412605171318</v>
+        <v>-1.337708381102974</v>
       </c>
       <c r="E21" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.627737488341612</v>
+        <v>-0.9934513139993099</v>
       </c>
       <c r="G21" t="n">
         <v>2.532501625081374</v>
@@ -2444,23 +2228,23 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2610001282880125</v>
+        <v>0.9443425960458677</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09837774426515113</v>
+        <v>-0.4264358540163395</v>
       </c>
       <c r="E22" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9259740614097032</v>
+        <v>1.003875362653046</v>
       </c>
       <c r="G22" t="n">
         <v>2.532501625081374</v>
@@ -2514,23 +2298,23 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1091462465640447</v>
+        <v>-1.14364827765869</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1567785633191066</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E23" t="n">
-        <v>2.044691420363169</v>
+        <v>0.9993025638977986</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7775241057125686</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G23" t="n">
         <v>2.532501625081374</v>
@@ -2539,13 +2323,17 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9435076852138952</v>
+        <v>-0.2347588133950737</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.574342265380581</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -2562,25 +2350,49 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
+      <c r="AC23" t="n">
+        <v>0.4461113399775876</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-1.524762239756724</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-1.638281620181021</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-1.050311109373125</v>
+      </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>-0.7628951317308241</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.09626131107792331</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-0.1422446830399108</v>
+      </c>
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
+      <c r="AQ23" t="n">
+        <v>-1.27661724620507</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>-1.03481080131474</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>-0.7700652620771546</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-1.7252342179863</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>-2.110314085501147</v>
+      </c>
       <c r="AV23" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2588,23 +2400,23 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1344552268513727</v>
+        <v>-0.8019770437797622</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.082552073518716</v>
+        <v>-0.3899849529328742</v>
       </c>
       <c r="E24" t="n">
-        <v>1.423108857059435</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F24" t="n">
-        <v>1.786611492692483</v>
+        <v>1.260288922493552</v>
       </c>
       <c r="G24" t="n">
         <v>2.532501625081374</v>
@@ -2612,12 +2424,8 @@
       <c r="H24" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I24" t="n">
-        <v>-0.4710084373346808</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1651869347333529</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -2662,23 +2470,23 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08383726627671673</v>
+        <v>1.121505458057164</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6306402774041565</v>
+        <v>1.068051090405741</v>
       </c>
       <c r="E25" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.438801181090714</v>
+        <v>-1.276855774875658</v>
       </c>
       <c r="G25" t="n">
         <v>2.532501625081374</v>
@@ -2686,8 +2494,12 @@
       <c r="H25" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.7222481054033678</v>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -2732,23 +2544,23 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5267444213049562</v>
+        <v>-0.194561516883891</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.301257480019509</v>
+        <v>1.323207397989999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F26" t="n">
-        <v>1.935061448389618</v>
+        <v>0.9498935605813611</v>
       </c>
       <c r="G26" t="n">
         <v>2.532501625081374</v>
@@ -2756,12 +2568,8 @@
       <c r="H26" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I26" t="n">
-        <v>-0.4710084373346808</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1651869347333529</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2806,42 +2614,38 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.358774610100978</v>
+        <v>-0.2198704971712189</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9222474860718796</v>
+        <v>-1.483511985436836</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.468191854065507</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3726605901749289</v>
+        <v>-0.02177887670897437</v>
       </c>
       <c r="G27" t="n">
-        <v>4.256064548547412</v>
+        <v>2.532501625081374</v>
       </c>
       <c r="H27" t="n">
         <v>4.806475834200292</v>
       </c>
       <c r="I27" t="n">
-        <v>3.781484793578249</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J27" t="n">
-        <v>4.010738775325809</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.058814064093999</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.032948611842629</v>
-      </c>
+        <v>-0.1306247453122206</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2858,49 +2662,25 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="n">
-        <v>-0.6511238405732754</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.177956939159982</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.922177505230173</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.305436783739022</v>
-      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="n">
-        <v>1.936162242306585</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.3450153206147231</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>-0.3949512647078243</v>
-      </c>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="n">
-        <v>0.9454402959528412</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0.7133681774783123</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>5.83248428806029</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.239416968149064</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>1.259839768476614</v>
-      </c>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="n">
         <v>-0.1883756946268106</v>
       </c>
@@ -2908,23 +2688,23 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C28" t="n">
-        <v>1.804847925815019</v>
+        <v>0.2989635987190045</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9586983871553449</v>
+        <v>-0.9731993702683203</v>
       </c>
       <c r="E28" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3591651396570075</v>
+        <v>1.935061448389618</v>
       </c>
       <c r="G28" t="n">
         <v>2.532501625081374</v>
@@ -2978,23 +2758,23 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7545252438909079</v>
+        <v>1.602376083516395</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.337708381102974</v>
+        <v>-1.155453875685647</v>
       </c>
       <c r="E29" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G29" t="n">
         <v>2.532501625081374</v>
@@ -3002,8 +2782,12 @@
       <c r="H29" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.4264364253577941</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -3048,23 +2832,23 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C30" t="n">
-        <v>1.235395869350139</v>
+        <v>1.450522201792427</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5212875741537604</v>
+        <v>1.031600189322276</v>
       </c>
       <c r="E30" t="n">
-        <v>2.044691420363169</v>
+        <v>-0.1025937983224562</v>
       </c>
       <c r="F30" t="n">
-        <v>1.908070547353775</v>
+        <v>-0.8719922593380179</v>
       </c>
       <c r="G30" t="n">
         <v>2.532501625081374</v>
@@ -3073,17 +2857,13 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2347588133950737</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4609986147789265</v>
-      </c>
-      <c r="K30" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L30" t="n">
-        <v>-0.9557475844431046</v>
-      </c>
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -3126,23 +2906,23 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.678482090289918</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C31" t="n">
-        <v>1.121505458057164</v>
+        <v>1.058233007338844</v>
       </c>
       <c r="D31" t="n">
-        <v>1.068051090405741</v>
+        <v>0.7035420795710873</v>
       </c>
       <c r="E31" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.276855774875658</v>
+        <v>-0.8719922593380179</v>
       </c>
       <c r="G31" t="n">
         <v>2.532501625081374</v>
@@ -3151,10 +2931,10 @@
         <v>4.806475834200292</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9435076852138952</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.7222481054033678</v>
+        <v>-0.1306247453122206</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -3200,23 +2980,23 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.194561516883891</v>
+        <v>-0.2325249873148829</v>
       </c>
       <c r="D32" t="n">
-        <v>1.323207397989999</v>
+        <v>-0.6815921616005972</v>
       </c>
       <c r="E32" t="n">
-        <v>2.044691420363169</v>
+        <v>-0.1214296335740845</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9498935605813611</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G32" t="n">
         <v>2.532501625081374</v>
@@ -3224,8 +3004,12 @@
       <c r="H32" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>-0.9435076852138952</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.574342265380581</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -3244,49 +3028,73 @@
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>-0.8447939548066603</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-2.192270339726984</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>-1.955806121344441</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>-1.330490655239496</v>
+      </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
+      <c r="AI32" t="n">
+        <v>-0.5536103179206151</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.235383801553074</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>-0.7773359721053614</v>
+      </c>
       <c r="AL32" t="inlineStr"/>
       <c r="AM32" t="inlineStr"/>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
+      <c r="AQ32" t="n">
+        <v>-1.031537370231771</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.2598898397375366</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>-0.6794410950955772</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>-1.906322242899729</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>-1.787568249784367</v>
+      </c>
       <c r="AV32" t="n">
-        <v>-0.1883756946268106</v>
+        <v>5.308540478011726</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.678482090289918</v>
+        <v>1.607676405679417</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2198704971712189</v>
+        <v>0.4128540100119804</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.483511985436836</v>
+        <v>-0.6086903594336665</v>
       </c>
       <c r="E33" t="n">
-        <v>2.044691420363169</v>
+        <v>2.054109337988983</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.02177887670897437</v>
+        <v>-0.1162470303344236</v>
       </c>
       <c r="G33" t="n">
         <v>2.532501625081374</v>
@@ -3294,12 +3102,8 @@
       <c r="H33" t="n">
         <v>4.806475834200292</v>
       </c>
-      <c r="I33" t="n">
-        <v>-0.707258061274288</v>
-      </c>
-      <c r="J33" t="n">
-        <v>-0.1306247453122206</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -3341,708 +3145,6 @@
         <v>-0.1883756946268106</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.9443425960458677</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.4264358540163395</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.044691420363169</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.003875362653046</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H34" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>f1nnRRDE</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.14364827765869</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.6670911784876219</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.9993025638977986</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.9498935605813611</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H35" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I35" t="n">
-        <v>-0.2347588133950737</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.01728109471056615</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="n">
-        <v>0.4461113399775876</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>-1.524762239756724</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>-1.638281620181021</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>-1.050311109373125</v>
-      </c>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="n">
-        <v>-0.7628951317308241</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>-0.09626131107792331</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>-0.1422446830399108</v>
-      </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="n">
-        <v>-1.27661724620507</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>-1.03481080131474</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>-0.7700652620771546</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>-1.7252342179863</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>-2.110314085501147</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>MZjh9ghT</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.8019770437797622</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-0.3899849529328742</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2.044691420363169</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.260288922493552</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1.678482090289918</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.2989635987190045</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.9731993702683203</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2.044691420363169</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.935061448389618</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.602376083516395</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-1.155453875685647</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2.044691420363169</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-0.3726605901749289</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J38" t="n">
-        <v>-0.4264364253577941</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1.450522201792427</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.031600189322276</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.1025937983224562</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.8719922593380179</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H39" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I39" t="n">
-        <v>-0.707258061274288</v>
-      </c>
-      <c r="J39" t="n">
-        <v>-0.2785305853350074</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.2325249873148829</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.6815921616005972</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-0.1214296335740845</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1.624666086477427</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H40" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I40" t="n">
-        <v>-0.9435076852138952</v>
-      </c>
-      <c r="J40" t="n">
-        <v>-0.574342265380581</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="n">
-        <v>-0.8447939548066603</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>-2.192270339726984</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>-1.955806121344441</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>-1.330490655239496</v>
-      </c>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="n">
-        <v>-0.5536103179206151</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.235383801553074</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>-0.7773359721053614</v>
-      </c>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="n">
-        <v>-1.031537370231771</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.2598898397375366</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>-0.6794410950955772</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>-1.906322242899729</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>-1.787568249784367</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>5.308540478011726</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1.607676405679417</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.4128540100119804</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-0.6086903594336665</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2.044691420363169</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-0.1162470303344236</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H41" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1.572273563374167</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1.058233007338844</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0.7035420795710873</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2.044691420363169</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.8719922593380179</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.532501625081374</v>
-      </c>
-      <c r="H42" t="n">
-        <v>4.806475834200292</v>
-      </c>
-      <c r="I42" t="n">
-        <v>-0.707258061274288</v>
-      </c>
-      <c r="J42" t="n">
-        <v>-0.1306247453122206</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="n">
-        <v>-0.1883756946268106</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV10"/>
+  <dimension ref="A1:AV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,23 +668,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.572273563374167</v>
+        <v>1.749287774900418</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5741962211938105</v>
+        <v>1.070887497482508</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4264358540163395</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1214296335740845</v>
+        <v>-0.1025937983224562</v>
       </c>
       <c r="F2" t="n">
-        <v>1.003875362653046</v>
+        <v>1.962052349425461</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9146242218507028</v>
@@ -693,16 +693,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4739900584237479</v>
+        <v>4.253984041457463</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1651869347333529</v>
+        <v>4.454456295394169</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5272045276949199</v>
+        <v>1.29300929589446</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53483257912834</v>
+        <v>2.032948611842629</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -721,27 +721,27 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-0.4678241088959745</v>
+        <v>-0.1562246800056923</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.5426897999655441</v>
+        <v>1.78925275683105</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.7215373675514996</v>
+        <v>1.314607856095266</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.005600572526204695</v>
+        <v>2.037458983018613</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-0.2116685356242426</v>
+        <v>3.234098521195671</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.7278215005846517</v>
+        <v>0.567918916911214</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.006547406204662</v>
+        <v>-0.7940956452455974</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -749,19 +749,19 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-0.002201891143915388</v>
+        <v>2.398975757898186</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.01718646097479571</v>
+        <v>-0.0711014771878576</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.1352760523980218</v>
+        <v>4.519117748820581</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02913672807600247</v>
+        <v>1.741153027974496</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.7187528302882625</v>
+        <v>1.610643241146131</v>
       </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
@@ -770,23 +770,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.572273563374167</v>
+        <v>1.749287774900418</v>
       </c>
       <c r="C3" t="n">
-        <v>1.172123418631819</v>
+        <v>-0.4349968296135067</v>
       </c>
       <c r="D3" t="n">
-        <v>1.031600189322276</v>
+        <v>0.6306402774041565</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5849141883619763</v>
+        <v>2.082363090866425</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8719922593380179</v>
+        <v>-1.438801181090714</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9146242218507028</v>
@@ -795,16 +795,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.778503172489181</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.342670026269265</v>
+        <v>-0.4264364253577941</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.770209776903699</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.450095682585971</v>
+        <v>-1.453863617157394</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -823,27 +823,27 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-0.2139949343712192</v>
+        <v>1.298940381093122</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.242517411791314</v>
+        <v>-0.5049388145898835</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.28193045903274</v>
+        <v>-0.4694478427674444</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2.430252599108575</v>
+        <v>-0.3906165801826259</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-3.184600423410339</v>
+        <v>-0.2058154030606272</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.7333410217846953</v>
+        <v>0.4745214039507792</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3702700015491096</v>
+        <v>-0.2903674870345065</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
@@ -851,19 +851,19 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-2.771604489642197</v>
+        <v>-0.7468513760301952</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.061904022276729</v>
+        <v>0.2371098200725917</v>
       </c>
       <c r="AS3" t="n">
-        <v>-3.809268019317399</v>
+        <v>-0.3677275730646657</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.350936608882302</v>
+        <v>-1.387959901505905</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.578427827594632</v>
+        <v>-0.3672914973440328</v>
       </c>
       <c r="AV3" t="n">
         <v>-0.1883756946268106</v>
@@ -872,20 +872,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>1.04557851719518</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.046101172435251</v>
+        <v>-0.3899849529328742</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1779371393289693</v>
+        <v>0.6885112822459319</v>
       </c>
       <c r="F4" t="n">
         <v>1.260288922493552</v>
@@ -897,55 +897,81 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I4" t="n">
-        <v>4.253984041457463</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J4" t="n">
-        <v>2.679586215120728</v>
+        <v>-0.2785305853350074</v>
       </c>
       <c r="K4" t="n">
-        <v>2.058814064093999</v>
+        <v>0.5272045276949199</v>
       </c>
       <c r="L4" t="n">
-        <v>2.531064644556918</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>1.036716546414051</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.9953452199653782</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.130232835378576</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.2772787054164285</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2912359590073237</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2.449741993267547</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.449699785539934</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4005818751632176</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.708024290601938</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.8455113198645524</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.288802087128868</v>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>-2.235279354180576</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.161056869616338</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6407939806281977</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.09580842897850105</v>
+        <v>-0.7329069265868214</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4337359069304182</v>
+        <v>0.10594724812918</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.444818638474652</v>
+        <v>0.4849720161454072</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.420636078005337</v>
+        <v>0.04036840652349678</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>1.292970503711792</v>
+        <v>0.4968760917273337</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.6315166655496703</v>
+        <v>1.061364957371215</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.08126065397404854</v>
+        <v>-1.109110749236878</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
@@ -953,19 +979,19 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>1.063555180623306</v>
+        <v>-0.03989293350765222</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9019473589008786</v>
+        <v>0.4424255172428448</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.632734291996711</v>
+        <v>2.996080238670935</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.034730415736267</v>
+        <v>0.7072510263894199</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.7525143192487757</v>
+        <v>0.2671326424091813</v>
       </c>
       <c r="AV4" t="n">
         <v>-0.1883756946268106</v>
@@ -974,20 +1000,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.572273563374167</v>
+        <v>1.749287774900418</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6026713621669401</v>
+        <v>-1.055066846653042</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9222474860718796</v>
+        <v>-1.155453875685647</v>
       </c>
       <c r="E5" t="n">
-        <v>1.583213456698276</v>
+        <v>1.950512244105027</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3726605901749289</v>
@@ -999,16 +1025,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2377404344841407</v>
+        <v>1.182738930242569</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.313871465494515</v>
+        <v>1.052621974870074</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5272045276949199</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L5" t="n">
-        <v>1.036716546414051</v>
+        <v>-1.951979649871683</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1027,27 +1053,27 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.3179735788861295</v>
+        <v>1.456073271819734</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.4742862876577292</v>
+        <v>-0.7771661301611035</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.58269111267378</v>
+        <v>-0.6343111528906779</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5121996489459079</v>
+        <v>-0.5522924711029472</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-0.3354470833648286</v>
+        <v>-0.4854105321251523</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.3701337175031765</v>
+        <v>-0.9846776532754178</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7404655827801735</v>
+        <v>-0.4240291047462559</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
@@ -1055,44 +1081,44 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>0.2633013078271583</v>
+        <v>-0.4843097813700841</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.634315614604176</v>
+        <v>1.583943937671755</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1349805857365448</v>
+        <v>-0.8216372180618065</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.232072716379941</v>
+        <v>-1.309787491453432</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2158632685594284</v>
+        <v>-0.5313390707264165</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.308540478011726</v>
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5647078917359482</v>
+        <v>-1.029757866365714</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5722394583502011</v>
+        <v>0.7035420795710873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6885112822459319</v>
+        <v>0.06692871894219841</v>
       </c>
       <c r="F6" t="n">
-        <v>1.786611492692483</v>
+        <v>-0.4401378427645355</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9146242218507028</v>
@@ -1101,16 +1127,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001490810544533536</v>
+        <v>0.4739900584237479</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01728109471056615</v>
+        <v>0.4609986147789265</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.004405008704159</v>
+        <v>2.058814064093999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4576315517288156</v>
+        <v>1.036716546414051</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1129,27 +1155,27 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>-0.407459004397252</v>
+        <v>-0.1575321769649781</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.2850998185532756</v>
+        <v>0.5942411378288215</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6555728538868929</v>
+        <v>-0.06372968284522738</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1902937838347055</v>
+        <v>0.01315250414955912</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.1726132449304686</v>
+        <v>0.6616078960469952</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.9993982106568903</v>
+        <v>-1.073417000882123</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.168733946552381</v>
+        <v>-0.3966389161565329</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
@@ -1157,19 +1183,19 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>0.5062253885951371</v>
+        <v>-0.2379021669256436</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.3073652210048103</v>
+        <v>-1.366062968923348</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2420962070462711</v>
+        <v>0.004474351161966465</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.5985330621135077</v>
+        <v>0.1716676037906917</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.313423714917849</v>
+        <v>0.4440040877414008</v>
       </c>
       <c r="AV6" t="n">
         <v>-0.1883756946268106</v>
@@ -1178,23 +1204,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.7007411226304503</v>
+        <v>1.032924027051516</v>
       </c>
       <c r="D7" t="n">
-        <v>1.323207397989999</v>
+        <v>-0.6815921616005972</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5849141883619763</v>
+        <v>0.6885112822459319</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9498935605813611</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9146242218507028</v>
@@ -1203,16 +1229,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001490810544533536</v>
+        <v>1.182738930242569</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2785305853350074</v>
+        <v>0.7568102948244999</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.004405008704159</v>
+        <v>1.29300929589446</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.951979649871683</v>
+        <v>2.032948611842629</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1231,27 +1257,27 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>-0.317623514347781</v>
+        <v>-0.8156932649745166</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01876990172882822</v>
+        <v>0.1989695436822857</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3806763877262273</v>
+        <v>-0.3437639681958272</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02320887026119992</v>
+        <v>-0.624050339962646</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>-0.1526384538479748</v>
+        <v>0.5078254687704862</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.7727873175204797</v>
+        <v>0.6186611989949513</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.365042266414406</v>
+        <v>-0.7757378180915593</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
@@ -1259,19 +1285,19 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>-0.05326019863835257</v>
+        <v>-0.1024123293196638</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.6441798531825026</v>
+        <v>-0.8180650336188547</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.1489565390801936</v>
+        <v>0.1751852596456193</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.129231182530129</v>
+        <v>-0.2031119904171901</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.3167213422209179</v>
+        <v>0.4169651114033013</v>
       </c>
       <c r="AV7" t="n">
         <v>-0.1883756946268106</v>
@@ -1280,23 +1306,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4223423394698427</v>
+        <v>-1.320811139669986</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.082552073518716</v>
+        <v>1.177403793656137</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06692871894219841</v>
+        <v>-0.01783253969012888</v>
       </c>
       <c r="F8" t="n">
-        <v>1.786611492692483</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9146242218507028</v>
@@ -1305,17 +1331,13 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7102396823633551</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J8" t="n">
-        <v>1.348433654915647</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.29300929589446</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.032948611842629</v>
-      </c>
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1333,27 +1355,27 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>-0.8814483756420427</v>
+        <v>0.3326479020757634</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.074221483049433</v>
+        <v>-1.657590536587118</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.598754045857112</v>
+        <v>-1.848886950749103</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.624949535613936</v>
+        <v>-0.6198089881563845</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>2.521406045030111</v>
+        <v>-0.8637008192638077</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.01396870627988998</v>
+        <v>-0.2526951067366487</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.8661753701620944</v>
+        <v>0.8450481831500924</v>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
@@ -1361,19 +1383,19 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>1.506653040748488</v>
+        <v>-0.8564803159651293</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.842483241753157</v>
+        <v>-0.1801793628823292</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.906031649049988</v>
+        <v>-1.351609774691356</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.111821690833059</v>
+        <v>-1.848926020851917</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.72228233729058</v>
+        <v>-1.754180136157805</v>
       </c>
       <c r="AV8" t="n">
         <v>-0.1883756946268106</v>
@@ -1382,23 +1404,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C9" t="n">
-        <v>0.678598303028924</v>
+        <v>-0.5362327507628185</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.337708381102974</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4604746681033937</v>
+        <v>-1.279833501549224</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9934513139993099</v>
+        <v>1.962052349425461</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9146242218507028</v>
@@ -1407,16 +1429,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2347588133950737</v>
+        <v>-1.179757309153502</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1651869347333529</v>
+        <v>-2.792929865722383</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5272045276949199</v>
+        <v>-2.536014545103239</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5386005136997623</v>
+        <v>-1.453863617157394</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1435,27 +1457,27 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>-0.2543643934588306</v>
+        <v>-0.1038173863100494</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.494418826078481</v>
+        <v>-1.74569968200273</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.337249760989129</v>
+        <v>-2.405713377709071</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.9524592513175321</v>
+        <v>-2.108046752694408</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.6834065946764667</v>
+        <v>-2.433560032997935</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.2240231284673604</v>
+        <v>-0.6852471725812138</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.3952565032218492</v>
+        <v>0.221926074228314</v>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1463,19 +1485,19 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>1.261774876607267</v>
+        <v>-2.024305375761708</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.7012280456811396</v>
+        <v>0.38139690798625</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.7593291777279051</v>
+        <v>-3.303017184498212</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.686532647881219</v>
+        <v>-2.089786757717471</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.565651409109486</v>
+        <v>-1.680306488906272</v>
       </c>
       <c r="AV9" t="n">
         <v>-0.1883756946268106</v>
@@ -1484,23 +1506,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.156302767802354</v>
+        <v>1.286013829924795</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.374159282186439</v>
+        <v>-0.6086903594336665</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5829075972389774</v>
+        <v>2.082363090866425</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7609572533304625</v>
+        <v>1.962052349425461</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9146242218507028</v>
@@ -1509,16 +1531,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.597255052791145</v>
+        <v>1.418988554182177</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.792929865722383</v>
+        <v>0.7568102948244999</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.536014545103239</v>
+        <v>0.5272045276949199</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.453863617157394</v>
+        <v>0.5386005136997623</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1537,27 +1559,27 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.0578590090147615</v>
+        <v>0.4813453497817327</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.505827576245416</v>
+        <v>1.233563910736295</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.396759502358214</v>
+        <v>1.769828942726446</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.958284167247056</v>
+        <v>1.190846451546119</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>-2.655387892614179</v>
+        <v>0.6049325787716631</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1589026079707665</v>
+        <v>-0.0999360993637351</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.7866493765860476</v>
+        <v>-0.5769279934987692</v>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
@@ -1565,21 +1587,943 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
-        <v>-1.10392670396833</v>
+        <v>1.101565253980276</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.2426795390814543</v>
+        <v>0.6160497225838937</v>
       </c>
       <c r="AS10" t="n">
-        <v>-4.715257960423127</v>
+        <v>0.7367083634703329</v>
       </c>
       <c r="AT10" t="n">
-        <v>-1.396315094659601</v>
+        <v>1.238189188397167</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.5460173139031</v>
+        <v>1.420188886959019</v>
       </c>
       <c r="AV10" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.749287774900418</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.5741962211938105</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4264358540163395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.618878536078533</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.222873972803972</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4739900584237479</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.53483257912834</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>-0.5467810932456048</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.5229049809445721</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.6461059669597367</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.005600572526204695</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>-0.2050163396483246</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.7521606805325548</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.885297314907718</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-0.002201891143915388</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.0121028407391161</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.1183076087917558</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.0532720532475169</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.7166810200645597</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.749287774900418</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.172123418631819</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.031600189322276</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5849141883619763</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.962052349425461</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-3.778503172489181</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-6.342670026269265</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.770209776903699</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-2.450095682585971</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>-0.1552423496364267</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.248944587444395</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.261427876623892</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-2.536805852796431</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>-3.038017718289495</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.8176822671168309</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.4172981220591114</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-2.649842583007843</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.9454729673229934</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-4.057754557840714</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-1.336432163444458</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1.53083375645873</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.04557851719518</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.046101172435251</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.082363090866425</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.260288922493552</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.253984041457463</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.679586215120728</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.058814064093999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.531064644556918</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>-1.153928679318295</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.3044132601771926</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.4927238255178888</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.522633666618142</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.471511316730633</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>1.375400460802489</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.7159517582147182</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.04322823072322397</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>1.11518080264546</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.7094342671746996</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.73231571939543</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.9884831027554775</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.76460350237262</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6026713621669401</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9222474860718796</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9993025638977986</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.5885877984616701</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2377404344841407</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.313871465494515</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.036716546414051</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>1.802060807442758</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.3123625599166595</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.5056121377535405</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.5630165304821283</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.4863956228898947</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>-0.3340544339499588</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.4056986205708091</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.6340759461479435</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>0.3164624611709969</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.636057674166943</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.1041775077170895</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.2104306435487572</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0.2087699990990375</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5.308540478011726</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.572273563374167</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5647078917359482</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.5722394583502011</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.082363090866425</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.786611492692483</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="n">
+        <v>-0.3736190689015811</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2878050619653528</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.721927148309484</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.03776097268981374</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>0.1567871284276966</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.149678533778468</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.1945526409625787</v>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>0.439015366346851</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.3909171048421222</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.2600775012849931</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.6304480667536131</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.2737596913520125</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.678598303028924</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.337708381102974</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.082363090866425</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.9934513139993099</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5386005136997623</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>-0.2128823948737711</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.487848824299769</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.359467191728355</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.9924872449248229</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>0.699874177018694</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.2019743987524133</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.3671294229398835</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>1.294603477277764</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.7477158674410478</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.7734184018685237</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.681868662638923</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.584494851678343</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.749287774900418</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.7007411226304503</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.323207397989999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1214296335740845</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8284345059200692</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.951979649871683</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>-0.3429200465246514</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.03627834435711591</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.3768619082069526</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.05242992038200701</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>-0.1616503752989727</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.7747883152514747</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.3071470700163367</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>-0.07663355718025176</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0.6791345497351032</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.1304415824751814</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.1433637886193465</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0.3369884193274686</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.4223423394698427</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.082552073518716</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.552953112697834</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.962052349425461</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7102396823633551</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.348433654915647</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.29300929589446</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.032948611842629</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>-0.8319289427456884</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.11432981962963</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.622281618782475</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.611315175700067</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>2.511049453197314</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.1105774492731499</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.7464100887362761</v>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>1.541555713668811</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-1.789038696772341</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.97949292577358</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.050561182602982</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.754921801983263</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.156302767802354</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.374159282186439</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.347765516052922</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.5885877984616701</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2.597255052791145</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2.792929865722383</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2.536014545103239</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.453863617157394</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>0.07019030940054685</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.461684461627323</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-1.519929978636471</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-1.121793401225435</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>-2.52288326750676</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.1591228435700929</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.7748929130478045</v>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>-1.026160563366736</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.2690640050988491</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-5.160616925810523</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-1.450122059313527</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-1.513684500724622</v>
+      </c>
+      <c r="AV19" t="n">
         <v>-0.1883756946268106</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV10"/>
+  <dimension ref="A1:AV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,23 +668,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.572273563374167</v>
+        <v>1.784690617205668</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.5741962211938105</v>
+        <v>1.070887497482508</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4264358540163395</v>
+        <v>0.6670911784876219</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1214296335740845</v>
+        <v>-0.1025937983224562</v>
       </c>
       <c r="F2" t="n">
-        <v>1.003875362653046</v>
+        <v>1.962052349425461</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9146242218507028</v>
@@ -693,16 +693,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4739900584237479</v>
+        <v>4.253984041457463</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1651869347333529</v>
+        <v>4.454456295394169</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5272045276949199</v>
+        <v>1.29300929589446</v>
       </c>
       <c r="L2" t="n">
-        <v>1.53483257912834</v>
+        <v>2.032948611842629</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -721,27 +721,27 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-0.4678241088959745</v>
+        <v>-0.1562246800056908</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.5426897999655441</v>
+        <v>1.78925275683105</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.7215373675514996</v>
+        <v>1.314607856095266</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.005600572526204695</v>
+        <v>2.037458983018612</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-0.2116685356242426</v>
+        <v>3.234098521195671</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.7278215005846517</v>
+        <v>0.567918916911214</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.006547406204662</v>
+        <v>-0.7940956452455974</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
@@ -749,19 +749,19 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-0.002201891143915388</v>
+        <v>2.398975757898186</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.01718646097479571</v>
+        <v>-0.0711014771878576</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.1352760523980218</v>
+        <v>4.519117748820581</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02913672807600247</v>
+        <v>1.741153027974496</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.7187528302882625</v>
+        <v>1.610643241146131</v>
       </c>
       <c r="AV2" t="n">
         <v>-0.1883756946268106</v>
@@ -770,23 +770,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.572273563374167</v>
+        <v>1.784690617205668</v>
       </c>
       <c r="C3" t="n">
-        <v>1.172123418631819</v>
+        <v>-0.4349968296135067</v>
       </c>
       <c r="D3" t="n">
-        <v>1.031600189322276</v>
+        <v>0.6306402774041565</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5849141883619763</v>
+        <v>2.101198926118053</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8719922593380179</v>
+        <v>-1.438801181090714</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9146242218507028</v>
@@ -795,16 +795,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.778503172489181</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.342670026269265</v>
+        <v>-0.4264364253577941</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.770209776903699</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.450095682585971</v>
+        <v>-1.453863617157394</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -823,27 +823,27 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-0.2139949343712192</v>
+        <v>1.298940381093121</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.242517411791314</v>
+        <v>-0.5049388145898835</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.28193045903274</v>
+        <v>-0.4694478427674444</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2.430252599108575</v>
+        <v>-0.3906165801826259</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-3.184600423410339</v>
+        <v>-0.2058154030606272</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.7333410217846953</v>
+        <v>0.4745214039507792</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3702700015491096</v>
+        <v>-0.2903674870345065</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
@@ -851,19 +851,19 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-2.771604489642197</v>
+        <v>-0.7468513760301952</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.061904022276729</v>
+        <v>0.2371098200725917</v>
       </c>
       <c r="AS3" t="n">
-        <v>-3.809268019317399</v>
+        <v>-0.3677275730646657</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.350936608882302</v>
+        <v>-1.387959901505905</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.578427827594632</v>
+        <v>-0.3672914973440328</v>
       </c>
       <c r="AV3" t="n">
         <v>-0.1883756946268106</v>
@@ -872,20 +872,20 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C4" t="n">
-        <v>1.04557851719518</v>
+        <v>-1.358774610100978</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.046101172435251</v>
+        <v>-0.3899849529328742</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1779371393289693</v>
+        <v>0.6885112822459319</v>
       </c>
       <c r="F4" t="n">
         <v>1.260288922493552</v>
@@ -897,55 +897,81 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I4" t="n">
-        <v>4.253984041457463</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J4" t="n">
-        <v>2.679586215120728</v>
+        <v>-0.2785305853350074</v>
       </c>
       <c r="K4" t="n">
-        <v>2.058814064093999</v>
+        <v>0.5272045276949199</v>
       </c>
       <c r="L4" t="n">
-        <v>2.531064644556918</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>1.036716546414051</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.9953452199653782</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.130232835378576</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.2772787054164285</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2912359590073237</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-2.449741993267547</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.449699785539934</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4005818751632176</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.708024290601938</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.8455113198645524</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.288802087128868</v>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>-2.235279354180576</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.161056869616338</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6407939806281977</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0.09580842897850105</v>
+        <v>-0.7329069265868214</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4337359069304182</v>
+        <v>0.10594724812918</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.444818638474652</v>
+        <v>0.4849720161454072</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.420636078005337</v>
+        <v>0.04036840652349678</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>1.292970503711792</v>
+        <v>0.4968760917273337</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.6315166655496703</v>
+        <v>1.061364957371215</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.08126065397404854</v>
+        <v>-1.109110749236878</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
@@ -953,19 +979,19 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>1.063555180623306</v>
+        <v>-0.03989293350765222</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9019473589008786</v>
+        <v>0.4424255172428448</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.632734291996711</v>
+        <v>2.996080238670935</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.034730415736267</v>
+        <v>0.7072510263894199</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.7525143192487757</v>
+        <v>0.2671326424091813</v>
       </c>
       <c r="AV4" t="n">
         <v>-0.1883756946268106</v>
@@ -974,23 +1000,23 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1.572273563374167</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6026713621669401</v>
+        <v>-1.029757866365714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9222474860718796</v>
+        <v>0.7035420795710873</v>
       </c>
       <c r="E5" t="n">
-        <v>1.583213456698276</v>
+        <v>-0.03666837494175717</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3726605901749289</v>
+        <v>-0.4401378427645355</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9146242218507028</v>
@@ -999,13 +1025,13 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2377404344841407</v>
+        <v>0.4739900584237479</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.313871465494515</v>
+        <v>0.4609986147789265</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5272045276949199</v>
+        <v>2.058814064093999</v>
       </c>
       <c r="L5" t="n">
         <v>1.036716546414051</v>
@@ -1027,27 +1053,27 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>0.3179735788861295</v>
+        <v>-0.2674270388328317</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.4742862876577292</v>
+        <v>0.6070278653367334</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.58269111267378</v>
+        <v>-0.08570487379799087</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5121996489459079</v>
+        <v>-0.002957471962253925</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>-0.3354470833648286</v>
+        <v>0.656509488065489</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.3701337175031765</v>
+        <v>-1.041759167238547</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7404655827801735</v>
+        <v>-0.3624944240259279</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
@@ -1055,44 +1081,44 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>0.2633013078271583</v>
+        <v>-0.2385678159714966</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.634315614604176</v>
+        <v>-1.381169748490702</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1349805857365448</v>
+        <v>0.01414922167302514</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.232072716379941</v>
+        <v>0.2165355401588873</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2158632685594284</v>
+        <v>0.4442258450579788</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.308540478011726</v>
+        <v>-0.1883756946268106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.572273563374167</v>
+        <v>1.749287774900418</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5647078917359482</v>
+        <v>-1.320811139669986</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5722394583502011</v>
+        <v>1.177403793656137</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6885112822459319</v>
+        <v>-0.01783253969012888</v>
       </c>
       <c r="F6" t="n">
-        <v>1.786611492692483</v>
+        <v>0.5990118471154066</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9146242218507028</v>
@@ -1101,17 +1127,13 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001490810544533536</v>
+        <v>-0.707258061274288</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01728109471056615</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-1.004405008704159</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-0.4576315517288156</v>
-      </c>
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1129,27 +1151,27 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>-0.407459004397252</v>
+        <v>0.3937832009345116</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.2850998185532756</v>
+        <v>-1.676264032325856</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6555728538868929</v>
+        <v>-1.81682301431724</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.1902937838347055</v>
+        <v>-0.6053288847407879</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>0.1726132449304686</v>
+        <v>-0.8775328944890269</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.9993982106568903</v>
+        <v>-0.2275871697089698</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.168733946552381</v>
+        <v>0.7834381878348016</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
@@ -1157,19 +1179,19 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>0.5062253885951371</v>
+        <v>-0.869603111440525</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.3073652210048103</v>
+        <v>-0.1264525821622905</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2420962070462711</v>
+        <v>-1.326215228736959</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.5985330621135077</v>
+        <v>-1.863761249518931</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.313423714917849</v>
+        <v>-1.759228376246889</v>
       </c>
       <c r="AV6" t="n">
         <v>-0.1883756946268106</v>
@@ -1178,23 +1200,23 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.572273563374167</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.7007411226304503</v>
+        <v>-0.5362327507628185</v>
       </c>
       <c r="D7" t="n">
-        <v>1.323207397989999</v>
+        <v>0.9586983871553449</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5849141883619763</v>
+        <v>1.489034280440134</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9498935605813611</v>
+        <v>1.962052349425461</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9146242218507028</v>
@@ -1203,16 +1225,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001490810544533536</v>
+        <v>-1.179757309153502</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2785305853350074</v>
+        <v>-2.792929865722383</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.004405008704159</v>
+        <v>-2.536014545103239</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.951979649871683</v>
+        <v>-1.453863617157394</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1231,27 +1253,27 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
-        <v>-0.317623514347781</v>
+        <v>-0.08116763723644635</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01876990172882822</v>
+        <v>-1.732268196556282</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3806763877262273</v>
+        <v>-2.353712424660719</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02320887026119992</v>
+        <v>-2.096077179662724</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
-        <v>-0.1526384538479748</v>
+        <v>-2.430623373955854</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.7727873175204797</v>
+        <v>-0.6565104720133689</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.365042266414406</v>
+        <v>0.1866447197967289</v>
       </c>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
@@ -1259,19 +1281,19 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>-0.05326019863835257</v>
+        <v>-2.022749313057115</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.6441798531825026</v>
+        <v>0.3580472468293134</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.1489565390801936</v>
+        <v>-3.292318188797271</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.129231182530129</v>
+        <v>-2.056154387674827</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.3167213422209179</v>
+        <v>-1.679239207703504</v>
       </c>
       <c r="AV7" t="n">
         <v>-0.1883756946268106</v>
@@ -1280,23 +1302,23 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.607676405679417</v>
+        <v>1.678482090289918</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4223423394698427</v>
+        <v>1.032924027051516</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.082552073518716</v>
+        <v>-0.6815921616005972</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06692871894219841</v>
+        <v>0.6885112822459319</v>
       </c>
       <c r="F8" t="n">
-        <v>1.786611492692483</v>
+        <v>1.624666086477427</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9146242218507028</v>
@@ -1305,10 +1327,10 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7102396823633551</v>
+        <v>1.182738930242569</v>
       </c>
       <c r="J8" t="n">
-        <v>1.348433654915647</v>
+        <v>0.7568102948244999</v>
       </c>
       <c r="K8" t="n">
         <v>1.29300929589446</v>
@@ -1333,27 +1355,27 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>-0.8814483756420427</v>
+        <v>-0.815693264974518</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.074221483049433</v>
+        <v>0.1989695436822857</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.598754045857112</v>
+        <v>-0.3437639681958235</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.624949535613936</v>
+        <v>-0.6240503399626455</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="n">
-        <v>2.521406045030111</v>
+        <v>0.5078254687704862</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.01396870627988998</v>
+        <v>0.6186611989949513</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.8661753701620944</v>
+        <v>-0.7757378180915497</v>
       </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
@@ -1361,19 +1383,19 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>1.506653040748488</v>
+        <v>-0.1024123293196638</v>
       </c>
       <c r="AR8" t="n">
-        <v>-1.842483241753157</v>
+        <v>-0.8180650336188547</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.906031649049988</v>
+        <v>0.1751852596456191</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.111821690833059</v>
+        <v>-0.2031119904171901</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.72228233729058</v>
+        <v>0.4169651114033013</v>
       </c>
       <c r="AV8" t="n">
         <v>-0.1883756946268106</v>
@@ -1382,23 +1404,23 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.607676405679417</v>
+        <v>1.784690617205668</v>
       </c>
       <c r="C9" t="n">
-        <v>0.678598303028924</v>
+        <v>-1.055066846653042</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.337708381102974</v>
+        <v>-1.155453875685647</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4604746681033937</v>
+        <v>1.950512244105027</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9934513139993099</v>
+        <v>-0.3726605901749289</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9146242218507028</v>
@@ -1407,16 +1429,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2347588133950737</v>
+        <v>1.182738930242569</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1651869347333529</v>
+        <v>1.052621974870074</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5272045276949199</v>
+        <v>-1.004405008704159</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5386005136997623</v>
+        <v>-1.951979649871683</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1435,27 +1457,27 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>-0.2543643934588306</v>
+        <v>1.456073271819734</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.494418826078481</v>
+        <v>-0.7771661301611035</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.337249760989129</v>
+        <v>-0.6343111528906779</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.9524592513175321</v>
+        <v>-0.5522924711029472</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="n">
-        <v>0.6834065946764667</v>
+        <v>-0.4854105321251523</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.2240231284673604</v>
+        <v>-0.9846776532754178</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0.3952565032218492</v>
+        <v>-0.4240291047462654</v>
       </c>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
@@ -1463,19 +1485,19 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>1.261774876607267</v>
+        <v>-0.4843097813700841</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.7012280456811396</v>
+        <v>1.583943937671755</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.7593291777279051</v>
+        <v>-0.8216372180618065</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.686532647881219</v>
+        <v>-1.309787491453432</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.565651409109486</v>
+        <v>-0.5313390707264165</v>
       </c>
       <c r="AV9" t="n">
         <v>-0.1883756946268106</v>
@@ -1484,23 +1506,23 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.607676405679417</v>
+        <v>1.572273563374167</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.156302767802354</v>
+        <v>1.286013829924795</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.374159282186439</v>
+        <v>-0.6086903594336665</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5829075972389774</v>
+        <v>2.101198926118053</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7609572533304625</v>
+        <v>1.962052349425461</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9146242218507028</v>
@@ -1509,16 +1531,16 @@
         <v>-0.2080526428291888</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.597255052791145</v>
+        <v>1.418988554182177</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.792929865722383</v>
+        <v>0.7568102948244999</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.536014545103239</v>
+        <v>0.5272045276949199</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.453863617157394</v>
+        <v>0.5386005136997623</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1537,27 +1559,27 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0.0578590090147615</v>
+        <v>0.4813453497817327</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1.505827576245416</v>
+        <v>1.233563910736295</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.396759502358214</v>
+        <v>1.769828942726446</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.958284167247056</v>
+        <v>1.190846451546119</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
-        <v>-2.655387892614179</v>
+        <v>0.6049325787716631</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1589026079707665</v>
+        <v>-0.09993609936376059</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.7866493765860476</v>
+        <v>-0.5769279934987692</v>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
@@ -1565,21 +1587,943 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
-        <v>-1.10392670396833</v>
+        <v>1.101565253980276</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.2426795390814543</v>
+        <v>0.6160497225838937</v>
       </c>
       <c r="AS10" t="n">
-        <v>-4.715257960423127</v>
+        <v>0.7367083634703329</v>
       </c>
       <c r="AT10" t="n">
-        <v>-1.396315094659601</v>
+        <v>1.238189188397167</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.5460173139031</v>
+        <v>1.420188886959019</v>
       </c>
       <c r="AV10" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.784690617205668</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.5741962211938105</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4264358540163395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.618878536078533</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.222873972803972</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4739900584237479</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.53483257912834</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>-0.5467810932456048</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.5229049809445721</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.6461059669597367</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.005600572526204695</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>-0.2050163396483246</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.752160680532542</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.885297314907718</v>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-0.002201891143915388</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.0121028407391161</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.1183076087917558</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.0532720532475169</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.7166810200645597</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.784690617205668</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.172123418631819</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.031600189322276</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.101198926118053</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.962052349425461</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-3.778503172489181</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-6.342670026269265</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.770209776903699</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-2.450095682585971</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="n">
+        <v>-0.2163776484951764</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-1.230271091705657</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-1.293491813055756</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-2.551285956212028</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>-3.024185643064276</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.792574330089152</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.4789081173744022</v>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-2.636719787532447</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.999199748043032</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-4.083149103795112</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-1.321596934777444</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-1.525785516369646</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.607676405679417</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.04557851719518</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.046101172435251</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.101198926118053</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1131756284702389</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.253984041457463</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.679586215120728</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.058814064093999</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.531064644556918</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>-1.098788567237595</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.4143081220450461</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.479937098009977</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.544608857570905</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.487621292842446</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>1.380498868783995</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.6842939245711425</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.009083738592619045</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>1.115846451691313</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.7245410467420534</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.722640848884371</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.9436151663872818</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.764381745056042</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.678598303028924</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.337708381102974</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.101198926118053</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.9934513139993099</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2347588133950737</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1651869347333529</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5386005136997623</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="n">
+        <v>-0.2128823948737711</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.487848824299769</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.359467191728355</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.9924872449248229</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="n">
+        <v>0.699874177018694</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.2019743987524133</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.3671294229398835</v>
+      </c>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>1.294603477277764</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.7477158674410478</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.7734184018685235</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.681868662638923</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.584494851678343</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6026713621669401</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9222474860718796</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9993025638977986</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.5885877984616701</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2377404344841407</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.313871465494515</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5272045276949199</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.036716546414051</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>1.802060807442758</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.312362559916661</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.5056121377535405</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.5630165304821283</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.4863956228898942</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>-0.3340544339499588</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.4056986205708091</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.6340759461479341</v>
+      </c>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>0.3164624611709969</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.636057674166943</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.1041775077170896</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.2104306435487572</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.2087699990990375</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5.308540478011726</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.784690617205668</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.7007411226304503</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.323207397989999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.1214296335740845</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8284345059200692</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.2785305853350074</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.951979649871683</v>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="n">
+        <v>-0.3429200465246514</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.03627834435711591</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.3768619082069563</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.05242992038200758</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>-0.1616503752989727</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.774788315251462</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.3071470700163367</v>
+      </c>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>-0.07663355718025176</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.6791345497351032</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.1304415824751814</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.1433637886193465</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.3369884193274686</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.4223423394698427</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.082552073518716</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.552953112697834</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.962052349425461</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7102396823633551</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.348433654915647</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.29300929589446</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.032948611842629</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="n">
+        <v>-0.8319289427456884</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.11432981962963</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.622281618782475</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.611315175700067</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>2.511049453197314</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.1105774492731499</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.7464100887362761</v>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>1.541555713668811</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-1.789038696772341</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.97949292577358</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.050561182602982</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.754921801983263</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.607676405679417</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5647078917359482</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5722394583502011</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.101198926118053</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.236369423321894</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.001490810544533536</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.01728109471056615</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.004405008704159</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.4576315517288156</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>-0.3962688179751827</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.2743735765189046</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.669926195261133</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.04973054572149711</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>0.1538504693856158</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.120941833210623</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.1592712865309937</v>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>0.4374593036422589</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.3675674436851857</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.2493785055840518</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.5968156967109696</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.2726924101492443</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.1883756946268106</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.678482090289918</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.156302767802354</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.374159282186439</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.347765516052922</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.5885877984616701</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9146242218507028</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2080526428291888</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-2.597255052791145</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2.792929865722383</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2.536014545103239</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.453863617157394</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="n">
+        <v>0.07019030940054685</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.461684461627323</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-1.519929978636471</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-1.121793401225435</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>-2.52288326750676</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.1591228435700929</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.7748929130478139</v>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>-1.026160563366736</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.2690640050988491</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>-5.160616925810523</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-1.450122059313527</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-1.513684500724622</v>
+      </c>
+      <c r="AV19" t="n">
         <v>-0.1883756946268106</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ7"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,165 +441,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35_segun_loc</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>h2h_3</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3_segun_loc</t>
+          <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points</t>
+          <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_sum_val_player_miss</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
@@ -608,671 +538,571 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.586525478891599</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C2" t="n">
-        <v>1.063407388277644</v>
+        <v>1.081903776399266</v>
       </c>
       <c r="D2" t="n">
-        <v>2.144705951685369</v>
+        <v>0.6686343909026068</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1384166366940627</v>
+        <v>-0.121788644330891</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2420721743261735</v>
+        <v>-0.6205523013167357</v>
       </c>
       <c r="G2" t="n">
-        <v>4.116938145318066</v>
+        <v>-0.3103265160783306</v>
       </c>
       <c r="H2" t="n">
-        <v>2.569784038132072</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.055094026036159</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.499366889792507</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.730205332102995</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-0.6992601315218938</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.805553877311657</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1.528982814878413</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.550064771749718</v>
-      </c>
+        <v>1.728143232208024</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-1.550044894375292</v>
+        <v>-0.2078679648564952</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2015388132652178</v>
+        <v>0.5326857889052377</v>
       </c>
       <c r="R2" t="n">
-        <v>1.654469009249619</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.256215447288921</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.446425964683562</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.8945313526322429</v>
-      </c>
+        <v>-0.759921821787492</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1426009292449432</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.2137005645314</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.4888428331252617</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.599941088510377</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.580120245223329</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.25119389066498</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.6798672072916325</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.04015701220540818</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.6687603448250262</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.4505091354201304</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.097314062461461</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.7294414065941354</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.470578714236133</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.9603608896931971</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.7916601985810195</v>
+        <v>1.307530737968684</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.621697193950348</v>
+        <v>1.762176681478981</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.7058307910279186</v>
+        <v>-0.4268916392166902</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09718048099852507</v>
+        <v>0.6318919225277279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8583872015130566</v>
+        <v>2.127697067495167</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2420721743261735</v>
+        <v>-1.283043417957283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01421891662351881</v>
+        <v>-0.3103265160783306</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2632374046752233</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-0.969412801665261</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-1.922146097955435</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7520466431583639</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.1872509827280312</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.1221829482311655</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.2804415981615715</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-0.9368918200430224</v>
-      </c>
+        <v>-1.226640650748756</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>0.9368613210289978</v>
+        <v>1.297372158492442</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.653706947473047</v>
+        <v>0.4726742901672594</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2038017571839124</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.8932833398303881</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1.092742347518978</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.7598605836025211</v>
-      </c>
+        <v>-0.2856067832458896</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3524408871432577</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1499665536954876</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.04002267311976893</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.3834274699542006</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.06332152804195171</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.1457111992199747</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.7669091821013292</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.9393023808784573</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>-0.3879246955258789</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.07134205670908073</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.6729184645368991</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.1154403762891302</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.1537985890544174</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-0.3404048547069909</v>
+        <v>-0.2801560315530942</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.832727484302845</v>
+        <v>1.762176681478981</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.423778327660365</v>
+        <v>-1.352455213502108</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.541107335947474</v>
+        <v>-0.3968971919688834</v>
       </c>
       <c r="E4" t="n">
-        <v>1.999472624999764</v>
+        <v>-0.4101842484111548</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2420721743261735</v>
+        <v>1.988006470455419</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6980054547392767</v>
+        <v>-0.3103265160783306</v>
       </c>
       <c r="H4" t="n">
-        <v>1.294924388868789</v>
+        <v>0.8839192656489443</v>
       </c>
       <c r="I4" t="n">
-        <v>1.298967319110804</v>
+        <v>0.2938567128847251</v>
       </c>
       <c r="J4" t="n">
-        <v>2.008087668931624</v>
+        <v>-2.225917709408243</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2410223151810009</v>
+        <v>0.3859749293291037</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.132665565155191</v>
+        <v>2.95008242183073</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2462208061634122</v>
+        <v>-0.8015790771651877</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5836587507928045</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-1.806315669206339</v>
-      </c>
+        <v>1.225733055340246</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.806267558934563</v>
+        <v>-0.7394079049695005</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.461682746074422</v>
+        <v>0.9885172110219901</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.8928235020412898</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.045201092948131</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.457300764191704</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.434385563403587</v>
-      </c>
+        <v>-1.107153569199315</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>1.399094075204022</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.3733979603070443</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.142249639120815</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.6801159811915</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.710847565942918</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.275265893941473</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.1109894374081458</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.5065662470072488</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.2232309616266477</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.9740830355414649</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.514518317707942</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-1.781782250808666</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.703388102067259</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.076036476547077</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.809806339262886</v>
+        <v>0.2431770524406804</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.832727484302845</v>
+        <v>1.623270151678116</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5762258606427793</v>
+        <v>-1.048160339764437</v>
       </c>
       <c r="D5" t="n">
-        <v>2.144705951685369</v>
+        <v>-1.168489027841342</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.220018391266303</v>
+        <v>1.262510255254375</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2420721743261735</v>
+        <v>0.7596375250177376</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01421891662351881</v>
+        <v>-0.3103265160783306</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02006473960550622</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.969412801665261</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-0.4483084353727878</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-2.627307783788713</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.452779385811173</v>
-      </c>
-      <c r="M5" t="n">
-        <v>-2.978763500075003</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.286819021029404</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.6942619086486087</v>
-      </c>
+        <v>-1.648752634028296</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>0.6942363244041891</v>
+        <v>1.324191875795249</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.456202866322695</v>
+        <v>-0.8979453430857665</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.143376863807608</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.725892292235259</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-2.982979968808971</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.110838598251922</v>
-      </c>
+        <v>-0.3957561223554982</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4059195171901562</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.9245287632822188</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.2808878410344149</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.6970816113030867</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.04464795038850679</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.140074847424933</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.11283244218766</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.3115223851810246</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1.336121879567678</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.04285093295540181</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.4324800310009241</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.3616434036999043</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.2288265778970179</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.6108264985089938</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.286267614758868</v>
+        <v>-0.456994967757046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.692040624067847</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6916109592931421</v>
+        <v>-0.5283232637959141</v>
       </c>
       <c r="D6" t="n">
-        <v>2.144705951685369</v>
+        <v>0.9625741379016386</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9755000862334373</v>
+        <v>-1.45802160990278</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2420721743261735</v>
+        <v>0.09714640837719042</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2137099294150671</v>
+        <v>-0.3103265160783306</v>
       </c>
       <c r="H6" t="n">
-        <v>0.161715811745871</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.5428406121854487</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5342500063489772</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.1546094226079252</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.6797571573113228</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-1.738384920752535</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.057281134035044</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.1887829265769138</v>
-      </c>
+        <v>-1.226640650748756</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.1887675814358379</v>
+        <v>-0.03250891075221508</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.62044314949393</v>
+        <v>-0.6155101675760588</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44567454111102</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.198913514930569</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.280109134525907</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.4591650536230942</v>
-      </c>
+        <v>0.1654910366005701</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>2.008750457738692</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-1.030209594047599</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.508480332758037</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.408835313999561</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.056832060020017</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.6346724353802176</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-0.1989263588662984</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.477545472185626</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.573289762711088</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.6862565331209288</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.272499801628709</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.7525945045396232</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.7038136168599101</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.704436382636641</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.634629635900263</v>
+        <v>-1.370823558187982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.586525478891599</v>
+        <v>1.692723416578548</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6146875601929002</v>
+        <v>-1.3144183542849</v>
       </c>
       <c r="D7" t="n">
-        <v>1.033262254125981</v>
+        <v>1.183028948150912</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5679695778453275</v>
+        <v>-0.4870897428325585</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2420721743261735</v>
+        <v>0.5940147458576008</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2421477626621047</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.254794909657777</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5428406121854487</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.02552922720986</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.8964189309621616</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.1872509827280314</v>
-      </c>
-      <c r="M7" t="n">
-        <v>-1.295392570994512</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.503188711433916</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-1.47269954103902</v>
-      </c>
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1.472658188575451</v>
+        <v>0.398658308801131</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.141031725908057</v>
+        <v>-0.2063380235052531</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5269788813011842</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3595596523913682</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-1.173177990978127</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.4551041742961169</v>
-      </c>
+        <v>0.7207726535183028</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5526037596045109</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.719715410402316</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.5081720167942231</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.5867279845421685</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.5219632349916095</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.3018777362593884</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.4009323774647734</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.3244902077305764</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.381416058428295</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.1815960287354669</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.3139005166255312</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.640103630385361</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.09721714792749826</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.2213943449772011</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-0.2086130217498565</v>
+        <v>-1.413351375184906</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.553816886777683</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.043866917182056</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.6908369389679152</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.146923441100518</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8286470163344613</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.728143232208024</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>-0.8082936343375829</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5937796593638854</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.7114586088070329</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3292855745945031</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.623270151678116</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.022802433619631</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7053768592774857</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.146923441100518</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.034609249217078</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8839192656489443</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>-0.3470387053721214</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.9589761123124237</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.3623551914718397</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.3690291756211415</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.519090254327467</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.297445978630116</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.6173520022181572</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.647037727361394</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.988006470455419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4618072823694042</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0.4374077842045511</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.04846616470601493</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.6065676042132055</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>1.151578125668891</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.727450049028765</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.5663601230131231</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4336396603437624</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.66951171956164</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.269241519693938</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.306031248928484</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>-0.5617101627100337</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.7045200230732235</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.8809730903795808</v>
+      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>-0.003995095342279618</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.3014139890931187</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.5721993865741554</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.519090254327467</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.183335400978489</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.036059074651396</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.127697067495167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.988006470455419</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.070864617307837</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>-0.2287750814902195</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.7534326061140151</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4717666174299594</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.0004662700274582115</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.21859965207908</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.293994384654854</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.224303173524103</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
         <v>0.6686343909026068</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.121788644330891</v>
+        <v>0.5799739922644176</v>
       </c>
       <c r="F2" t="n">
         <v>-0.6205523013167357</v>
@@ -570,19 +570,19 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-0.2078679648564952</v>
+        <v>-0.1154423519880312</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5326857889052377</v>
+        <v>0.5215413689659228</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.759921821787492</v>
+        <v>-0.7242905259271538</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.307530737968684</v>
+        <v>1.321454953904791</v>
       </c>
     </row>
     <row r="3">
@@ -601,7 +601,7 @@
         <v>0.6318919225277279</v>
       </c>
       <c r="E3" t="n">
-        <v>2.127697067495167</v>
+        <v>2.156536627903193</v>
       </c>
       <c r="F3" t="n">
         <v>-1.283043417957283</v>
@@ -620,19 +620,19 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.297372158492442</v>
+        <v>1.258416742344588</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4726742901672594</v>
+        <v>0.5050452221852312</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2856067832458896</v>
+        <v>-0.2456896939542993</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2801560315530942</v>
+        <v>-0.2894702030238677</v>
       </c>
     </row>
     <row r="4">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.692723416578548</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C7" t="n">
         <v>-1.3144183542849</v>
@@ -816,7 +816,7 @@
         <v>-0.4870897428325585</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5940147458576008</v>
+        <v>1.988006470455419</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3103265160783306</v>
@@ -830,19 +830,19 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.398658308801131</v>
+        <v>0.3387096095963538</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2063380235052531</v>
+        <v>-0.1455483752215773</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7207726535183028</v>
+        <v>0.6902788514949701</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-1.413351375184906</v>
+        <v>-1.410702010855441</v>
       </c>
     </row>
     <row r="8">
@@ -880,13 +880,13 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>-0.8082936343375829</v>
+        <v>-0.8082936343375845</v>
       </c>
       <c r="Q8" t="n">
         <v>0.5937796593638854</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.7114586088070329</v>
+        <v>-0.7114586088070234</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -930,7 +930,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-0.3470387053721214</v>
+        <v>-0.3470387053721199</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9589761123124237</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.519090254327467</v>
+        <v>1.727450049028765</v>
       </c>
       <c r="C10" t="n">
         <v>1.297445978630116</v>
@@ -964,7 +964,7 @@
         <v>1.647037727361394</v>
       </c>
       <c r="F10" t="n">
-        <v>1.988006470455419</v>
+        <v>-1.269241519693938</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3103265160783306</v>
@@ -980,129 +980,19 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.4374077842045511</v>
+        <v>0.5087731052252982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.04846616470601493</v>
+        <v>-0.06079065192053278</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.6065676042132055</v>
+        <v>-0.4883631459585451</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>1.151578125668891</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.727450049028765</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.5663601230131231</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.4336396603437624</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1.66951171956164</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1.269241519693938</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.3103265160783306</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.306031248928484</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
-        <v>-0.5617101627100337</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.7045200230732235</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.8809730903795808</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="n">
-        <v>-0.003995095342279618</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.3014139890931187</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-0.5721993865741554</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.519090254327467</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.183335400978489</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.036059074651396</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2.127697067495167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.988006470455419</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.3103265160783306</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-2.070864617307837</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>-0.2287750814902195</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.7534326061140151</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.4717666174299594</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.0004662700274582115</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1.21859965207908</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-1.293994384654854</v>
-      </c>
-      <c r="V12" t="n">
-        <v>-1.224303173524103</v>
+        <v>1.151406407610498</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -570,19 +570,19 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>-0.1154423519880312</v>
+        <v>-0.116117335228587</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5215413689659228</v>
+        <v>0.5338540631434774</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.7242905259271538</v>
+        <v>-0.7279442179579094</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.321454953904791</v>
+        <v>1.264969588871839</v>
       </c>
     </row>
     <row r="3">
@@ -682,19 +682,19 @@
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-0.7394079049695005</v>
+        <v>-0.7349714040284639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9885172110219901</v>
+        <v>0.9249863603780604</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.107153569199315</v>
+        <v>-1.009057336819134</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2431770524406804</v>
+        <v>0.2122845277151693</v>
       </c>
     </row>
     <row r="5">
@@ -732,19 +732,19 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.324191875795249</v>
+        <v>1.472908329348411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.8979453430857665</v>
+        <v>-0.9475779087627235</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.3957561223554982</v>
+        <v>-0.3289659576072819</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.456994967757046</v>
+        <v>-0.4383863373477119</v>
       </c>
     </row>
     <row r="6">
@@ -782,19 +782,19 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>-0.03250891075221508</v>
+        <v>-0.004506514993771841</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.6155101675760588</v>
+        <v>-0.6721714681308216</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1654910366005701</v>
+        <v>0.2420284983931011</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-1.370823558187982</v>
+        <v>-1.350001748025615</v>
       </c>
     </row>
     <row r="7">
@@ -830,19 +830,19 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.3387096095963538</v>
+        <v>0.2841551697392878</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1455483752215773</v>
+        <v>-0.03876914916063828</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6902788514949701</v>
+        <v>0.6845932758365587</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-1.410702010855441</v>
+        <v>-1.450835929975729</v>
       </c>
     </row>
     <row r="8">
@@ -880,19 +880,19 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>-0.8082936343375845</v>
+        <v>-0.865563508626034</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5937796593638854</v>
+        <v>0.6988212577846828</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.7114586088070234</v>
+        <v>-0.8277127336628463</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3292855745945031</v>
+        <v>0.3373820491890105</v>
       </c>
     </row>
     <row r="9">
@@ -930,19 +930,19 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-0.3470387053721199</v>
+        <v>-0.3070960135022786</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9589761123124237</v>
+        <v>-1.008504640495977</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.3623551914718397</v>
+        <v>-0.3900929297854547</v>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3690291756211415</v>
+        <v>0.3316026931537518</v>
       </c>
     </row>
     <row r="10">
@@ -980,19 +980,25 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.5087731052252982</v>
+        <v>0.477470830502758</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.06079065192053278</v>
+        <v>-0.1337696129140001</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.4883631459585451</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+        <v>-0.3872988650172041</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8915250364242157</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3746500281677533</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.02944614276079314</v>
+      </c>
       <c r="V10" t="n">
-        <v>1.151406407610498</v>
+        <v>1.152985202235945</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,282 +538,328 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>x4pn9lxH</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.519090254327467</v>
       </c>
       <c r="C2" t="n">
-        <v>1.081903776399266</v>
+        <v>-1.3144183542849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6686343909026068</v>
+        <v>1.036059074651396</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5799739922644176</v>
+        <v>-0.4870897428325585</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6205523013167357</v>
+        <v>1.988006470455419</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3103265160783306</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.728143232208024</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>1.134565214604147</v>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>1.03717755812051</v>
+      </c>
       <c r="P2" t="n">
-        <v>-0.116117335228587</v>
+        <v>0.1013982623680225</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5338540631434774</v>
+        <v>0.6644021340126427</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.7279442179579094</v>
+        <v>1.161812490188133</v>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.264969588871839</v>
+        <v>-2.62111520602651</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.762176681478981</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.4268916392166902</v>
+        <v>-1.149591964343661</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6318919225277279</v>
+        <v>0.9258316695267595</v>
       </c>
       <c r="E3" t="n">
-        <v>2.156536627903193</v>
+        <v>-0.4101842484111548</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.283043417957283</v>
+        <v>-0.6205523013167357</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.226640650748756</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-0.3824166841896761</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.134565214604147</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-2.324313059838333</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.6588350919331993</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.8661009280428361</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1934277589006974</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.334726473868955</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-2.153891304989904</v>
+      </c>
       <c r="P3" t="n">
-        <v>1.258416742344588</v>
+        <v>-0.4898471035695668</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5050452221852312</v>
+        <v>-0.1084575134707216</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2456896939542993</v>
+        <v>0.4251471542603153</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2894702030238677</v>
+        <v>-0.09575042990325328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>r7j4bXNb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.762176681478981</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.352455213502108</v>
+        <v>0.6888562311547728</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3968971919688834</v>
+        <v>-1.388943838090616</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4101842484111548</v>
+        <v>-0.4870897428325585</v>
       </c>
       <c r="F4" t="n">
-        <v>1.988006470455419</v>
+        <v>0.7596375250177376</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8839192656489443</v>
+        <v>-1.648752634028296</v>
       </c>
       <c r="I4" t="n">
         <v>0.2938567128847251</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.225917709408243</v>
+        <v>-1.192766529892296</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3859749293291037</v>
+        <v>0.7777786873024672</v>
       </c>
       <c r="L4" t="n">
-        <v>2.95008242183073</v>
+        <v>0.0181366774156729</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8015790771651877</v>
+        <v>-0.3040756591322451</v>
       </c>
       <c r="N4" t="n">
-        <v>1.225733055340246</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>1.63392532989419</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
       <c r="P4" t="n">
-        <v>-0.7349714040284639</v>
+        <v>0.419868894135721</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9249863603780604</v>
+        <v>0.3390223810509602</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.009057336819134</v>
+        <v>1.20464527404834</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2122845277151693</v>
+        <v>-1.212809692014735</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>tI0qkTpo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.623270151678116</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.048160339764437</v>
+        <v>1.183335400978489</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.168489027841342</v>
+        <v>-1.058261622716705</v>
       </c>
       <c r="E5" t="n">
-        <v>1.262510255254375</v>
+        <v>0.5799739922644176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7596375250177376</v>
+        <v>0.09714640837719042</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.648752634028296</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>1.306031248928484</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.554919465463859</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.143568854677252</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.344993719195922</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.13506838957379</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.4035763427388336</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7154927121478168</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.090201683953099</v>
+      </c>
       <c r="P5" t="n">
-        <v>1.472908329348411</v>
+        <v>0.2831342440773292</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9475779087627235</v>
+        <v>1.324004508720818</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.3289659576072819</v>
+        <v>-0.1196322832964652</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.4383863373477119</v>
+        <v>-0.1926718135905663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>WSMotj8U</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.519090254327467</v>
+        <v>1.553816886777683</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.5283232637959141</v>
+        <v>-0.4142126861442872</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9625741379016386</v>
+        <v>1.329998821650428</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.45802160990278</v>
+        <v>1.262510255254375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09714640837719042</v>
+        <v>1.988006470455419</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.226640650748756</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+        <v>-0.3824166841896761</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.126497537974986</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3323614017740999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.050638849906563</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.531233029771436</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.000580444378365</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3073004375938732</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
       <c r="P6" t="n">
-        <v>-0.004506514993771841</v>
+        <v>-0.763721119041315</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.6721714681308216</v>
+        <v>-0.9061297107448892</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2420284983931011</v>
+        <v>0.1875660157345279</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-1.350001748025615</v>
+        <v>0.8891803881084344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>vZqDdBhB</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.519090254327467</v>
+        <v>1.762176681478981</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.3144183542849</v>
+        <v>0.6127825127203549</v>
       </c>
       <c r="D7" t="n">
-        <v>1.183028948150912</v>
+        <v>-1.095004091091584</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4870897428325585</v>
+        <v>2.146923441100518</v>
       </c>
       <c r="F7" t="n">
         <v>1.988006470455419</v>
@@ -821,106 +867,136 @@
       <c r="G7" t="n">
         <v>-0.3103265160783306</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2.572367198767104</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-2.228268792273541</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.832336307687882</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-2.879056387115593</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.6799456426831502</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.005573608312479569</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.9172763860679577</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1.090201683953099</v>
+      </c>
       <c r="P7" t="n">
-        <v>0.2841551697392878</v>
+        <v>-0.5971097259890576</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.03876914916063828</v>
+        <v>0.4033652756166482</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6845932758365587</v>
+        <v>0.5271289491778925</v>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-1.450835929975729</v>
+        <v>0.4848501586402499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.553816886777683</v>
+        <v>1.727450049028765</v>
       </c>
       <c r="C8" t="n">
-        <v>1.043866917182056</v>
+        <v>1.056545870254459</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6908369389679152</v>
+        <v>-0.4336396603437624</v>
       </c>
       <c r="E8" t="n">
         <v>2.146923441100518</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8286470163344613</v>
+        <v>-1.269241519693938</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H8" t="n">
-        <v>1.728143232208024</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+        <v>0.03969529908986404</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2938567128847251</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.070326529999776</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.442442607879927</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.657260890821503</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7904318605402285</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3073004375938732</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
       <c r="P8" t="n">
-        <v>-0.865563508626034</v>
+        <v>-0.9038841234103588</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6988212577846828</v>
+        <v>-0.8654864935529429</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8277127336628463</v>
+        <v>0.1538289493976941</v>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3373820491890105</v>
+        <v>1.452539709026321</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.623270151678116</v>
+        <v>1.519090254327467</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.022802433619631</v>
+        <v>1.081903776399266</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7053768592774857</v>
+        <v>0.6686343909026068</v>
       </c>
       <c r="E9" t="n">
-        <v>2.146923441100518</v>
+        <v>0.5799739922644176</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.034609249217078</v>
+        <v>-0.6205523013167357</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8839192656489443</v>
+        <v>1.728143232208024</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -930,47 +1006,53 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-0.3070960135022786</v>
+        <v>-0.116117335228587</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.008504640495977</v>
+        <v>0.5338540631434774</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.3900929297854547</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+        <v>-0.7279442179579094</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4778191805971497</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.008771347288438</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.3014139890931187</v>
+      </c>
       <c r="V9" t="n">
-        <v>0.3316026931537518</v>
+        <v>1.264969588871839</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.727450049028765</v>
+        <v>1.762176681478981</v>
       </c>
       <c r="C10" t="n">
-        <v>1.297445978630116</v>
+        <v>-0.4268916392166902</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6173520022181572</v>
+        <v>0.6318919225277279</v>
       </c>
       <c r="E10" t="n">
-        <v>1.647037727361394</v>
+        <v>2.156536627903193</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.269241519693938</v>
+        <v>-1.283043417957283</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4618072823694042</v>
+        <v>-1.226640650748756</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -980,25 +1062,369 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.477470830502758</v>
+        <v>1.302947419504265</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1337696129140001</v>
+        <v>0.4638721455389415</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.3872988650172041</v>
+        <v>-0.2628410502686603</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8915250364242157</v>
+        <v>0.0004662700274582115</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3746500281677533</v>
+        <v>-0.1724584031788525</v>
       </c>
       <c r="U10" t="n">
+        <v>-0.9631342528009423</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.2855178403151039</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.519090254327467</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.352455213502108</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3968971919688834</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.166149814705868</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.988006470455419</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8839192656489443</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2938567128847251</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-2.225917709408243</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3859749293291037</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.95008242183073</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.8015790771651877</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.225733055340246</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>-0.6980402319756048</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.9249863603780604</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1.085067315065873</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3346133074262422</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.4140284295105418</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.9631342528009423</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2122845277151693</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.5885435192279</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.043866917182056</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.6908369389679152</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.243283881649024</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8286470163344613</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.728143232208024</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>-0.8640361325567594</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.8525002253091506</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.9141948553913041</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2677838999464854</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.3412752218982436</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.35288667017644</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2661210062982308</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.727450049028765</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.022802433619631</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7053768592774857</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.146923441100518</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.034609249217078</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.8839192656489443</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>-0.3070960135022771</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.008504640495977</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.3900929297854547</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.534168989810596</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.368336730451094</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.9631342528009423</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.3316026931537518</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.692723416578548</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.048160339764437</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.168489027841342</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.262510255254375</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7596375250177376</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.648752634028296</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>1.408438752303929</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.8591478422325544</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.3737911915589178</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4459956532258368</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.04408051845070462</v>
+      </c>
+      <c r="U14" t="n">
         <v>0.02944614276079314</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.152985202235945</v>
+      <c r="V14" t="n">
+        <v>-0.4566965419221502</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.657996784128332</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.5283232637959141</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9625741379016386</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.45802160990278</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.09714640837719042</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-1.226640650748756</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>-0.004506514993771841</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.6721714681308216</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2420284983930916</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>0.2200928896101428</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6911664064686167</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.350001748025615</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.553816886777683</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-1.3144183542849</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.183028948150912</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.4870897428325585</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.988006470455419</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0.2841551697392878</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.03876914916063828</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6845932758365587</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.8905924963692992</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.4346890238678573</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.3014139890931187</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-1.450835929975729</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,113 +538,573 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>8OhVCWxh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.519090254327467</v>
+        <v>1.657996784128332</v>
       </c>
       <c r="C2" t="n">
-        <v>1.081903776399266</v>
+        <v>-0.693149653737153</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6686343909026068</v>
+        <v>-0.5806095338432783</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5799739922644176</v>
+        <v>-0.6120611712673395</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6205523013167357</v>
+        <v>1.988006470455419</v>
       </c>
       <c r="G2" t="n">
         <v>-0.3103265160783306</v>
       </c>
       <c r="H2" t="n">
-        <v>1.728143232208024</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-0.3824166841896761</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7142109637444363</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.651592102526801</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.005828828644260011</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.716218997514496</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.4035763427388336</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.63392532989419</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
       <c r="P2" t="n">
-        <v>-0.116117335228587</v>
+        <v>0.1317484024794229</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5338540631434774</v>
+        <v>-0.2389784349022492</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.7279442179579094</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.371740756026107</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.8307723805177193</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.9631342528009423</v>
-      </c>
+        <v>-0.2751622701448405</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1.264969588871839</v>
+        <v>0.1957427264409271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.762176681478981</v>
+        <v>1.553816886777683</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.4268916392166902</v>
+        <v>0.5747456535031459</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6318919225277279</v>
+        <v>-0.6173520022181572</v>
       </c>
       <c r="E3" t="n">
-        <v>2.156536627903193</v>
+        <v>-1.304210621059973</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.283043417957283</v>
+        <v>1.988006470455419</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3103265160783306</v>
       </c>
-      <c r="H3" t="n">
-        <v>-1.226640650748756</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>-0.126497537974986</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1.783138632472837</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.005828828644260011</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.6799456426831502</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.6025777099520107</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9195888494247885</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-2.153891304989904</v>
+      </c>
       <c r="P3" t="n">
-        <v>1.302947419504265</v>
+        <v>-0.2546919767275423</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4638721455389415</v>
+        <v>-0.2368760503253837</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.2628410502686412</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.0004662700274582115</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.1184230025520272</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.6322741209470305</v>
-      </c>
+        <v>-0.3630496630473681</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.2855178403151039</v>
+        <v>0.6898056868452878</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.519090254327467</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.3144183542849</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.036059074651396</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.073494137795762</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.988006470455419</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>2.815982218042992</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1.783138632472837</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.691987455906982</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4369860694749668</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.8015790771651877</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.225733055340246</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.03717755812051</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.860950409672971</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8789200218079906</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3571259659829081</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>-2.719494679924857</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.5885435192279</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.149591964343661</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9258316695267595</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.175763001508544</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.6429590138718</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.3824166841896761</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.134565214604147</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-2.324313059838333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.6588350919331993</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.8661009280428361</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1934277589006974</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.334726473868955</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-2.153891304989904</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4496840542844665</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.6821896106182261</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.09546533780445926</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.346358419539581</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.727450049028765</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.183335400978489</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.058261622716705</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.073494137795762</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.4687314204199436</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.306031248928484</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.554919465463859</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.143568854677252</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.344993719195922</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.13506838957379</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.4035763427388336</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7154927121478168</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.090201683953099</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.627633009473924</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1433348553579947</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.07639282780570879</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.2816279006250172</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.519090254327467</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6888562311547728</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.388943838090616</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05124871811726728</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.270307760761493</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-1.648752634028296</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2938567128847251</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.192766529892296</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7777786873024672</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0181366774156729</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.3040756591322451</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.63392532989419</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0994556205592898</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8888618065020447</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.411928797522559</v>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-1.488008588701307</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.553816886777683</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.4142126861442872</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.329998821650428</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6857190470938477</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.988006470455419</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.3824166841896761</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.126497537974986</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3323614017740999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.050638849906563</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.531233029771436</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.000580444378365</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3073004375938732</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.4602822135828376</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.200373958363982</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2885740397285356</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.784824870908971</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.692723416578548</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.6127825127203549</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.095004091091584</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.175763001508544</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.39972192910322</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.572367198767104</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-2.228268792273541</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.832336307687882</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-2.879056387115593</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.6799456426831502</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.005573608312479569</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.9172763860679577</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.090201683953099</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.486095099512631</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2207489315151285</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.6794485003685701</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.7767379539058407</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.519090254327467</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.056545870254459</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.4336396603437624</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.323436994665323</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.490071891907454</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.3103265160783306</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.03969529908986404</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2938567128847251</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.070326529999776</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1.442442607879927</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.657260890821503</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7904318605402285</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3073004375938732</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.02651206291629423</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-1.006562501788553</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.879706859934357</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.5109712974316841</v>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>1.799043016174546</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,650 +461,1984 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.657996784128332</v>
+        <v>1.573238689761835</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.693149653737153</v>
+        <v>-0.5761763022038064</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5806095338432783</v>
+        <v>-0.3886791966078407</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6120611712673395</v>
+        <v>0.7824474868221981</v>
       </c>
       <c r="F2" t="n">
-        <v>1.988006470455419</v>
+        <v>1.261988283971336</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3103265160783306</v>
+        <v>-0.9218765849180053</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3824166841896761</v>
+        <v>-0.2287672839087636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7142109637444363</v>
+        <v>-0.7323406985236492</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.651592102526801</v>
+        <v>-2.292603792049225</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.005828828644260011</v>
+        <v>-1.213487330884536</v>
       </c>
       <c r="L2" t="n">
-        <v>0.716218997514496</v>
+        <v>-2.63788338947508</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4035763427388336</v>
+        <v>-1.983900390866941</v>
       </c>
       <c r="N2" t="n">
-        <v>1.63392532989419</v>
+        <v>-1.088394189931904</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.02651206291629423</v>
+        <v>3.553499389604492</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1317484024794229</v>
+        <v>0.5922897171403941</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2389784349022492</v>
+        <v>0.6300260445361239</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2751622701448405</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>2.018529228597021</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-3.644053496801368</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.8677863821581575</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.552415113077356</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.1957427264409271</v>
+        <v>0.05720038943394449</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-2.353003990881652</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-2.441096791664881</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>0.137975956222854</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.3748302737235641</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-2.196922922358198</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.533084192243063</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>-2.253421569755531</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-2.329941311186687</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.553816886777683</v>
+        <v>1.71483521195432</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5747456535031459</v>
+        <v>1.030012435513498</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6173520022181572</v>
+        <v>0.9593728649913704</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.304210621059973</v>
+        <v>-0.5835108872250427</v>
       </c>
       <c r="F3" t="n">
-        <v>1.988006470455419</v>
+        <v>1.96384970268984</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3103265160783306</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
       <c r="I3" t="n">
-        <v>-0.126497537974986</v>
+        <v>3.904996351714279</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.783138632472837</v>
+        <v>1.27188774652232</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.005828828644260011</v>
+        <v>1.029895218092143</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6799456426831502</v>
+        <v>-0.01595266339741781</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6025777099520107</v>
+        <v>2.69318636766769</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9195888494247885</v>
+        <v>3.439297845715287</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.153891304989904</v>
+        <v>0.8781259210034177</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2546919767275423</v>
+        <v>-0.6919311777281673</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2368760503253837</v>
+        <v>-1.172875093672041</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.3630496630473681</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+        <v>0.2810941843530353</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.8318456725828507</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.201633920701586</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.4651616164308853</v>
+      </c>
       <c r="V3" t="n">
-        <v>0.6898056868452878</v>
+        <v>-0.172374028243528</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1.228010482036265</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-2.49682472422616</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>0.1246282425556696</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1.042711833790355</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-1.182959508956664</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1076600936528267</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>-1.69883981486867</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>-1.395601494236466</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>x4pn9lxH</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.519090254327467</v>
+        <v>1.608637820309956</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.3144183542849</v>
+        <v>-1.360299937939813</v>
       </c>
       <c r="D4" t="n">
-        <v>1.036059074651396</v>
+        <v>1.177975902007459</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.073494137795762</v>
+        <v>0.6882434610258367</v>
       </c>
       <c r="F4" t="n">
-        <v>1.988006470455419</v>
+        <v>0.6006188701788999</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3103265160783306</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
       <c r="I4" t="n">
-        <v>2.815982218042992</v>
+        <v>0.6463270731687079</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.783138632472837</v>
+        <v>0.8899779388182255</v>
       </c>
       <c r="K4" t="n">
-        <v>1.691987455906982</v>
+        <v>1.029895218092143</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4369860694749668</v>
+        <v>-0.01595266339741781</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8015790771651877</v>
+        <v>1.523914678034032</v>
       </c>
       <c r="N4" t="n">
-        <v>1.225733055340246</v>
+        <v>0.9239133814668476</v>
       </c>
       <c r="O4" t="n">
-        <v>1.03717755812051</v>
+        <v>1.948275308443847</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.860950409672971</v>
+        <v>-2.03730544854285</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8789200218079906</v>
+        <v>-0.72214980912</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3571259659829081</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>-1.456340859890951</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8318456725828507</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.201633920701586</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.9208838427801046</v>
+      </c>
       <c r="V4" t="n">
-        <v>-2.719494679924857</v>
+        <v>-0.06849239651195881</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.372828085659237</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.380213259265939</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>-1.588609433223827</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4301550303305826</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.040577505292451</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.5568500298820573</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>1.173450246311897</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>1.347372648783217</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5885435192279</v>
+        <v>1.750234342502441</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.149591964343661</v>
+        <v>-1.031473897147294</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9258316695267595</v>
+        <v>-1.15378982616415</v>
       </c>
       <c r="E5" t="n">
-        <v>2.175763001508544</v>
+        <v>0.0664968907698512</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6429590138718</v>
+        <v>-0.371189248046721</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3103265160783306</v>
+        <v>-0.9218765849180053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3824166841896761</v>
+        <v>-0.2287672839087636</v>
       </c>
       <c r="I5" t="n">
-        <v>1.134565214604147</v>
+        <v>-0.7323406985236492</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.324313059838333</v>
+        <v>-0.001144945824660649</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6588350919331993</v>
+        <v>-0.09179605639619649</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8661009280428361</v>
+        <v>-0.01595266339741781</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1934277589006974</v>
+        <v>-1.048483039160015</v>
       </c>
       <c r="N5" t="n">
-        <v>3.334726473868955</v>
+        <v>0.1692980421923159</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.153891304989904</v>
+        <v>0.3430512272832028</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4496840542844665</v>
+        <v>-0.4473176739436794</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6821896106182261</v>
+        <v>0.3295425215014297</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09546533780445926</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>1.07083738628212</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3345235426512709</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8677863821581575</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.07506870034820189</v>
+      </c>
       <c r="V5" t="n">
-        <v>0.346358419539581</v>
+        <v>-1.603595887770427</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.06853733496006581</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.3905881520095791</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>0.5905080355510274</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.4025890456174009</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8173026684422859</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4705633418503638</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>0.3096916418064927</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>-0.7152829557059008</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tI0qkTpo</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.727450049028765</v>
+        <v>1.608637820309956</v>
       </c>
       <c r="C6" t="n">
-        <v>1.183335400978489</v>
+        <v>-1.056768207977488</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.058261622716705</v>
+        <v>-1.335959023677556</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.073494137795762</v>
+        <v>2.148405860869439</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4687314204199436</v>
+        <v>0.6006188701788999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3103265160783306</v>
+        <v>-0.9218765849180053</v>
       </c>
       <c r="H6" t="n">
-        <v>1.306031248928484</v>
+        <v>-0.2287672839087636</v>
       </c>
       <c r="I6" t="n">
-        <v>1.554919465463859</v>
+        <v>0.6463270731687079</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.143568854677252</v>
+        <v>0.6353714003488294</v>
       </c>
       <c r="K6" t="n">
-        <v>2.344993719195922</v>
+        <v>1.029895218092143</v>
       </c>
       <c r="L6" t="n">
-        <v>1.13506838957379</v>
+        <v>1.295012699641414</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4035763427388336</v>
+        <v>-1.048483039160015</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7154927121478168</v>
+        <v>-0.08224040423252799</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.090201683953099</v>
+        <v>1.948275308443847</v>
       </c>
       <c r="P6" t="n">
-        <v>1.627633009473924</v>
+        <v>-1.548078440973875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1433348553579947</v>
+        <v>-1.172875093672041</v>
       </c>
       <c r="R6" t="n">
-        <v>0.07639282780570879</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+        <v>-0.03480309641859847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-2.649409236938209</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.2991373871135568</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6861649278405095</v>
+      </c>
       <c r="V6" t="n">
-        <v>-0.2816279006250172</v>
+        <v>-0.8956039401246199</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1067390200938163</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1118958834236394</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-0.6624566958919285</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9681969560442006</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.205542258119396</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.3308999600108825</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>0.7963245271094783</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>0.2241431423259405</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r7j4bXNb</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.519090254327467</v>
+        <v>1.573238689761835</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6888562311547728</v>
+        <v>-0.5382348359585157</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.388943838090616</v>
+        <v>1.032240543996733</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05124871811726728</v>
+        <v>-1.280620678118117</v>
       </c>
       <c r="F7" t="n">
-        <v>1.270307760761493</v>
+        <v>1.96384970268984</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3103265160783306</v>
+        <v>-0.9218765849180053</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.648752634028296</v>
+        <v>-0.2287672839087636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2938567128847251</v>
+        <v>-2.737675639167078</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.192766529892296</v>
+        <v>0.7626746695835275</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7777786873024672</v>
+        <v>-0.09179605639619649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0181366774156729</v>
+        <v>-0.01595266339741781</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3040756591322451</v>
+        <v>-2.919317742573868</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63392532989419</v>
+        <v>1.930067167166223</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02651206291629423</v>
+        <v>1.056484152243489</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0994556205592898</v>
+        <v>-2.709992583950192</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8888618065020447</v>
+        <v>0.1793007599840825</v>
       </c>
       <c r="R7" t="n">
-        <v>1.411928797522559</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>1.07083738628212</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-3.644053496801368</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.8825992717494139</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.0551738549281</v>
+      </c>
       <c r="V7" t="n">
-        <v>-1.488008588701307</v>
+        <v>-0.8066314516729988</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-4.136049817360202</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-4.336356774809949</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>0.1452764309389087</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2482321735556509</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.914272507818443</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.05154103465318432</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>-2.126594930842682</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>-2.996558559198801</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WSMotj8U</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.553816886777683</v>
+        <v>1.785633473050563</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.4142126861442872</v>
+        <v>1.282955543815435</v>
       </c>
       <c r="D8" t="n">
-        <v>1.329998821650428</v>
+        <v>0.7043359884726007</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6857190470938477</v>
+        <v>0.7824474868221981</v>
       </c>
       <c r="F8" t="n">
-        <v>1.988006470455419</v>
+        <v>-0.4386759229235002</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3103265160783306</v>
+        <v>-0.9218765849180053</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3824166841896761</v>
+        <v>-0.2287672839087636</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.126497537974986</v>
+        <v>-1.233674433684506</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3323614017740999</v>
+        <v>-0.7649645612328487</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.050638849906563</v>
+        <v>-0.09179605639619649</v>
       </c>
       <c r="L8" t="n">
-        <v>2.531233029771436</v>
+        <v>-0.01595266339741781</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.000580444378365</v>
+        <v>-0.5807743633065522</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3073004375938732</v>
+        <v>-1.339932636356748</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.02651206291629423</v>
+        <v>-1.262172853877442</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4602822135828376</v>
+        <v>-2.220765576381217</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.200373958363982</v>
+        <v>-0.2714245245679588</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2885740397285356</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+        <v>-0.03480309641859847</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.157442847143469</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-2.632984925656985</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.21969817457688</v>
+      </c>
       <c r="V8" t="n">
-        <v>0.784824870908971</v>
+        <v>0.3971433139463598</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.3187023028807089</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.06818159082674183</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>-0.688473135477103</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.06915461278079725</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.3912111534007649</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.001355101756566003</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>0.2526491881104964</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>-0.09934922358102802</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vZqDdBhB</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.692723416578548</v>
+        <v>1.573238689761835</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6127825127203549</v>
+        <v>-0.4370575926377407</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.095004091091584</v>
+        <v>0.6679021489699194</v>
       </c>
       <c r="E9" t="n">
-        <v>2.175763001508544</v>
+        <v>-1.261779872958845</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.39972192910322</v>
+        <v>1.96384970268984</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3103265160783306</v>
+        <v>-0.9218765849180053</v>
       </c>
       <c r="H9" t="n">
-        <v>2.572367198767104</v>
+        <v>-0.2287672839087636</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.228268792273541</v>
+        <v>1.648994543490422</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.832336307687882</v>
+        <v>1.90840409269581</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.879056387115593</v>
+        <v>-0.09179605639619649</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6799456426831502</v>
+        <v>-0.01595266339741781</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.005573608312479569</v>
+        <v>1.523914678034032</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9172763860679577</v>
+        <v>-0.3337788506573719</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.090201683953099</v>
+        <v>-1.262172853877442</v>
       </c>
       <c r="P9" t="n">
-        <v>1.486095099512631</v>
+        <v>-0.6307778017820452</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2207489315151285</v>
+        <v>1.681718375157554</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.6794485003685701</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+        <v>0.2810941843530353</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.826489932446011</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.8825992717494139</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.447494349074804</v>
+      </c>
       <c r="V9" t="n">
-        <v>0.7767379539058407</v>
+        <v>-0.2096590461920693</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-1.745893589253147</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.7165837710048489</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>0.9081789553612705</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.3302039481166408</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.243607681192111</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.026213889809446</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>-0.7419231203035238</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>-1.279814460566896</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.644036950858078</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5620676851549131</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.6801499126292917</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.261779872958845</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.626416328305944</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.484341301264935</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.019571099702245</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.326918026436249</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.983900390866941</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.8368557435070597</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8781259210034177</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.997698057458777</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.022633332154694</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.9824949387334998</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-1.157442847143469</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.2843244975223004</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3178260754911323</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.2168907683713144</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1867872257710262</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1571607598755916</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>-0.3066474447401574</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1.071637221309152</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.2243868917569426</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.3821333094872711</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>-0.3005613539471421</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>0.2620861000199569</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.71483521195432</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.7026478563547752</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5708483941212475</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.5835108872250427</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.4816738309432206</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.035707361930508</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-2.451609066720405</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.9239133814668476</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8781259210034177</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.8142379296204112</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.02905899846673543</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.7549401055104861</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-1.654764977075049</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.2991373871135568</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2523436128512433</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1403276252653953</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.52883324173642</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.08187990237810251</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>-0.2070487206630772</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6438760014669435</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.09366315324976227</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.1027958252487598</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>0.2442109553152302</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>0.2265347296241711</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.608637820309956</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.5620676851549131</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.607282233623929</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.261779872958845</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-1.567896923791745</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.847543515739993</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.213487330884536</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.326918026436249</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.905948944891364</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.259297976699973</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.3430512272832028</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-2.078074365840266</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.579945457363675</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.08745264321387058</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1687494993407442</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.062273677036777</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3317897186523135</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.06354393075869184</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.22112752243947</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.2333880545204417</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>-0.24892058324031</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.2765853027272763</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.7096167664490398</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.7068409693901283</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>0.7556522450362977</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>0.7664503995472911</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.322358471694522</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.032240543996733</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.035690211047578</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.8158963210504588</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7626746695835275</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.029895218092143</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6395300181219978</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.6587258092821294</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5885287862337225</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.483350002164062</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-1.548078440973875</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.182524246882044</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.965538292691575</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-3.146731366869788</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.2843244975223004</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.9280965831336265</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.7114478927935604</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-4.53481785219841</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-4.727712211159009</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>0.3397521097012298</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.08082154031326653</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-3.194032148638188</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.04981784444033</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>-3.390895350557375</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="n">
+        <v>-3.752175787473679</v>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.750234342502441</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6000091514002037</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.080922147158787</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.148405860869439</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.371189248046721</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.484341301264935</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.97434561896248</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.6526416936403662</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.8899295720899721</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1.633118883976844</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.968778752418857</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-2.064784894457764</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-2.404225704219582</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-2.975776231880207</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.061469258926408</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.577828867480221</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.2991373871135568</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.5871971149870433</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.513745507777779</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.732370867394129</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.7338487544093786</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>-0.1055602835272414</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.9234441400484393</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.08918119201283625</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.6042016668696024</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0.8293180173389662</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>1.676054683325506</v>
+      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.608637820309956</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.4244104372226438</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.323711260018184</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6882434610258367</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.233674433684506</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3807648618794334</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1.048483039160015</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9239133814668476</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.192023466437012</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4088295893020282</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.172875093672041</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.808272430526106</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.162798587280309</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.2991373871135568</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.5633853103907172</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.4662420148336422</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.531264356255374</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.878500541823825</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>0.1989306972237687</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-1.064108695790563</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.514777812103444</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.7267340093104</v>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>0.9720085339069102</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="n">
+        <v>1.532920872402042</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.675892083890785</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.372392863180238</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0664968907698512</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.261988283971336</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.1056735295725778</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.738666400382879</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.4656931478923095</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3546429884003742</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.259297976699973</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.3430512272832028</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.853845320704485</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5298648701912259</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.7718967515524108</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.660715889135484</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.840222856551253</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.0304215667300943</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.04364938770172225</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-1.198556037120645</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-2.769838198910187</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>1.365065671311309</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.17498375893975</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.337881722083585</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.22550640019065</v>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>-1.516067692523208</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="n">
+        <v>-1.745325162924062</v>
+      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.644036950858078</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.157945451298263</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.922939025488689</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.148405860869439</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.626416328305944</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.270326771798065</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.157428515842142</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.6526416936403662</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.326918026436249</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.9003031102294147</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.60699014333185</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.413200614723632</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-2.893452711788558</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.72214980912</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.035144485528772</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.8258947605224154</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.451248266794015</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.175051040958776</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5983829769291583</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.2875085659492818</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.09009078780212604</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>0.1229745554400039</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8081167292278156</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.2414945723311968</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.7446693721232016</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>0.4272151290625549</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
+        <v>0.269190668710752</v>
+      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.785633473050563</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.169131145079564</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.044488307656106</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.035690211047578</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.4386759229235002</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.2310069633627921</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7626746695835275</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.6714353449168335</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.75004605294021</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.433144060015911</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.948275308443847</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.04190933362529634</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.733410705778983</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.860580588211204</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.6601207172118889</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.034710151429872</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.5820812975933031</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.614111393803048</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1092263911869601</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1539430396934064</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="n">
+        <v>0.08591750525852117</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.4342881004325298</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.5106858504602174</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.141266668387917</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>-0.358827351398448</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>0.8779980922991847</v>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>zsmd0ggn</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1.519090254327467</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.056545870254459</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.4336396603437624</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-1.323436994665323</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.490071891907454</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.3103265160783306</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.03969529908986404</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2938567128847251</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.070326529999776</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-1.442442607879927</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1.657260890821503</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.7904318605402285</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3073004375938732</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.02651206291629423</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-1.006562501788553</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.879706859934357</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.5109712974316841</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>1.799043016174546</v>
+      <c r="B19" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.042659590928595</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.425113036110522</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.280620678118117</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.437478711099833</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.272994242119779</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1261583234100374</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.3546429884003742</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1692980421923159</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3430512272832028</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.570743732278346</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.924083901258777</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.8245462983476829</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.162798587280309</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.2843244975223004</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.4992164697202136</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-1.051819262573624</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.661294469613264</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.172307249508951</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>-1.002594571274465</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.2577144591576436</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.892588055069117</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-1.175784675199048</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>2.240570261183217</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="n">
+        <v>1.992251453882762</v>
+      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="n">
+        <v>-0.1868942137766378</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,23 +608,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1.821032603598684</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7026478563547752</v>
+        <v>0.675892083890785</v>
       </c>
       <c r="D2" t="n">
         <v>-0.5708483941212475</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5835108872250427</v>
+        <v>-0.4610456536897728</v>
       </c>
       <c r="F2" t="n">
-        <v>1.96384970268984</v>
+        <v>-1.235018686469495</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9218765849180053</v>
@@ -633,86 +633,76 @@
         <v>-0.2287672839087636</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4816738309432206</v>
+        <v>0.3538823943248747</v>
       </c>
       <c r="J2" t="n">
-        <v>2.035707361930508</v>
+        <v>2.502486015791067</v>
       </c>
       <c r="K2" t="n">
         <v>-0.09179605639619649</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01595266339741781</v>
+        <v>0.6395300181219978</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.451609066720405</v>
+        <v>-0.4248714713553979</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9239133814668476</v>
+        <v>2.097759464782786</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8781259210034177</v>
+        <v>1.591558845963704</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8142379296204112</v>
+        <v>-0.3453953807001425</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02905899846673543</v>
+        <v>0.1292201728116337</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7549401055104861</v>
+        <v>-0.1927517368044154</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.654764977075049</v>
+        <v>-0.4943466739013624</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2991373871135568</v>
+        <v>2.229197446308491</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2523436128512433</v>
+        <v>0.4296919491676082</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1403276252653953</v>
+        <v>-0.1357163656935234</v>
       </c>
       <c r="W2" t="n">
-        <v>0.52883324173642</v>
+        <v>0.5122729348529519</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08187990237810251</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-0.8983493814004372</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.2776012269506325</v>
-      </c>
+        <v>0.3421303381814558</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-0.2070487206630772</v>
+        <v>-0.3613413426042498</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6438760014669435</v>
+        <v>0.547342473600255</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.09366315324976227</v>
+        <v>0.2745615506514802</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1027958252487598</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.06975054614426714</v>
-      </c>
+        <v>1.184465795427284</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0.2442109553152302</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.7562891048212796</v>
-      </c>
+        <v>0.2147615228597485</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>0.2265347296241711</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-0.6310866090907351</v>
-      </c>
+        <v>0.4092430040820755</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
         <v>-0.1868942137766378</v>
       </c>
@@ -720,23 +710,23 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.573238689761835</v>
+        <v>1.608637820309956</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5620676851549131</v>
+        <v>-1.322358471694522</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.607282233623929</v>
+        <v>-1.044488307656106</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.261779872958845</v>
+        <v>-1.05453101620685</v>
       </c>
       <c r="F3" t="n">
-        <v>1.96384970268984</v>
+        <v>0.1147148110660895</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9218765849180053</v>
@@ -745,87 +735,1709 @@
         <v>-0.2287672839087636</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.567896923791745</v>
+        <v>-1.359007867474721</v>
       </c>
       <c r="J3" t="n">
-        <v>0.847543515739993</v>
+        <v>1.484059861913483</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.213487330884536</v>
+        <v>0.4690495808479731</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.326918026436249</v>
+        <v>0.6395300181219978</v>
       </c>
       <c r="M3" t="n">
         <v>-1.905948944891364</v>
       </c>
       <c r="N3" t="n">
-        <v>1.259297976699973</v>
+        <v>3.02006710167388</v>
       </c>
       <c r="O3" t="n">
+        <v>2.483350002164062</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.04190933362529634</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.831960136674901</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.649982401030115</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-1.654764977075049</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.396121215580206</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.6392854375415021</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.598631615273969</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.7980921357540146</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.270479777825258</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>-0.1146486795287062</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5227509412319546</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-2.28545659336099</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3442387731830103</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>-2.174075812002542</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>-0.8730168839038466</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.067953901758788</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.372392863180238</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1.05453101620685</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.76258688988317</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-2.654120016640269</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.1708826381375912</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.4656931478923098</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-2.217754728793673</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2531441910005974</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.3430512272832028</v>
       </c>
-      <c r="P3" t="n">
-        <v>-2.078074365840266</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.579945457363675</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.08745264321387058</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.1687494993407442</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.062273677036777</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.3317897186523135</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-0.06354393075869184</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.22112752243947</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.2333880545204417</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0008084515317019571</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.6058341641436644</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.24892058324031</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.2765853027272763</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.7096167664490398</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.7068409693901283</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.05161284348246963</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.7556522450362977</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.8076489777149362</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.7664503995472911</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.6310866090907351</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="P4" t="n">
+        <v>0.2457539201123693</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.982201898192248</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.1927517368044154</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.8258947605224154</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.8825992717494139</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8524755005679578</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7100205553354776</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.114324348701871</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.415469730844337</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>1.009720954039587</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4677283162411375</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3680688529052061</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.2294850733230617</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>0.4986658652564705</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>0.5492243307911934</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.785633473050563</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.157945451298263</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.323711260018184</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.3856824330526837</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.977347037665196</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.2727847746261967</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.07814178500874</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6395300181219978</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.056206002180569</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.936220952865599</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.840066464644206</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1642160855175403</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.6720692219475513</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2810941843530353</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6660716292723241</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.396121215580205</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.177283397639679</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.2545765865169869</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.05214473067500171</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.274600298979196</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>0.1935778806592455</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.5465720961604835</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3811411324515793</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.8645034031587318</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>0.2102681638962687</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>0.4441356111193154</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6000091514002037</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.607282233623929</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.12014465313053</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.941439222334255</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1685927464882699</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.6526416936403662</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.6714353449168335</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6664487723026831</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1.591471082781591</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.797247547597657</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.385002771784216</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.323116855189388</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1231455439672184</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9976197158933775</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.8825992717494139</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.6616090043505525</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.552446984721738</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.714767315371555</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.7691524930622073</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>-0.1181847840151379</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.06009066429459776</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9752080235927109</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.9147271266674809</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>1.193427762454689</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>1.41910264115428</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.856431734146805</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.169131145079564</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.922939025488689</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5846190326498391</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.5871466076524146</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2076600549029579</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.20823611190497</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.4656931478923098</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.4529411177436952</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.282337377086747</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.307374836803489</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.948275308443847</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.670385192866119</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.8723915706373472</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.9918630660892114</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-1.406103912109259</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.159517324476086</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.100639151595267</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6870134934684889</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.367843974445471</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2567774608692599</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>0.6228559015972123</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.03313427472576187</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.003269531999753482</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.4527879108151747</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="n">
+        <v>0.3503438830767818</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0.4107400578584253</v>
+      </c>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.679436081406199</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.7026478563547752</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.425113036110522</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.630283718989451</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.221521351494139</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.1474513408359824</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.27188774652232</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.9705315931844378</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8400672326585664</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.413200614723632</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2457539201123693</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.8723915706373472</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1231455439672184</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.820539020385575</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4788117924009195</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.8067121886093986</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.2223048903120447</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.9719077024675449</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.3602970865751696</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>-0.6002532526723294</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3831884229423927</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.19518973238048</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-2.122959129745616</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="n">
+        <v>0.6384346437190583</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>0.3337410678144038</v>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.4244104372226438</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.631468309467238</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.157826263449075</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.6070072647334349</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3807648618794334</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.8146287012332837</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.5853172970822158</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.7270981601572269</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.5696244258359233</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3295425215014297</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7549401055104861</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-1.654764977075049</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-2.632984925656985</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.07506870034820189</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1008717793880781</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.177039629883179</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.220857201578438</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>0.182038257047372</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.1011013164616694</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.514970733181296</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.8532418007466495</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>1.509439580637399</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>1.405038399889881</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.042659590928595</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.080922147158787</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.12014465313053</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01965990421763644</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-2.122866099736294</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4325944343759515</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.256086487548466</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-2.867396935038086</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.652281566873175</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.274648011465921</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.07049599717194631</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.489586105688117</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.1046500922349376</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.243137919726389</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.181077829186268</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.757333567887822</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.181107100473134</v>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="n">
+        <v>-0.2323327309425134</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.5540015621327767</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.807545713792162</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.6462896882127769</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>2.34106961377483</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>2.34866787776726</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.785633473050563</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.5761763022038064</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3886791966078407</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1.412506314233023</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.977347037665196</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.7323406985236492</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-2.292603792049225</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-1.213487330884536</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-2.63788338947508</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.983900390866941</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.088394189931904</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.553499389604492</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.5922897171403941</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6300260445361239</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.018529228597021</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-3.644053496801368</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8677863821581575</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.552415113077356</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2812238135377453</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-2.214989718531525</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.448088099766447</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>-0.01196826122371436</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.3574453233483926</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-2.267064126313037</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.600767178551694</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>-2.286267390911102</v>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>-2.189778105098589</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.679436081406199</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.030012435513498</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9593728649913704</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.3856824330526837</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1.221521351494139</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.904996351714279</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.27188774652232</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.029895218092143</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.69318636766769</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.439297845715287</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8781259210034177</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.6919311777281673</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1.172875093672041</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2810941843530353</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.8318456725828507</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.201633920701586</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.4651616164308853</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.2329754266907581</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-1.282297363465406</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-2.490293716695615</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>0.5189009472235848</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.09388599540752</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1.1288238068673</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.07752585954756704</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>-1.685967290739486</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>-1.294892356828254</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.608637820309956</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.360299937939813</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.177975902007459</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.4610456536897728</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1147148110660895</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6463270731687079</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8899779388182255</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.029895218092143</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.523914678034032</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.9239133814668476</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.948275308443847</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2.03730544854285</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.72214980912</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.456340859890951</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8318456725828507</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.201633920701586</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.9208838427801046</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.1200187384465058</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.408735321630329</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.501366123084674</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>-1.578736364403651</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.5250243578194791</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.059631073882837</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.4652021268969095</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>1.257426484311285</v>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="n">
+        <v>1.299973115688892</v>
+      </c>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.856431734146805</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.031473897147294</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.15378982616415</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5846190326498391</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.5871466076524146</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.7323406985236492</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.001144945824660649</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1.048483039160015</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1692980421923159</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3430512272832028</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.4473176739436794</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3295425215014297</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.07083738628212</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3345235426512709</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.8677863821581575</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.07506870034820189</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.502382969541509</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.126195570248367</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.3927186860811626</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>0.7730722161441083</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.4516235210345502</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.7779104013269705</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.3957379298508789</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0.3001986299118165</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>-0.7411915505380001</v>
+      </c>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.282955543815435</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7043359884726007</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.157826263449075</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.76258688988317</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.233674433684506</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.7649645612328487</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.5807743633065522</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1.339932636356748</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.262172853877442</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-2.220765576381217</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.2714245245679588</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.03480309641859847</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.157442847143469</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2.632984925656985</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.21969817457688</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4776102841596608</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.2208513766758446</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.1243698239590418</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>-0.5999194363830772</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.2857978405329209</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.4753776195904835</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.05709625463496378</v>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>0.1429310661900499</v>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="n">
+        <v>-0.008647464275859121</v>
+      </c>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.573238689761835</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.4370575926377407</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.6679021489699194</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.12014465313053</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.648994543490422</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.90840409269581</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.523914678034032</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.3337788506573719</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-1.262172853877442</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.6307778017820452</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.681718375157554</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2810941843530353</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.826489932446011</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.8825992717494139</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.447494349074804</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.2009306367341258</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-1.619028738286722</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.7222811961203495</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="n">
+        <v>0.5929195029928871</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.3774677341437271</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.272926706463571</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.020498059726158</v>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>-0.7510891506773798</v>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="n">
+        <v>-1.256352234177303</v>
+      </c>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.785633473050563</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.5382348359585157</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.032240543996733</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.630283718989451</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3.489676241908363</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.017281208052923</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.01595266339741781</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-3.932686540256372</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.930067167166223</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.413200614723632</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-2.526532456111826</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1793007599840825</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.07083738628212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-4.472923713354001</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.8825992717494139</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.04437379598575379</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.8092070741321544</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-3.996028311293969</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-4.572372604739789</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="n">
+        <v>0.5740022465166368</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.1234171452210953</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.869674018141807</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.1243257535981524</v>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="n">
+        <v>-2.249244644521871</v>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
+        <v>-2.93192759147357</v>
+      </c>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.785633473050563</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.056768207977488</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.335959023677556</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.12014465313053</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.96384970268984</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6463270731687079</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6353714003488294</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.029895218092143</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.295012699641414</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.048483039160015</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.08224040423252799</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.948275308443847</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-1.548078440973875</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.172875093672041</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.03480309641859847</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-2.649409236938209</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.2991373871135568</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6861649278405095</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.7348274518336191</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1227175924066835</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1216361722925678</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="n">
+        <v>-0.8594148318630721</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.5887245990659404</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.10299072534386</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.7216265463824453</v>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="n">
+        <v>0.7734727379207963</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>0.2645211448690192</v>
+      </c>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="n">
+        <v>-0.1868942137766378</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.821032603598684</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5620676851549131</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.6801499126292917</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1.412506314233023</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.235018686469495</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9218765849180053</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2287672839087636</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.4816738309432206</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.019571099702245</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.09179605639619649</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.326918026436249</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.3469200253798206</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-1.591471082781591</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3430512272832028</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-1.058851433404899</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.8723915706373472</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.9824949387334998</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.6601207172118889</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.2991373871135568</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.3178260754911323</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.3772389095408306</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.07026435648108394</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.1657924915359775</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="n">
+        <v>-0.07168308190152516</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.018788953359559</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.1374841841812439</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.3177003158210505</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="n">
+        <v>-0.3140203352555912</v>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="n">
+        <v>0.2266628779956525</v>
+      </c>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="n">
         <v>-0.1868942137766378</v>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,409 +425,2566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>dif_mean_last_30_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>dif_mean_last_180_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>dif_mean_last_30_matches_goal_attempts</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_30_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_180_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_30_matches_goals</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_last_30_matches_goals_against</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_180_matches_goals</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_180_matches_goals_against</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_last_30_matches_points</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>dif_mean_last_180_matches_points</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_last_30_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_180_matches_goal_ratio_against</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_30_matches_PPS</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_30_matches_PPS_against</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_180_matches_PPS</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_last_180_matches_PPS_against</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_30_matches_attacks</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_30_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_180_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.821032603598684</v>
+        <v>-0.9791716727913095</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.7026478563547752</v>
+        <v>-0.2144316357968612</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.5708483941212475</v>
+        <v>1.820577536872672</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5835108872250427</v>
+        <v>0.9276223122156908</v>
       </c>
       <c r="F2" t="n">
-        <v>1.96384970268984</v>
+        <v>-1.807738658276718</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9218765849180053</v>
+        <v>0.969240788922946</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2287672839087636</v>
+        <v>-1.317882671315732</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4816738309432206</v>
+        <v>-1.88785806199129</v>
       </c>
       <c r="J2" t="n">
-        <v>2.035707361930508</v>
+        <v>2.535030908405925</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.09179605639619649</v>
+        <v>-1.898021859403193</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01595266339741781</v>
+        <v>0.4389209813898919</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.451609066720405</v>
+        <v>-1.883212449918165</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9239133814668476</v>
+        <v>1.836131625927605</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8781259210034177</v>
+        <v>0.6914785406396636</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8142379296204112</v>
+        <v>0.9749943906544315</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02905899846673543</v>
+        <v>0.690479929778097</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7549401055104861</v>
+        <v>0.1513319016105389</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.654764977075049</v>
+        <v>-0.05994679080763907</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2991373871135568</v>
+        <v>-1.234878907709559</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2523436128512433</v>
+        <v>0.4687309520398528</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1403276252653953</v>
+        <v>1.461341357235435</v>
       </c>
       <c r="W2" t="n">
-        <v>0.52883324173642</v>
+        <v>-1.336178439479998</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08187990237810251</v>
+        <v>0.05315458653686211</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.8983493814004372</v>
+        <v>-0.9840970974249087</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.2776012269506325</v>
+        <v>-0.1959316116572213</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.2070487206630772</v>
+        <v>-0.3604036611784783</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6438760014669435</v>
+        <v>-0.2871170167853009</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.09366315324976227</v>
+        <v>0.7909865064205607</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.1027958252487598</v>
+        <v>-0.9845803562711131</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.06975054614426714</v>
+        <v>1.055106826932596</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2442109553152302</v>
+        <v>-0.9369860892129086</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.7562891048212796</v>
+        <v>1.618998785013775</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2265347296241711</v>
+        <v>1.297882733077671</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.6310866090907351</v>
+        <v>1.696975370093243</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.1868942137766378</v>
-      </c>
+        <v>-0.3986653370942375</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.369188650263038</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.7594208905727531</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1934050588694637</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1771253831654</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.3400385533376675</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.001634702959892351</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.573238689761835</v>
+        <v>-0.9791716727913095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5620676851549131</v>
+        <v>-0.2144316357968612</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.607282233623929</v>
+        <v>-1.840980382142393</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.261779872958845</v>
+        <v>-1.08428065123058</v>
       </c>
       <c r="F3" t="n">
-        <v>1.96384970268984</v>
+        <v>0.6531837121487459</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9218765849180053</v>
+        <v>-1.966374156860084</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2287672839087636</v>
+        <v>3.699336413145727</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.567896923791745</v>
+        <v>0.6665060933928998</v>
       </c>
       <c r="J3" t="n">
-        <v>0.847543515739993</v>
+        <v>-2.844926754544863</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.213487330884536</v>
+        <v>-0.04827809700722777</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.326918026436249</v>
+        <v>-1.94933930312765</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.905948944891364</v>
+        <v>1.128928481173307</v>
       </c>
       <c r="N3" t="n">
-        <v>1.259297976699973</v>
+        <v>0.04983033330445124</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3430512272832028</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-2.078074365840266</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.579945457363675</v>
-      </c>
+        <v>-1.284610669105834</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-0.08745264321387058</v>
+        <v>5.335769329494885</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1687494993407442</v>
+        <v>-2.982497731501146</v>
       </c>
       <c r="T3" t="n">
-        <v>1.062273677036777</v>
+        <v>2.959509539610773</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3317897186523135</v>
+        <v>-1.896510647227973</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.06354393075869184</v>
+        <v>-3.034039344270123</v>
       </c>
       <c r="W3" t="n">
-        <v>1.22112752243947</v>
+        <v>2.863104020569912</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2333880545204417</v>
+        <v>-0.8032173125261485</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008084515317019571</v>
+        <v>0.4681457078368119</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.6058341641436644</v>
+        <v>-0.5442914747449021</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.24892058324031</v>
+        <v>0.5123429795977122</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.2765853027272763</v>
+        <v>0.1204368660868552</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7096167664490398</v>
+        <v>-3.530133126753423</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7068409693901283</v>
+        <v>1.931129850456413</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05161284348246963</v>
+        <v>-1.959396638033005</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7556522450362977</v>
+        <v>1.687477301081975</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.8076489777149362</v>
+        <v>-5.787495784686499</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.7664503995472911</v>
+        <v>-2.364405540678881</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.6310866090907351</v>
+        <v>-0.2052043543652164</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.1868942137766378</v>
-      </c>
+        <v>-0.7826208542645894</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-1.980163710433372</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.7520229429351315</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-3.095296134772617</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-3.605052686682285</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-2.217113587341839</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.467359871499285</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3332800625479544</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09023567337589147</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3988136370407662</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.7703828826521827</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02004241787399014</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1726440654990714</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8796593198056827</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.188773487185711</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01361435537991863</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6360326924492476</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.5456034309032667</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.632601538986761</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.4186310289445481</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.771417761132297</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.010474136329083</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1.239110111427037</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.732499241976484</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.020503044845077</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-3.36397554254576</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.953981013754983</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.9895752050471989</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.061799016744476</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.1902075051827183</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.4424142685261549</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9981508005856273</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.792019129327138</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.91737650042468</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.430297287747842</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.5799923360327528</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-2.309337517509608</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2.157055330669462</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.433417688601312</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.07841616376327377</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.02174804538517216</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.704814318100327</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-2.262902947877846</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-1.856940304593184</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.7319384091847105</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-1.852820087856862</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1178943026058918</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.04026614046927191</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4277557087509933</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.295420227343283</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.540870186180686</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.308942018182414</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.189555165944621</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.510714037606219</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.164157839724623</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3074354999665418</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.5456034309032665</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.5021997129629462</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.5763531469738304</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8376464513175979</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.2674150070549899</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-2.072372512574055</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.090857842900004</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1802406017561286</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.4357917828494792</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.3521928588905846</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.9100729896835124</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.7461451512924981</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.08522961229013945</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.5665571340777448</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1.172196382902244</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.2383282872420855</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.7345883976955888</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.585569008877584</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.7045777884025107</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.1572449774644659</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3.8004883885615</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.4211389121824238</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-1.882737923751981</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.522225984339808</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.4861463712774861</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-0.6438575959172832</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.3233297008929393</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.229365304684545</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1.078353023111933</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.251349056756798</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.811855756025548</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.398764641543902</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.491411501551184</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.76385770104564</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2.519537142968312</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.121188011255865</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1.898021859403193</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.865837294689624</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.082783391306445</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.538414743823746</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.36068351594869</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.112866359549527</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.27026289530676</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1499095971432133</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.710420544456027</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.576857979725852</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.1290996539862686</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.987296274260257</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-3.154424453109856</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.99515684774963</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.592775722518767</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.739742633889672</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1.068545381412853</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-2.81363542923761</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.448961163955986</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2.524955559825278</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.430206199657486</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.4355003384263151</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.133616486382539</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.467800394219557</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-1.054129969788112</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-1.096026194931142</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.2362385906514446</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.05441606633761744</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3.343198304352252</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.672030792077131</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.2499397481347972</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.081955851132846</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.840980382142393</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5469920218339639</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.404610390141253</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.162365431067985</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.692448779361143</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9298991749362755</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1.189555165944621</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.263901605987729</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2753415098475946</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.457525673656012</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.8433203130071257</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1498094171561266</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.510669615138882</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.601120121705664</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.14682311468022</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-2.345034384514419</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.2930910436063331</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.692648059840043</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1.178148228969663</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.04915185661894165</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.06244515595873191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.697511759005682</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.4994702335732952</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1976637797757038</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-0.3902330594397031</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.8818246133746898</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.545446151873848</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.149946105103843</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.8006460663788546</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-2.324299333382145</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.619992342781062</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.7792121763922477</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2884799005916314</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.9792078325240995</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3177597325446732</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1.259988115694976</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.5653200321748095</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.8570054138901441</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.4092898210646472</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.9794373423741424</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.6275243027725078</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05204236975473894</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5343348710291638</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.648920126720871</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.07387165992030545</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.189555165944621</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-2.822893740601176</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.425884994192298</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.1854602887575175</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3475472154083103</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.632601538986761</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.02582911048768314</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.05235448814847767</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.029485317959347</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.8934118404852656</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.704870865660802</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-2.070800772721616</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-1.879262650305392</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.51247759686629</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.7310787734857416</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.107438367661381</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.2640221271409419</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.002862370362079673</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.476903855766776</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.8076423020755655</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.509360449483249</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1.885322728993082</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.708558867675551</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.3901227835981697</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.485643971050541</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.505295686214232</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.979630279078053</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.5222259843398079</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.7176225741359614</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1.60904927123983</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1.117508757186871</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.6965823437170215</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1.526198241719752</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5486658224900172</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8280728516543158</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.58379675181639</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3168819120822727</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4660174476038976</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.851774960338089</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.3618693716444992</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.9731499782052102</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.3085113731956824</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.7750545815765464</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3475472154083101</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.7257457004323427</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.2150804327316325</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.345908399645439</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.03234035476823457</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.9508297177751286</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.2150490162291797</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.6155169247187499</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1883396341427512</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.8716917199276869</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.213656008145223</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.3301380977019008</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.290599392862007</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01285218622944516</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.492862290939481</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1048001269036619</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.218387306810585</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.07977119614496521</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1.257617552040668</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.473167997009757</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1957740731309727</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.6615699399680609</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0.4641493359574517</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.551182619900826</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.9665888619980315</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1.698915875135767</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>-0.5454151305798348</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1.002161033400495</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.174420257046484</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.671538813533815</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1271850375539897</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.295420227343283</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.094895156450779</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.9138523958673513</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.707345114105804</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.510714037606219</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1444779326137568</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.471734096207895</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9429809796160279</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1498094171561263</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.8845498640787366</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1640929164578384</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.8558313825904</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.8781577388339441</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.637233768513238</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.01860054133494667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.930696080262935</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.1240144303934258</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5974726538417489</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.414005123813618</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.7749073510461526</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.1320001438473522</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.08702279115830808</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.7037870662567917</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-1.37884305718081</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.8694519764455698</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.9238260809757054</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-1.438810344012069</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.607915595513797</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.6948098125619963</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-1.132987880388999</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.4787298935694637</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.9579023697695072</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0.3689332160032817</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-0.02003197362736928</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.189741949186969</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.625183603903084</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8154439904763796</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6829314112560092</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5968267112993073</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.114209428220873</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.205865346928118</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0354601688618974</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3278687902722686</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8765937841907547</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.2131971466901</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.033087633365851</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.141037195110984</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.1109942348915029</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.621355385205324</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4963988271494859</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.8969699735794172</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.500602458509038</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.2048837282351325</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.1796639741545532</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4302907376240686</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2872555012609469</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.8619806303232406</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-1.269271465856791</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.2833377586185168</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.5529346578949738</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.3742746242669984</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.291492277006458</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1.018199656348684</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6676618027010524</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-1.309427099032762</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.038592376232249</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.842931982447279</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.3362249162245229</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.8681716828955234</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.4787298935694637</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.161541535960486</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.4518772449233756</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.4425436171481708</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.1368876838128075</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1631723100135709</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.051232595688163</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02498476645330978</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8034690477472469</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.060320161248038</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.09145133955848672</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.272858916529211</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-1.051607533561267</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.418046919520726</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2535309136419546</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.02116169251616429</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2.33190472352642</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.280211243179941</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.1003256808284609</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5932057047728545</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3178290967254213</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.7909345324566324</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.6447965748944166</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.2943411442939804</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.075043167008526</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.8284001481745951</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.504382051835556</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.32525188451503</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.6787153311192154</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5641083890922418</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.939698475775219</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1357094232782972</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.2327305545363422</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.1628638441102034</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.995120106183074</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.7743660419467022</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.062646393165605</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.6651444723721587</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.508096344947992</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.52318186224908</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.00632410363714</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.9321217193945593</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.5040216424480674</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.530893223079936</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-2.083953969660146</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.04609904929187117</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.4535218843122893</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4315128421409554</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.4804456040563274</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.50370560036986</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3372647414636811</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8796593198056823</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.898021859403193</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2055476019895476</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3101738099038976</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.9429809796160279</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.4239586173486574</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>-1.923480321358372</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.1073986095378436</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.759808794425976</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.032600341909271</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4509117500162959</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.05907707276378799</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.3498282319411319</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3519732923097216</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.5597922649057128</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.09982515248233159</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9215503117566439</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.8997872296592759</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.2471085465708082</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.7935233148143404</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2823927992265019</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.602385749072608</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.502608529858093</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.6538819506498141</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.5253315550980638</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.1218436331760993</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.5586042827588308</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.6153063300494976</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.452315764655668</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.8586653755568014</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.4419103711924239</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.533396523616589</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.400691387404408</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.010111384195187</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.476631026465692</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8004987199013281</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.061595715707963</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.05197352550556147</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.184884411256749</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6134057510350093</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.7318735402567037</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.141037195110985</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.3717978869391317</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.1779167660970395</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.3600340479265446</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.722529068017316</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.8656974300434761</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.576770940516226</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.8345614682752581</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.1828385889173407</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.96390622989983</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.7283462530675442</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.687086029407097</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.2921369206309946</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.2053831829459407</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.9487782904843762</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.191570987435831</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.580558857646236</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.05165966449892</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.5534167854178201</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.332428356583353</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.184018510696733</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.09602479122877616</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.118287412821056</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.9792078325240995</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.7352429170508935</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.4434341346547216</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.005240475447081543</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.2461475317737236</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.1943520534695151</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.343547155340539</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.14209823845628</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3901843748513675</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.277773120194929</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.172144578009584</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2722606796725272</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-1.327502798327974</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2600125300587663</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.711939352120111</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.9172360590931017</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1.141037195110985</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.154208843082019</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.7067923825420074</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.8654323665893426</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2835014831513768</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7529323300504914</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.733104392910686</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.063050888838353</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8427109854686152</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.4703470044181607</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.189584310612991</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.6109373181233146</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.3188473285213174</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.136135595683522</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.7329952623314533</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.187208461556084</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.12732294860176</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-1.546071173359483</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.365908879738944</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1.581002203760361</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-2.189480162399331</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-1.276667428430929</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-1.420377735766152</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.2862383785869117</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.306954538627741</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.542728821548021</v>
+      </c>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>0.7223066109408679</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.2831677568264804</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.051232595688163</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.742744742601709</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.26295431673215</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.857647677386638</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.320802921252887</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.2965248610000655</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.4998170040278528</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1.898021859403193</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.9732805884280636</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-2.732088530498488</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6452640975121691</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.105836807513344</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.3828639702651865</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.7163648896698529</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.7772373972097533</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1231882046609648</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-1.404688623838527</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2846751604255826</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.7808479482919333</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.03743128688724207</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.3373367100293739</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.4474786622036227</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.9203268376743536</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.3031892612108402</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.03914748564019462</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.154479831786269</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9225508481292816</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.207182806855468</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.4316673263183924</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.61186465079818</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.7079546650536878</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.134881383374761</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.702020856755325</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.52318186224908</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.610537413655055</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.566535511229268</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.521720252701141</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.1750673797541137</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.511181655159925</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.09749145733617086</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2642380918361099</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3213035960353879</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.625414243354255</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.915436294226097</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.06564062612207539</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.3278687902722687</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.04827809700722777</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4934474719039913</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.1717687390707377</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3475472154083101</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.280211243179941</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.9339492749802129</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2652485426883799</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.004265522859773663</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.339416880347925</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.01599552399631592</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.531537514211416</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.1209755517406587</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-2.375176161554202</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.7581448544317456</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1.471653275711676</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.7533819622803313</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.4030874198844936</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.3598133936774306</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.08436476690910474</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.6361621554671949</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.02552759121860512</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1.311982440438043</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.3515771555803998</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.4553050704732337</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.8769865577493418</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.3950534652457516</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.9792078325240995</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.8486067720053687</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.3647997963989313</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.09095223728105761</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.2350196650095548</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.6215553633573065</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.389806016988547</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.5133352156579897</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.60735821081205</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.114209428220873</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.6117555409100451</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6390693140654647</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.15555458457239</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.3565687240732219</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.253530913641955</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.6235898787344584</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.538414743823746</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.280211243179941</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.6370268378021041</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.776514047775256</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.9792860540206452</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3738536817453456</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.647706502803525</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-1.867685387939744</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.240011266146345</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.369544795088243</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.203804805833862</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.232903637803605</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.6831082676020359</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.623139119217582</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.05660312539603501</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.05469184238945506</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.04539274610538237</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-1.003811144790712</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.288077439436397</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.789754721516329</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-2.80753583087146</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.3680302374454505</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.9104083546309039</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.022703923294444</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.6734602112676302</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.480768606676449</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.7132267616662097</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.4792137981126023</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.282428141796284</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.9791716727913095</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2144316357968612</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8154439904763798</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7598342658433375</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.981282438670226</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.9878358415990738</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1.801022286856465</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.745186809488629</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6037640550389758</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2600125300587665</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.144649558615232</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.9032886794786671</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.9429809796160279</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.397941180526923</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8113346756157077</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.23312220132232</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1.132317893666773</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.203467486757713</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.4803058819642641</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.3146474946361962</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.2502026713194332</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.09244342837203351</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.63039590576909</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.6729763431141932</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.2018994745908407</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.09535917585830957</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-2.708765712388405</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.203934705985686</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.4222211549735611</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.660370583690626</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.1764280328754161</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.4226393667274085</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.66103682398231</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.6803969691906036</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.058634949511194</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.094200771716535</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.558116279472779</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>2.558901578389759</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.629149885565059</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.05341587113451081</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.340447161554236</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,485 +425,836 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_shots_on_goal</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_shots_on_goal</t>
+          <t>dif_mean_last_120_matches_points</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_shots_on_goal_against</t>
+          <t>dif_mean_last_480_matches_points</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goal_attempts</t>
+          <t>dif_mean_last_120_matches_goal_ratio</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goal_attempts_against</t>
+          <t>dif_mean_last_120_matches_dead_balls</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goal_attempts_against</t>
+          <t>dif_mean_last_480_matches_dead_balls</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goals</t>
+          <t>dif_mean_last_120_matches_yellow_cards</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goals_against</t>
+          <t>dif_mean_last_480_matches_PPDA</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goals</t>
+          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_goals_against</t>
+          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_points</t>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_points</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_30_matches_goal_ratio_against</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_goal_ratio_against</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_PPS</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_PPS_against</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_PPS</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_PPS_against</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_attacks</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_attacks_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_attacks</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_attacks_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_dangerous_attacks</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_dangerous_attacks_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_dead_balls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_total_passes</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_total_passes_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_total_passes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_total_passes_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_PPDA_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_30_matches_KGP_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_KGP_against</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_180_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
+          <t>dif_mean_hei_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.9791716727913095</v>
+        <v>1.757607451174561</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2144316357968612</v>
+        <v>-1.472319026116054</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8154439904763796</v>
+        <v>-0.3435988950344519</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6829314112560092</v>
+        <v>-2.10600921615861</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5968267112993073</v>
+        <v>-1.458165473918372</v>
       </c>
       <c r="G2" t="n">
-        <v>1.114209428220873</v>
+        <v>-0.1729365025868828</v>
       </c>
       <c r="H2" t="n">
-        <v>0.205865346928118</v>
+        <v>1.774069169816956</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0354601688618974</v>
+        <v>0.1368718406664856</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3278687902722686</v>
+        <v>1.664129447714067</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8765937841907547</v>
+        <v>0.8083530281461615</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2131971466901</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.033087633365851</v>
-      </c>
+        <v>-1.090920919934323</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.141037195110984</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-0.1109942348915029</v>
-      </c>
+        <v>-1.749874562616504</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.621355385205324</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.4963988271494859</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.8969699735794172</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.500602458509038</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2048837282351325</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1796639741545532</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.4302907376240686</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.2872555012609469</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.8619806303232406</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1.269271465856791</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.2833377586185168</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.5529346578949738</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.3742746242669984</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.291492277006458</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1.018199656348684</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.6676618027010524</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1.309427099032762</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.038592376232249</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.842931982447279</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-0.3362249162245229</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.8681716828955234</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-0.4787298935694637</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.161541535960486</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.4518772449233756</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.4425436171481708</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-0.1368876838128075</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.1631723100135709</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.2331176690628715</v>
+        <v>0.02625657604685302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9791716727913095</v>
+        <v>-0.3570768017001661</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2144316357968612</v>
+        <v>-1.240840478084596</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.051232595688163</v>
+        <v>-0.3435988950344519</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02498476645330978</v>
+        <v>-1.593858339356973</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8034690477472469</v>
+        <v>-0.3607820477767276</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.060320161248038</v>
+        <v>0.4860384074601836</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.09145133955848672</v>
+        <v>-1.576175569293908</v>
       </c>
       <c r="I3" t="n">
-        <v>1.272858916529211</v>
+        <v>-0.5316884024274262</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.051607533561267</v>
+        <v>1.250004688877847</v>
       </c>
       <c r="K3" t="n">
-        <v>2.418046919520726</v>
+        <v>1.184769473442908</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2535309136419546</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-0.02116169251616429</v>
-      </c>
+        <v>0.6259330946594892</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-2.33190472352642</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.280211243179941</v>
-      </c>
+        <v>0.3543466348808704</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-0.1003256808284609</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.5932057047728545</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.3178290967254213</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.7909345324566324</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.6447965748944166</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.2943411442939804</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-1.075043167008526</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.8284001481745951</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.504382051835556</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.32525188451503</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.6787153311192154</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.5641083890922418</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.939698475775219</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.1357094232782972</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.2327305545363422</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.1628638441102034</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.995120106183074</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.7743660419467022</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1.062646393165605</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.6651444723721587</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.508096344947992</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.52318186224908</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.00632410363714</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-0.9321217193945593</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-0.5040216424480674</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.530893223079936</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-2.083953969660146</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.1869829786383015</v>
+        <v>-1.059084551421595</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.115018874195642</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1914330378600514</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.6975943049541062</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.304401758060096</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.8364956026498997</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.712483788583301</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.122691339401614</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.007630412369188048</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-2.092229720242784</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.333864049667056</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>1.978570113345892</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>-0.2667534176854157</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.115018874195642</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.472319026116054</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7108206062503982</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.377566431314073</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.3768833460985067</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.022727518766359</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.062124756283405</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.234743864139471</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.252836178683421</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4738985528084406</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0.4990635866323858</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>-0.5669883153726699</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.4365015623715173</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.144533286875479</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7108206062503982</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7147629022227943</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.210717202886448</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.145898281233669</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9039142989816624</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1.717889416115061</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7262356646276392</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6685358773487863</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0.4998705025603173</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0.4129494910627722</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.115018874195642</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.144533286875479</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.222971483052036</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.1475969235322008</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.022772859945979</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.749435017323494</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8576891330650751</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.733150240853437</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-1.543765329142122</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.290344682454102</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>1.770388508776489</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>0.2730709717635018</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6655169919434814</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.255307887336562</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9668960446512173</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.443019358247917</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.736089351899065</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.1597118009198298</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.64204047414607</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.4064943464670319</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.410147593437902</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2811489836278221</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.3669889980904975</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5103950531517431</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05282830722445839</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.1267800259099407</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-1.042115362490571</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8858686819544256</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.3134811473528777</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.4182517218349441</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>-1.391419425592941</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09938838981990998</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.648868622975691</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.116548755971258</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.152126048150225</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.638667728552401</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-2.726830950137502</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-3.075636068664038</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5833769476911527</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.757607451174561</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.472319026116054</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.337782900956154</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.9699605927938222</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1951342487586736</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.4553216308413756</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.2259870441865293</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4217551712054078</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.137829055468208</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.569926300430548</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3669889980904975</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.929416347127918</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.9022154059018634</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.636607390914947</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.115018874195642</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.240840478084596</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-2.10600921615861</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9537807693497232</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.680511358436192</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.673215735828328</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.724682026077359</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.9586606915819915</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.7379877945225739</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.8459331799444618</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.369817361411947</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.2637738921848613</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.06331680299965177</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8972588861823602</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.115018874195642</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1914330378600514</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1986697294487602</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.07078783788902211</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-1.179557554855823</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.318337348687905</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.108835147161262</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.802171033992807</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.619454430652961</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.735929721764679</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.6358393652309517</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.726359697529305</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.04873723345106813</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.5715494921119623</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.115018874195642</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.5608722432421874</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.593858339356973</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.133959693300594</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.3526434699908486</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-2.475322135305279</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.5543250014346915</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.802171033992807</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.05910125470119348</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.7242771178521575</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-1.638667728552401</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.6831943640068706</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1.141795411124376</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2019020188649466</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.3570768017001661</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.144533286875479</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.222971483052036</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.017764912578611</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.916702409146755</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2.056541542916422</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.6143788624025488</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.4064943464670316</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7979074306940952</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.373635099611363</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.301563244123802</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1.394855387582703</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.360898492823596</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1409792933935686</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.4365015623715173</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.144533286875479</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.593858339356973</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.4595751541339473</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>-0.2089801059067541</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.9429702720023043</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-2.062993381811911</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.1469128158046059</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.2820349487957776</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1.304391607445251</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.8385582818982311</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.3059273929036111</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.01457507812330886</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.360483647817805</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9582057282142562</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.3435988950344519</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.8256320241545158</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1171827823338121</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.074660221685341</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.14126463320411</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6884329570906579</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.802171033992807</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.01198416624910162</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.3524960984508846</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.301563244123802</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.08233595902376178</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.4189600107521809</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1799864768679914</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,158 +508,158 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.757607451174561</v>
+        <v>2.105090779111723</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.472319026116054</v>
+        <v>2.130065877623513</v>
       </c>
       <c r="D2" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.10600921615861</v>
+        <v>-2.490122373759839</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.458165473918372</v>
+        <v>-0.5900387778401321</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1729365025868828</v>
+        <v>1.047496784531184</v>
       </c>
       <c r="H2" t="n">
-        <v>1.774069169816956</v>
+        <v>0.04967849527459998</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1368718406664856</v>
+        <v>0.4727100094631203</v>
       </c>
       <c r="J2" t="n">
-        <v>1.664129447714067</v>
+        <v>1.526087861435327</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8083530281461615</v>
+        <v>-0.4456319619401702</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.090920919934323</v>
+        <v>0.1846792379193768</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.749874562616504</v>
+        <v>0.7569298244699207</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.02625657604685302</v>
+        <v>0.4124031924087511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3570768017001661</v>
+        <v>0.7747260378665893</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.240840478084596</v>
+        <v>2.130065877623513</v>
       </c>
       <c r="D3" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.593858339356973</v>
+        <v>-1.849933777757792</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3607820477767276</v>
+        <v>0.2839729621335489</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4860384074601836</v>
+        <v>1.170565780670074</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.576175569293908</v>
+        <v>-2.179712305383732</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5316884024274262</v>
+        <v>-0.2367229032303907</v>
       </c>
       <c r="J3" t="n">
-        <v>1.250004688877847</v>
+        <v>-1.234743864139471</v>
       </c>
       <c r="K3" t="n">
-        <v>1.184769473442908</v>
+        <v>-1.13938516213256</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6259330946594892</v>
+        <v>-0.9690553461423925</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>0.3543466348808704</v>
+        <v>-0.3231272659783381</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-1.059084551421595</v>
+        <v>-0.3094773086056799</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2.115018874195642</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1914330378600514</v>
+        <v>-0.5608722432421874</v>
       </c>
       <c r="D4" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6975943049541062</v>
+        <v>0.4547451678495792</v>
       </c>
       <c r="F4" t="n">
-        <v>1.304401758060096</v>
+        <v>0.5091172518844762</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8364956026498997</v>
+        <v>-1.665907903404312</v>
       </c>
       <c r="H4" t="n">
-        <v>1.712483788583301</v>
+        <v>-0.2533215803949851</v>
       </c>
       <c r="I4" t="n">
-        <v>2.122691339401614</v>
+        <v>0.3892135449256445</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007630412369188048</v>
+        <v>0.6702300265071396</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.092229720242784</v>
+        <v>-0.2302913465233374</v>
       </c>
       <c r="L4" t="n">
-        <v>1.333864049667056</v>
+        <v>1.328315692513218</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1.978570113345892</v>
+        <v>2.486685762961803</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-0.2667534176854157</v>
+        <v>-0.8626985257345556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.115018874195642</v>
+        <v>-0.4365015623715173</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.472319026116054</v>
+        <v>0.712259770930832</v>
       </c>
       <c r="D5" t="n">
         <v>-0.3435988950344519</v>
@@ -668,593 +668,427 @@
         <v>0.7108206062503982</v>
       </c>
       <c r="F5" t="n">
-        <v>0.377566431314073</v>
+        <v>0.7147629022227943</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3768833460985067</v>
+        <v>1.210717202886448</v>
       </c>
       <c r="H5" t="n">
-        <v>1.022727518766359</v>
+        <v>1.145898281233669</v>
       </c>
       <c r="I5" t="n">
-        <v>1.062124756283405</v>
+        <v>0.9039142989816624</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.234743864139471</v>
+        <v>-1.717889416115061</v>
       </c>
       <c r="K5" t="n">
-        <v>1.252836178683421</v>
+        <v>0.7262356646276392</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4738985528084406</v>
+        <v>0.6465354766163154</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.4990635866323858</v>
+        <v>0.4998705025603173</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-0.5669883153726699</v>
+        <v>0.3515779458002276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.4365015623715173</v>
+        <v>0.7747260378665893</v>
       </c>
       <c r="C6" t="n">
-        <v>2.144533286875479</v>
+        <v>0.1914330378600514</v>
       </c>
       <c r="D6" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7108206062503982</v>
+        <v>-0.6975943049541062</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7147629022227943</v>
+        <v>1.304401758060096</v>
       </c>
       <c r="G6" t="n">
-        <v>1.210717202886448</v>
+        <v>-0.9092653428564665</v>
       </c>
       <c r="H6" t="n">
-        <v>1.145898281233669</v>
+        <v>2.562362049607748</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9039142989816624</v>
+        <v>2.332976092950914</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.717889416115061</v>
+        <v>0.007630412369188048</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7262356646276392</v>
+        <v>-2.098400129962572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6685358773487863</v>
+        <v>1.361390829131057</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.4998705025603173</v>
+        <v>1.948334061143572</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.4129494910627722</v>
+        <v>-0.2997815500513066</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.115018874195642</v>
+        <v>-1.439239165847327</v>
       </c>
       <c r="C7" t="n">
-        <v>2.144533286875479</v>
+        <v>-1.240840478084596</v>
       </c>
       <c r="D7" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E7" t="n">
-        <v>1.222971483052036</v>
+        <v>-1.593858339356973</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1475969235322008</v>
+        <v>-0.3607820477767276</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.022772859945979</v>
+        <v>0.4860384074601836</v>
       </c>
       <c r="H7" t="n">
-        <v>1.749435017323494</v>
+        <v>-1.576175569293908</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8576891330650751</v>
+        <v>-0.5316884024274262</v>
       </c>
       <c r="J7" t="n">
-        <v>1.733150240853437</v>
+        <v>1.250004688877847</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.543765329142122</v>
+        <v>1.184769473442908</v>
       </c>
       <c r="L7" t="n">
-        <v>2.290344682454102</v>
+        <v>0.6131617201301293</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1.770388508776489</v>
+        <v>0.3338504979143095</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.2730709717635018</v>
+        <v>-0.9569037669145777</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6655169919434814</v>
+        <v>-1.300245834672462</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.255307887336562</v>
+        <v>-0.3293936952107294</v>
       </c>
       <c r="D8" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9668960446512173</v>
+        <v>0.7108206062503982</v>
       </c>
       <c r="F8" t="n">
-        <v>1.443019358247917</v>
+        <v>0.377566431314073</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.736089351899065</v>
+        <v>-0.3768833460985067</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1597118009198298</v>
+        <v>1.022727518766359</v>
       </c>
       <c r="I8" t="n">
-        <v>1.64204047414607</v>
+        <v>1.062124756283405</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4064943464670319</v>
+        <v>-1.234743864139471</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.410147593437902</v>
+        <v>1.252836178683421</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2811489836278221</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.3669889980904975</v>
-      </c>
+        <v>0.4986923632373519</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.5103950531517431</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.05282830722445839</v>
-      </c>
+        <v>0.4787226355384476</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>-0.1267800259099407</v>
+        <v>-0.5428479616816253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.042115362490571</v>
+        <v>2.105090779111723</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8858686819544256</v>
+        <v>-1.472319026116054</v>
       </c>
       <c r="D9" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3134811473528777</v>
+        <v>-2.10600921615861</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4182517218349441</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>-1.458165473918372</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.1729365025868828</v>
+      </c>
       <c r="H9" t="n">
-        <v>-1.391419425592941</v>
+        <v>1.774069169816956</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09938838981990998</v>
+        <v>0.1368718406664856</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.648868622975691</v>
+        <v>1.664129447714067</v>
       </c>
       <c r="K9" t="n">
-        <v>2.116548755971258</v>
+        <v>0.8083530281461615</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.152126048150225</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-1.638667728552401</v>
-      </c>
+        <v>-1.101642567687367</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>-2.726830950137502</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-3.075636068664038</v>
-      </c>
+        <v>-1.749006637388495</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>0.5833769476911527</v>
+        <v>0.001370795757258655</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.757607451174561</v>
+        <v>0.8740069887057784</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.472319026116054</v>
+        <v>1.811782874080258</v>
       </c>
       <c r="D10" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.337782900956154</v>
+        <v>1.222971483052036</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9699605927938222</v>
+        <v>-0.1475969235322008</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1951342487586736</v>
+        <v>-1.022772859945979</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4553216308413756</v>
+        <v>1.749435017323494</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2259870441865293</v>
+        <v>0.8576891330650751</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4217551712054078</v>
+        <v>1.733150240853437</v>
       </c>
       <c r="K10" t="n">
-        <v>1.137829055468208</v>
+        <v>-1.543765329142122</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.569926300430548</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.3669889980904975</v>
-      </c>
+        <v>2.26641686964339</v>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>-1.929416347127918</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.9022154059018634</v>
-      </c>
+        <v>1.859974826538413</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1.636607390914947</v>
+        <v>0.3317876515251157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.115018874195642</v>
+        <v>0.6655169919434814</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.240840478084596</v>
+        <v>-1.255307887336562</v>
       </c>
       <c r="D11" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.10600921615861</v>
+        <v>0.9668960446512173</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9537807693497232</v>
+        <v>1.443019358247917</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.680511358436192</v>
+        <v>-1.736089351899065</v>
       </c>
       <c r="H11" t="n">
-        <v>2.673215735828328</v>
+        <v>-0.1597118009198298</v>
       </c>
       <c r="I11" t="n">
-        <v>1.724682026077359</v>
+        <v>1.64204047414607</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9586606915819915</v>
+        <v>-0.4064943464670319</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7379877945225739</v>
+        <v>-1.410147593437902</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8459331799444618</v>
+        <v>0.2811489836278221</v>
       </c>
       <c r="M11" t="n">
-        <v>1.369817361411947</v>
+        <v>0.3669889980904975</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2637738921848613</v>
+        <v>0.5103950531517431</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06331680299965177</v>
+        <v>0.02497969123278176</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8972588861823602</v>
+        <v>-0.1267800259099407</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.115018874195642</v>
+        <v>-1.042115362490571</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1914330378600514</v>
+        <v>0.8858686819544256</v>
       </c>
       <c r="D12" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1986697294487602</v>
+        <v>-0.3134811473528777</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07078783788902211</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1.179557554855823</v>
-      </c>
+        <v>-0.4182517218349441</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1.318337348687905</v>
+        <v>-1.391419425592941</v>
       </c>
       <c r="I12" t="n">
-        <v>2.108835147161262</v>
+        <v>0.09938838981990998</v>
       </c>
       <c r="J12" t="n">
-        <v>1.802171033992807</v>
+        <v>-1.648868622975691</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.619454430652961</v>
+        <v>2.116548755971258</v>
       </c>
       <c r="L12" t="n">
-        <v>2.735929721764679</v>
+        <v>-1.152126048150225</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6358393652309517</v>
+        <v>-1.638667728552401</v>
       </c>
       <c r="N12" t="n">
-        <v>2.726359697529305</v>
+        <v>-2.726830950137502</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.04873723345106813</v>
+        <v>-3.075636068664038</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5715494921119623</v>
+        <v>0.5833769476911527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.115018874195642</v>
+        <v>1.757607451174561</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5608722432421874</v>
+        <v>-1.472319026116054</v>
       </c>
       <c r="D13" t="n">
         <v>-0.3435988950344519</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.593858339356973</v>
+        <v>-1.337782900956154</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.133959693300594</v>
+        <v>-0.9699605927938222</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3526434699908486</v>
+        <v>0.1951342487586736</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.475322135305279</v>
+        <v>-0.4553216308413756</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5543250014346915</v>
+        <v>-0.2259870441865293</v>
       </c>
       <c r="J13" t="n">
-        <v>1.802171033992807</v>
+        <v>0.4217551712054078</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.05910125470119348</v>
+        <v>1.137829055468208</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7242771178521575</v>
+        <v>-1.569926300430548</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.638667728552401</v>
+        <v>0.03271287698334772</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6831943640068706</v>
+        <v>-1.929416347127918</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.141795411124376</v>
+        <v>-1.016886177632297</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2019020188649466</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.3570768017001661</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2.144533286875479</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.3435988950344519</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.222971483052036</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.017764912578611</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.916702409146755</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-2.056541542916422</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-0.6143788624025488</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-0.4064943464670316</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.7979074306940952</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1.373635099611363</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-0.301563244123802</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-1.394855387582703</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.360898492823596</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.1409792933935686</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>-0.4365015623715173</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2.144533286875479</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.3435988950344519</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-1.593858339356973</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.4595751541339473</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
-        <v>-0.2089801059067541</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.9429702720023043</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-2.062993381811911</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.1469128158046059</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-0.2820349487957776</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-1.304391607445251</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.8385582818982311</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.3059273929036111</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.01457507812330886</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1.360483647817805</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.9582057282142562</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-0.3435988950344519</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-0.8256320241545158</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.1171827823338121</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.074660221685341</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.14126463320411</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.6884329570906579</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.802171033992807</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.01198416624910162</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.3524960984508846</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-0.301563244123802</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.08233595902376178</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.4189600107521809</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.1799864768679914</v>
+        <v>1.636607390914947</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,670 +425,1928 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>referee</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_points</t>
+          <t>dif_mean_last_240_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_points</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_goal_ratio</t>
+          <t>dif_mean_last_240_matches_goal_attempts</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_dead_balls</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_dead_balls</t>
+          <t>dif_mean_last_240_matches_goals</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_120_matches_yellow_cards</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_480_matches_PPDA</t>
+          <t>dif_mean_last_240_matches_points</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_240_matches_attacks</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_KGP</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_240_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>zyC4c6ee</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.105090779111723</v>
+        <v>1.950189756754252</v>
       </c>
       <c r="C2" t="n">
-        <v>2.130065877623513</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3435988950344519</v>
+        <v>1.521691499507181</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.490122373759839</v>
+        <v>1.160259693904506</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5900387778401321</v>
+        <v>1.351735799130871</v>
       </c>
       <c r="G2" t="n">
-        <v>1.047496784531184</v>
+        <v>0.9769077327982321</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04967849527459998</v>
+        <v>0.9558619249364738</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4727100094631203</v>
+        <v>0.6451343278745145</v>
       </c>
       <c r="J2" t="n">
-        <v>1.526087861435327</v>
+        <v>0.8523647721473392</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4456319619401702</v>
+        <v>0.4199156974534262</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1846792379193768</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>-0.8598484008940118</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.2754440944396629</v>
+      </c>
       <c r="N2" t="n">
-        <v>0.7569298244699207</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>-0.2336998687853039</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.9846688038511103</v>
+      </c>
       <c r="P2" t="n">
-        <v>0.4124031924087511</v>
+        <v>-0.5010175497261287</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.5173018769455205</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.2750088375021772</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.5073409499486906</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1.649572184538582</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.7889866616393522</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4479953871795845</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.5339653424369157</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-1.408164849337843</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.5898572755978689</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.2450876029464632</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.3195381166528281</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1.141419019079597</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.5702772707388544</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>-0.3068738506534701</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-0.921659120881662</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>ABBmcc1C</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7747260378665893</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C3" t="n">
-        <v>2.130065877623513</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3435988950344519</v>
+        <v>0.2007562869948844</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.849933777757792</v>
+        <v>-0.2890835456079938</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2839729621335489</v>
+        <v>0.6978900504783463</v>
       </c>
       <c r="G3" t="n">
-        <v>1.170565780670074</v>
+        <v>-0.3480565480507335</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.179712305383732</v>
+        <v>-0.6155377712879541</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2367229032303907</v>
+        <v>-0.6054629513759648</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.234743864139471</v>
+        <v>-0.5199481661119107</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.13938516213256</v>
+        <v>-0.6573159922864854</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9690553461423925</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
+        <v>-1.243143527790144</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1952671431668551</v>
+      </c>
       <c r="N3" t="n">
-        <v>-0.3231272659783381</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>-0.32954721264769</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9092924220352084</v>
+      </c>
       <c r="P3" t="n">
-        <v>-0.3094773086056799</v>
+        <v>-0.8138646557956888</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.6754525539855121</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.2584577246309376</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.8397215550157497</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.5969377549367263</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.0362028190738403</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-0.4043896566895928</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.7186945550513103</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-1.309869403600213</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.7571800397613025</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.02892730853890171</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-0.272973369832849</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.4634613189563985</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-0.4544395209472928</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>-0.6191873522542879</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.9986027775311592</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>WQadeyWO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.115018874195642</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5608722432421874</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-2.507160898655322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4547451678495792</v>
+        <v>-1.925523821493926</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5091172518844762</v>
+        <v>-3.038371370393218</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.665907903404312</v>
+        <v>-1.612242650879105</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2533215803949851</v>
+        <v>-2.44883741688312</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3892135449256445</v>
+        <v>-2.754216458451789</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6702300265071396</v>
+        <v>-1.892261104371161</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2302913465233374</v>
+        <v>-2.266751433505044</v>
       </c>
       <c r="L4" t="n">
-        <v>1.328315692513218</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>-0.170141239782045</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.6789108695309641</v>
+      </c>
       <c r="N4" t="n">
-        <v>2.486685762961803</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>-0.6219654207111551</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-1.315010878133609</v>
+      </c>
       <c r="P4" t="n">
-        <v>-0.8626985257345556</v>
+        <v>-1.000083171313285</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.707950545518031</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-2.839479181189207</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-1.852170371766067</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.859664933367864</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.863917837450493</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1.987390452446637</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-5.504174402228561</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2.53796533957988</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-5.355206379808119</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-3.818467303585076</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-2.463607447076392</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-3.854929738232017</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.789914340231797</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-3.226033520902061</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-2.894246477159194</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>MiACepQ7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.4365015623715173</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C5" t="n">
-        <v>0.712259770930832</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-1.417389348332678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7108206062503982</v>
+        <v>-2.186405604606176</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7147629022227943</v>
+        <v>-1.834464912556825</v>
       </c>
       <c r="G5" t="n">
-        <v>1.210717202886448</v>
+        <v>-2.577747421720553</v>
       </c>
       <c r="H5" t="n">
-        <v>1.145898281233669</v>
+        <v>-0.9210877122204818</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9039142989816624</v>
+        <v>-1.872301753733594</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.717889416115061</v>
+        <v>-0.4415302839256679</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7262356646276392</v>
+        <v>-1.863081008643091</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6465354766163154</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-2.268834938790664</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.7825794159085901</v>
+      </c>
       <c r="N5" t="n">
-        <v>0.4998705025603173</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>-2.002126537525549</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-1.676814102347772</v>
+      </c>
       <c r="P5" t="n">
-        <v>0.3515779458002276</v>
+        <v>-1.86664256879643</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.26932448409487</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1.405462828008767</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.644020278186389</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.080876181013424</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.8377352729992493</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-2.089787357067284</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-5.559312541449758</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-2.135281396154042</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-4.242267781416358</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-4.003755179901685</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-3.115293539699238</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3.609175321683169</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-2.332586554882897</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>-3.238891731485797</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-2.192217987926521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rwXP4l3L</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7747260378665893</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1914330378600514</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3435988950344519</v>
+        <v>2.578439669517017</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6975943049541062</v>
+        <v>1.76634868497337</v>
       </c>
       <c r="F6" t="n">
-        <v>1.304401758060096</v>
+        <v>2.892943635240391</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9092653428564665</v>
+        <v>2.013335610623111</v>
       </c>
       <c r="H6" t="n">
-        <v>2.562362049607748</v>
+        <v>2.418136642256428</v>
       </c>
       <c r="I6" t="n">
-        <v>2.332976092950914</v>
+        <v>1.028092346400977</v>
       </c>
       <c r="J6" t="n">
-        <v>0.007630412369188048</v>
+        <v>1.558125711823525</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.098400129962572</v>
+        <v>0.5007080741839194</v>
       </c>
       <c r="L6" t="n">
-        <v>1.361390829131057</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>1.177894907662872</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.041426629816667</v>
+      </c>
       <c r="N6" t="n">
-        <v>1.948334061143572</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
+        <v>0.8060495269651106</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.62031441049087</v>
+      </c>
       <c r="P6" t="n">
-        <v>-0.2997815500513066</v>
+        <v>1.181578469084648</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.333338501750523</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.134342586223446</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.593317100118999</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1980926748665774</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.7583433302984984</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.1603154348737371</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.321295536750299</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.516645560615102</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.573003692459827</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5600509126475441</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.447627747662427</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8424543969732615</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.561687572045438</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0.8666888759368219</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.715454640736778</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.439239165847327</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.240840478084596</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-0.5257580798868782</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.593858339356973</v>
+        <v>0.8176876554742788</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3607820477767276</v>
+        <v>-0.8277500297108757</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4860384074601836</v>
+        <v>0.8188844699446857</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.576175569293908</v>
+        <v>0.824911950251105</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5316884024274262</v>
+        <v>1.384123629249798</v>
       </c>
       <c r="J7" t="n">
-        <v>1.250004688877847</v>
+        <v>0.5779021844954891</v>
       </c>
       <c r="K7" t="n">
-        <v>1.184769473442908</v>
+        <v>1.362493425975848</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6131617201301293</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>0.9780636361483129</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.2502274209964566</v>
+      </c>
       <c r="N7" t="n">
-        <v>0.3338504979143095</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>0.7118212260733729</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.4120758750947823</v>
+      </c>
       <c r="P7" t="n">
-        <v>-0.9569037669145777</v>
+        <v>1.052789743752679</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.9738330780029734</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.868789357927146</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.205697553089229</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.020725642179032</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.6699005952202586</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.4479953871795845</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.781341147411706</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.477766550710214</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.867949626041404</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.833208820205521</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.270674865588942</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.15253201483144</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.104239382622232</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>1.486130959004362</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.298541131358918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1.300245834672462</v>
+        <v>1.875974797046204</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3293936952107294</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-0.06343075550757485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7108206062503982</v>
+        <v>-1.211392879843221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.377566431314073</v>
+        <v>0.7290255623189428</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3768833460985067</v>
+        <v>0.04092379128107277</v>
       </c>
       <c r="H8" t="n">
-        <v>1.022727518766359</v>
+        <v>-0.6155377712879541</v>
       </c>
       <c r="I8" t="n">
-        <v>1.062124756283405</v>
+        <v>-1.003380267501118</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.234743864139471</v>
+        <v>-0.2454855784600608</v>
       </c>
       <c r="K8" t="n">
-        <v>1.252836178683421</v>
+        <v>-1.061277875938952</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4986923632373519</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>-0.6384418990223328</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5483005713717437</v>
+      </c>
       <c r="N8" t="n">
-        <v>0.4787226355384476</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>0.227403569255366</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.006357418996381924</v>
+      </c>
       <c r="P8" t="n">
-        <v>-0.5428479616816253</v>
+        <v>-0.7512952345817759</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.30805526214548</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.8865548075323055</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-1.533246471357593</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.5103574338872227</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.140869696145199</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.6174859176568872</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.711723284718549</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1.672534755610957</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-2.407119505953475</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.414330068431641</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-1.45937784001522</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-2.721714081350401</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2.067872177309182</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>-2.351286430530976</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1.731613951047311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.105090779111723</v>
+        <v>1.913082276900228</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.472319026116054</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3435988950344519</v>
+        <v>0.1347095263692696</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.10600921615861</v>
+        <v>0.3697088359885973</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.458165473918372</v>
+        <v>1.133787216246696</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1729365025868828</v>
+        <v>0.8431957411529239</v>
       </c>
       <c r="H9" t="n">
-        <v>1.774069169816956</v>
+        <v>-0.6155377712879541</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1368718406664856</v>
+        <v>0.3609076734994054</v>
       </c>
       <c r="J9" t="n">
-        <v>1.664129447714067</v>
+        <v>-0.5199481661119107</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8083530281461615</v>
+        <v>0.5545696586709149</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.101642567687367</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>1.109002965212209</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.5276108288717262</v>
+      </c>
       <c r="N9" t="n">
-        <v>-1.749006637388495</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>0.5563931008911245</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2926538833745466</v>
+      </c>
       <c r="P9" t="n">
-        <v>0.001370795757258655</v>
+        <v>0.1038201886750191</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.049142924212493</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.598416441446425</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.440423600043637</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.829337564069604</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.9849348249975332</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.4043896566895928</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.936096253335443</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-1.646930697283496</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-1.183755967753518</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.021931780901068</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.7807504117930105</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.7590717425682004</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1.16210092224453</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>-0.5772845588100326</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1.519085281395751</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8740069887057784</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C10" t="n">
-        <v>1.811782874080258</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-1.38436596801987</v>
       </c>
       <c r="E10" t="n">
-        <v>1.222971483052036</v>
+        <v>-0.3695255627292615</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1475969235322008</v>
+        <v>-1.979763967812942</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.022772859945979</v>
+        <v>-0.09854613301881807</v>
       </c>
       <c r="H10" t="n">
-        <v>1.749435017323494</v>
+        <v>0.4320620261949978</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8576891330650751</v>
+        <v>1.072970239197047</v>
       </c>
       <c r="J10" t="n">
-        <v>1.733150240853437</v>
+        <v>0.3034395968436392</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.543765329142122</v>
+        <v>1.328829935671476</v>
       </c>
       <c r="L10" t="n">
-        <v>2.26641686964339</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>1.105580687293493</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001939313435606664</v>
+      </c>
       <c r="N10" t="n">
-        <v>1.859974826538413</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>0.3839650245170682</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.359056488037941</v>
+      </c>
       <c r="P10" t="n">
-        <v>0.3317876515251157</v>
+        <v>0.02925829506177376</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.5581277409433132</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.461617202970147</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.4977530478794484</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.139225525055944</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.8225863373918942</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8635330960658085</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.4150254041136789</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1484985639200246</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.2319282922153475</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.03805613143445013</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.04119093915223152</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.1289585679549848</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.1622158224956579</v>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>-0.1229758672167943</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.2268769782763414</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6655169919434814</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.255307887336562</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-0.701882774888518</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9668960446512173</v>
+        <v>-0.1725813139151229</v>
       </c>
       <c r="F11" t="n">
-        <v>1.443019358247917</v>
+        <v>-0.0804977455365629</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.736089351899065</v>
+        <v>0.4203075761885751</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1597118009198298</v>
+        <v>0.5848369966612617</v>
       </c>
       <c r="I11" t="n">
-        <v>1.64204047414607</v>
+        <v>0.01983568824927495</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4064943464670319</v>
+        <v>-0.2454855784600608</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.410147593437902</v>
+        <v>-0.2533541086340185</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2811489836278221</v>
+        <v>0.5544451476881849</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3669889980904975</v>
+        <v>0.3129449525684847</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5103950531517431</v>
+        <v>0.3744126709902423</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02497969123278176</v>
+        <v>0.07242583385288097</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1267800259099407</v>
+        <v>0.8233685326350043</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.1181596920350653</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.9758125331653642</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.4268499202315963</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.595870764053879</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.7924976507745651</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.087284170081467</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6821534873415558</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.4615224639065361</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.186305285124631</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.8584155454290224</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.5292440231622469</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.606989482214616</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.2193100728205921</v>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="n">
+        <v>0.3182395621114664</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.7475441953662636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-1.042115362490571</v>
+        <v>1.875974797046204</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8858686819544256</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3435988950344519</v>
+        <v>-1.197233479580629</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3134811473528777</v>
+        <v>-0.1476165499809362</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4182517218349441</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>-1.377810738894745</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.6046044363271387</v>
+      </c>
       <c r="H12" t="n">
-        <v>-1.391419425592941</v>
+        <v>-1.270287644714799</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09938838981990998</v>
+        <v>0.6660773445126804</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.648868622975691</v>
+        <v>-1.617798516719311</v>
       </c>
       <c r="K12" t="n">
-        <v>2.116548755971258</v>
+        <v>0.6892236198884039</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.152126048150225</v>
+        <v>0.7530860616658001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.638667728552401</v>
+        <v>-0.7125331007885728</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.726830950137502</v>
+        <v>-0.2837282965783398</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.075636068664038</v>
+        <v>-0.2799390453817828</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5833769476911527</v>
+        <v>-0.4175916547742467</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.9948405614193128</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2781285250000318</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.127968470470271</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.062456877255524</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.368208850533195</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.939669213950645</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.3589615308226909</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.8880767327358683</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.5171692902565586</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.5760402440806595</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.4470615090119144</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.7483180527273112</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1.234402063816614</v>
+      </c>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>-0.3360518138295941</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-1.245082618895903</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.757607451174561</v>
+        <v>1.950189756754252</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.472319026116054</v>
+        <v>-0.2278352655724001</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3435988950344519</v>
+        <v>0.9021099831621269</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.337782900956154</v>
+        <v>0.09703813657409245</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9699605927938222</v>
+        <v>1.042604645856378</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1951342487586736</v>
+        <v>0.4260655088431575</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4553216308413756</v>
+        <v>0.6160155620625402</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2259870441865293</v>
+        <v>0.407580682007318</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4217551712054078</v>
+        <v>0.6563200666817319</v>
       </c>
       <c r="K13" t="n">
-        <v>1.137829055468208</v>
+        <v>0.06981539828795499</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.569926300430548</v>
+        <v>0.2277970353442944</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03271287698334772</v>
+        <v>0.3003366158468815</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.929416347127918</v>
+        <v>0.5812692199460286</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.016886177632297</v>
+        <v>0.3146766883267133</v>
       </c>
       <c r="P13" t="n">
-        <v>1.636607390914947</v>
+        <v>0.5412847253289528</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.135832673496831</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.018187725879955</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.09406472406251851</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.2273980386345969</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.1890442169597996</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.5429022263183342</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.187365841794539</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.532909301959682</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.78602666340496</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.279922749317613</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.050331746460752</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.045756135843209</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.675180452489813</v>
+      </c>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>2.39668103464272</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.478562406776484</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.8119607092645426</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.171171871282587</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.1961869198246</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.8464376078196104</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.6155377712879542</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.003380267501118</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-1.068873341415611</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.9266239147214634</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.4052806164733267</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.06638192334602287</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.05869929171380074</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-2.019740636602935</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.9598599719614822</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.009986818200433</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.246185449646085</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.216332770040093</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.240066726211679</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.9614551218726568</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.4043896566895928</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-3.313283141976441</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.46696678596902</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-2.70180787447614</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1.961212358267823</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.302052100571041</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.516217713719125</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-1.429565027865299</v>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>-1.783403331482945</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-1.709085819569995</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.913082276900228</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.01362379855564244</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.4448161206260149</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.1583365251380544</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.118979753469857</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2574620599478394</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.130242978574888</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5779021844954891</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.343257145801921</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.428740107092075</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2008708483764565</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.7062985119175769</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.393794130982873</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.1697968834588359</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.01875700581051341</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.08063553725323262</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.3479016352507462</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.4036995235480447</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.711475550030912</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.178611139067451</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5984492437735583</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.8932167088337826</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.7138265512714098</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.5866366344779197</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.54114188812764</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.189865996622321</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.7855568888410249</v>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>0.3867461645787563</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.102817511285123</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8392083063758274</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.07706632542674331</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.04923355379925571</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.8579534731287757</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9122119333746842</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4506634590915451</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8523647721473392</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.285261736235937</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.753460196029596</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.4883848924045164</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1.114297340520978</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.03768819090795187</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-1.21013765681713</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.3321982023147537</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.1118324122317774</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.1481497298361585</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.4631100010707354</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.913284870810101</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8741879091141732</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.3009617577800062</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.08102596858034887</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7475147089372703</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.1965041735377646</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.1726408418777961</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9199738014378064</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.6149683963589642</v>
+      </c>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>0.3997011546678839</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.4260312817639359</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.318833591871363</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.904033140610399</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.913657655682586</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.814250727020723</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.03873431136430512</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.439609023979484</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.08864981408757518</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.472664848790158</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.314120363946752</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.044228482421468</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.548304037498274</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.87561429276436</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.514002219821894</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.348977005700252</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.36485282912047</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.681203087442455</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1.328639114783656</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.048220853523926</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.707200565622688</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.733899997345816</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.9815446454379616</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.967918451398497</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.627693894842722</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.679047975778906</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.571665406742679</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.766175831649412</v>
+      </c>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="n">
+        <v>2.583276890022335</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.018974361456725</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.261571037384419</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.1975460778493096</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.002658965935071951</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.01782808363324665</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.50641279238348</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.7179568693181135</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.5199481661119107</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.6303852000429876</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.1721105812953726</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.301737542149282</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2905557688928346</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1605170536615476</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.2804603399470906</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.7915039766536091</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.47834163181349</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8804585540902063</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.4909523732642342</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.255405774662167</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.6068311046085225</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.6097152202644555</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.344313039769818</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5392578887204068</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.1731052652305627</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1003450258662415</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8776663762467199</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.7437044326109541</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>0.3799803472577127</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.8666132033309355</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.913082276900228</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.7841693391878151</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8509740073865276</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.04923355379925516</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2936760729796751</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6939619755657359</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5583704018021126</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.126827359799189</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.4199156974534262</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.1173628872248733</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1896634379572537</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.3444424079776555</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.1164714437572143</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4375237684825469</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.6095712429158747</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.258230347242647</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.5558114008979275</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.829359112878775</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.264509345685196</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4479953871795845</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.208063439530801</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.91436372838701</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.926036576315097</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.778543924575275</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.683323090365928</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.973674362829557</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.842311326607721</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>2.582491504063506</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.537891859378797</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -655,32 +655,34 @@
         <v>0.4479953871795845</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5339653424369157</v>
+        <v>-0.5183745331777659</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.408164849337843</v>
+        <v>-1.446849244866611</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.5898572755978689</v>
+        <v>-0.4711724503485395</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.2450876029464632</v>
+        <v>-0.2439705806388603</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.3195381166528281</v>
+        <v>-0.3259296276759515</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.141419019079597</v>
+        <v>-1.180322398565654</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.5702772707388544</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-0.6074941701079993</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.4853957738244215</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-0.3068738506534701</v>
+        <v>-0.3201626110450043</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.921659120881662</v>
+        <v>-0.9793350684693459</v>
       </c>
     </row>
     <row r="3">
@@ -753,32 +755,34 @@
         <v>-0.4043896566895928</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.7186945550513103</v>
+        <v>-0.7179283394868706</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.309869403600213</v>
+        <v>-1.318645789291139</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.7571800397613025</v>
+        <v>-0.8360387692936996</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.02892730853890171</v>
+        <v>-0.0268900596500754</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.272973369832849</v>
+        <v>-0.2893582870057633</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.4634613189563985</v>
+        <v>-0.5070949957208727</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.4544395209472928</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>-0.4818916498899167</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.1580135454674385</v>
+      </c>
       <c r="AE3" t="n">
-        <v>-0.6191873522542879</v>
+        <v>-0.6301239652133207</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.9986027775311592</v>
+        <v>-0.9686519822568517</v>
       </c>
     </row>
     <row r="4">
@@ -851,32 +855,34 @@
         <v>-1.987390452446637</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.504174402228561</v>
+        <v>-5.121384010245507</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.53796533957988</v>
+        <v>-2.469066990473364</v>
       </c>
       <c r="Y4" t="n">
-        <v>-5.355206379808119</v>
+        <v>-5.161919148074234</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.818467303585076</v>
+        <v>-3.694325169418027</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.463607447076392</v>
+        <v>-2.550327642556798</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.854929738232017</v>
+        <v>-3.978447968100245</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.789914340231797</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>-2.846468133935089</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1.186984761976708</v>
+      </c>
       <c r="AE4" t="n">
-        <v>-3.226033520902061</v>
+        <v>-3.34155198006079</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2.894246477159194</v>
+        <v>-2.910970594265658</v>
       </c>
     </row>
     <row r="5">
@@ -949,32 +955,34 @@
         <v>-2.089787357067284</v>
       </c>
       <c r="W5" t="n">
-        <v>-5.559312541449758</v>
+        <v>-5.140190265711142</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.135281396154042</v>
+        <v>-2.078253821138245</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.242267781416358</v>
+        <v>-3.961929704302076</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4.003755179901685</v>
+        <v>-3.837777990163135</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.115293539699238</v>
+        <v>-3.232150579247008</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.609175321683169</v>
+        <v>-3.782052214274332</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.332586554882897</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-2.422019691178328</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.7163678546523053</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-3.238891731485797</v>
+        <v>-3.472814538852241</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2.192217987926521</v>
+        <v>-2.249067268128713</v>
       </c>
     </row>
     <row r="6">
@@ -1047,326 +1055,334 @@
         <v>0.1603154348737371</v>
       </c>
       <c r="W6" t="n">
-        <v>1.321295536750299</v>
+        <v>1.354272410949687</v>
       </c>
       <c r="X6" t="n">
-        <v>1.516645560615102</v>
+        <v>1.482003213790161</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.573003692459827</v>
+        <v>1.628284348482203</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5600509126475441</v>
+        <v>0.5629985854107241</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.447627747662427</v>
+        <v>0.4459557568381959</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8424543969732615</v>
+        <v>0.8657301120862257</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.561687572045438</v>
-      </c>
-      <c r="AD6" t="inlineStr"/>
+        <v>1.544006233733048</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.241247812926144</v>
+      </c>
       <c r="AE6" t="n">
-        <v>0.8666888759368219</v>
+        <v>0.8669745098937077</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.715454640736778</v>
+        <v>1.732587755867881</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>Mku6FvHt</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.801759837338154</v>
+        <v>1.913082276900228</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5257580798868782</v>
+        <v>0.1347095263692696</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8176876554742788</v>
+        <v>0.3697088359885973</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8277500297108757</v>
+        <v>1.133787216246696</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8188844699446857</v>
+        <v>0.8431957411529239</v>
       </c>
       <c r="H7" t="n">
-        <v>0.824911950251105</v>
+        <v>-0.6155377712879541</v>
       </c>
       <c r="I7" t="n">
-        <v>1.384123629249798</v>
+        <v>0.3609076734994054</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5779021844954891</v>
+        <v>-0.5199481661119107</v>
       </c>
       <c r="K7" t="n">
-        <v>1.362493425975848</v>
+        <v>0.5545696586709149</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9780636361483129</v>
+        <v>1.109002965212209</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2502274209964566</v>
+        <v>-0.5276108288717262</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7118212260733729</v>
+        <v>0.5563931008911245</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4120758750947823</v>
+        <v>0.2926538833745466</v>
       </c>
       <c r="P7" t="n">
-        <v>1.052789743752679</v>
+        <v>0.1038201886750191</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9738330780029734</v>
+        <v>1.049142924212493</v>
       </c>
       <c r="R7" t="n">
-        <v>0.868789357927146</v>
+        <v>0.598416441446425</v>
       </c>
       <c r="S7" t="n">
-        <v>1.205697553089229</v>
+        <v>1.440423600043637</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.020725642179032</v>
+        <v>-0.829337564069604</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6699005952202586</v>
+        <v>0.9849348249975332</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4479953871795845</v>
+        <v>-0.4043896566895928</v>
       </c>
       <c r="W7" t="n">
-        <v>2.781341147411706</v>
+        <v>-0.9399804624154515</v>
       </c>
       <c r="X7" t="n">
-        <v>1.477766550710214</v>
+        <v>-1.676060881106925</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.867949626041404</v>
+        <v>-1.183755967753518</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.833208820205521</v>
+        <v>-1.021873093446294</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.270674865588942</v>
+        <v>-0.7789331593546177</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.15253201483144</v>
+        <v>-0.7590717425682004</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.104239382622232</v>
-      </c>
-      <c r="AD7" t="inlineStr"/>
+        <v>-1.167753893533371</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.7294733369960206</v>
+      </c>
       <c r="AE7" t="n">
-        <v>1.486130959004362</v>
+        <v>-0.5784490859732719</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.298541131358918</v>
+        <v>-1.540642223217389</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.875974797046204</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06343075550757485</v>
+        <v>-0.5257580798868782</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.211392879843221</v>
+        <v>0.8176876554742788</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7290255623189428</v>
+        <v>-0.8277500297108757</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04092379128107277</v>
+        <v>0.8188844699446857</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6155377712879541</v>
+        <v>0.824911950251105</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.003380267501118</v>
+        <v>1.384123629249798</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2454855784600608</v>
+        <v>0.5779021844954891</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.061277875938952</v>
+        <v>1.362493425975848</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6384418990223328</v>
+        <v>0.9780636361483129</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5483005713717437</v>
+        <v>-0.2502274209964566</v>
       </c>
       <c r="N8" t="n">
-        <v>0.227403569255366</v>
+        <v>0.7118212260733729</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006357418996381924</v>
+        <v>-0.4120758750947823</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7512952345817759</v>
+        <v>1.052789743752679</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.30805526214548</v>
+        <v>0.9738330780029734</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.8865548075323055</v>
+        <v>0.868789357927146</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.533246471357593</v>
+        <v>1.205697553089229</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5103574338872227</v>
+        <v>-1.020725642179032</v>
       </c>
       <c r="U8" t="n">
-        <v>1.140869696145199</v>
+        <v>-0.6699005952202586</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6174859176568872</v>
+        <v>0.4479953871795845</v>
       </c>
       <c r="W8" t="n">
-        <v>-2.711723284718549</v>
+        <v>2.71670098129261</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.672534755610957</v>
+        <v>1.435293046933131</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.407119505953475</v>
+        <v>1.814591447154707</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.414330068431641</v>
+        <v>1.835002699370185</v>
       </c>
       <c r="AA8" t="n">
-        <v>-1.45937784001522</v>
+        <v>1.267147577617848</v>
       </c>
       <c r="AB8" t="n">
-        <v>-2.721714081350401</v>
+        <v>1.144331359269323</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.067872177309182</v>
-      </c>
-      <c r="AD8" t="inlineStr"/>
+        <v>1.078626425914686</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3412252977173532</v>
+      </c>
       <c r="AE8" t="n">
-        <v>-2.351286430530976</v>
+        <v>1.485567557730715</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.731613951047311</v>
+        <v>1.276657569206644</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.913082276900228</v>
+        <v>1.875974797046204</v>
       </c>
       <c r="C9" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1347095263692696</v>
+        <v>-0.06343075550757485</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3697088359885973</v>
+        <v>-1.211392879843221</v>
       </c>
       <c r="F9" t="n">
-        <v>1.133787216246696</v>
+        <v>0.7290255623189428</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8431957411529239</v>
+        <v>0.04092379128107277</v>
       </c>
       <c r="H9" t="n">
         <v>-0.6155377712879541</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3609076734994054</v>
+        <v>-1.003380267501118</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5199481661119107</v>
+        <v>-0.2454855784600608</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5545696586709149</v>
+        <v>-1.061277875938952</v>
       </c>
       <c r="L9" t="n">
-        <v>1.109002965212209</v>
+        <v>-0.6384418990223328</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5276108288717262</v>
+        <v>0.5483005713717437</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5563931008911245</v>
+        <v>0.227403569255366</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2926538833745466</v>
+        <v>0.006357418996381924</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1038201886750191</v>
+        <v>-0.7512952345817759</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.049142924212493</v>
+        <v>-1.30805526214548</v>
       </c>
       <c r="R9" t="n">
-        <v>0.598416441446425</v>
+        <v>-0.8865548075323055</v>
       </c>
       <c r="S9" t="n">
-        <v>1.440423600043637</v>
+        <v>-1.533246471357593</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.829337564069604</v>
+        <v>-0.5103574338872227</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9849348249975332</v>
+        <v>1.140869696145199</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4043896566895928</v>
+        <v>-0.6174859176568872</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.936096253335443</v>
+        <v>-2.701462339988562</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.646930697283496</v>
+        <v>-1.665622545396872</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.183755967753518</v>
+        <v>-2.454994606148681</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.021931780901068</v>
+        <v>-1.458895514359248</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.7807504117930105</v>
+        <v>-1.464749555216472</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.7590717425682004</v>
+        <v>-2.714154447382088</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.16210092224453</v>
-      </c>
-      <c r="AD9" t="inlineStr"/>
+        <v>-2.070960541815229</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.4119183452429304</v>
+      </c>
       <c r="AE9" t="n">
-        <v>-0.5772845588100326</v>
+        <v>-2.357386712469199</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1.519085281395751</v>
+        <v>-1.725734785095956</v>
       </c>
     </row>
     <row r="10">
@@ -1439,32 +1455,34 @@
         <v>0.8635330960658085</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4150254041136789</v>
+        <v>-0.3782866279434894</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1484985639200246</v>
+        <v>-0.1101268988014108</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.2319282922153475</v>
+        <v>-0.1313873504256737</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.03805613143445013</v>
+        <v>-0.02606611888458909</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04119093915223152</v>
+        <v>0.04013655723175022</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.1289585679549848</v>
+        <v>-0.1216641843013496</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.1622158224956579</v>
-      </c>
-      <c r="AD10" t="inlineStr"/>
+        <v>-0.1731424922392659</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.1649257758882625</v>
+      </c>
       <c r="AE10" t="n">
-        <v>-0.1229758672167943</v>
+        <v>-0.1158767643722872</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2268769782763414</v>
+        <v>-0.1967990034042646</v>
       </c>
     </row>
     <row r="11">
@@ -1557,7 +1575,9 @@
       <c r="AC11" t="n">
         <v>0.2193100728205921</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>0.6479032209443636</v>
+      </c>
       <c r="AE11" t="n">
         <v>0.3182395621114664</v>
       </c>
@@ -1635,32 +1655,34 @@
         <v>1.939669213950645</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3589615308226909</v>
+        <v>-0.3556962072980042</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8880767327358683</v>
+        <v>-0.8505910789294349</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.5171692902565586</v>
+        <v>-0.4383105607241616</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0.5760402440806595</v>
+        <v>-0.5685383790613868</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.4470615090119144</v>
+        <v>-0.4297449905685842</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.7483180527273112</v>
+        <v>-0.704684375962837</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.234402063816614</v>
-      </c>
-      <c r="AD12" t="inlineStr"/>
+        <v>-1.208936602100101</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.1557712110158144</v>
+      </c>
       <c r="AE12" t="n">
-        <v>-0.3360518138295941</v>
+        <v>-0.3265660561059912</v>
       </c>
       <c r="AF12" t="n">
-        <v>-1.245082618895903</v>
+        <v>-1.297824576179278</v>
       </c>
     </row>
     <row r="13">
@@ -1733,32 +1755,34 @@
         <v>-0.5429022263183342</v>
       </c>
       <c r="W13" t="n">
-        <v>4.187365841794539</v>
+        <v>3.76756703652297</v>
       </c>
       <c r="X13" t="n">
-        <v>1.532909301959682</v>
+        <v>1.4699440315626</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.78602666340496</v>
+        <v>3.537458775648699</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.279922749317613</v>
+        <v>3.143293828479285</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.050331746460752</v>
+        <v>2.137792331494973</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.045756135843209</v>
+        <v>3.145998650598474</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.675180452489813</v>
-      </c>
-      <c r="AD13" t="inlineStr"/>
+        <v>1.751402251731605</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.019401584598228</v>
+      </c>
       <c r="AE13" t="n">
-        <v>2.39668103464272</v>
+        <v>2.513364715079993</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.478562406776484</v>
+        <v>1.500944570760913</v>
       </c>
     </row>
     <row r="14">
@@ -1831,32 +1855,34 @@
         <v>-0.4043896566895928</v>
       </c>
       <c r="W14" t="n">
-        <v>-3.313283141976441</v>
+        <v>-3.271474306625823</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.46696678596902</v>
+        <v>-1.469396122772627</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.70180787447614</v>
+        <v>-2.601223983610761</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.961212358267823</v>
+        <v>-1.950142878825982</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.302052100571041</v>
+        <v>-1.296138865882982</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.516217713719125</v>
+        <v>-1.503397281843039</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1.429565027865299</v>
-      </c>
-      <c r="AD14" t="inlineStr"/>
+        <v>-1.420739409218388</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.9654683830236555</v>
+      </c>
       <c r="AE14" t="n">
-        <v>-1.783403331482945</v>
+        <v>-1.796374958303987</v>
       </c>
       <c r="AF14" t="n">
-        <v>-1.709085819569995</v>
+        <v>-1.733018707513565</v>
       </c>
     </row>
     <row r="15">
@@ -1929,32 +1955,34 @@
         <v>1.178611139067451</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5984492437735583</v>
+        <v>0.5821543505464121</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8932167088337826</v>
+        <v>0.9036334355757883</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.7138265512714098</v>
+        <v>0.6153783857391522</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5866366344779197</v>
+        <v>0.5884747458861008</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.54114188812764</v>
+        <v>0.5504682766613814</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.189865996622321</v>
+        <v>1.233146006300559</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.7855568888410249</v>
-      </c>
-      <c r="AD15" t="inlineStr"/>
+        <v>0.8448257944200047</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.4196413731379282</v>
+      </c>
       <c r="AE15" t="n">
-        <v>0.3867461645787563</v>
+        <v>0.4026003751378084</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.102817511285123</v>
+        <v>1.181096553711183</v>
       </c>
     </row>
     <row r="16">
@@ -2027,32 +2055,34 @@
         <v>0.8741879091141732</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3009617577800062</v>
+        <v>0.3328501343000003</v>
       </c>
       <c r="X16" t="n">
-        <v>0.08102596858034887</v>
+        <v>0.1327311063485522</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.7475147089372703</v>
+        <v>0.7454644157817253</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1965041735377646</v>
+        <v>0.1947102943731006</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1726408418777961</v>
+        <v>0.1706679519956585</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9199738014378064</v>
+        <v>0.9182717785852912</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6149683963589642</v>
-      </c>
-      <c r="AD16" t="inlineStr"/>
+        <v>0.6369210692074914</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.02628229999105549</v>
+      </c>
       <c r="AE16" t="n">
-        <v>0.3997011546678839</v>
+        <v>0.4116965248389085</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.4260312817639359</v>
+        <v>0.4584302842952783</v>
       </c>
     </row>
     <row r="17">
@@ -2125,32 +2155,34 @@
         <v>1.707200565622688</v>
       </c>
       <c r="W17" t="n">
-        <v>4.733899997345816</v>
+        <v>4.314777721607199</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9815446454379616</v>
+        <v>0.9245170704221639</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.967918451398497</v>
+        <v>2.687580374284215</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.627693894842722</v>
+        <v>3.461716705104173</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.679047975778906</v>
+        <v>2.795905015326675</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.571665406742679</v>
+        <v>2.744542299333842</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.766175831649412</v>
-      </c>
-      <c r="AD17" t="inlineStr"/>
+        <v>1.855608967944842</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.922917289034664</v>
+      </c>
       <c r="AE17" t="n">
-        <v>2.583276890022335</v>
+        <v>2.817199697388779</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.018974361456725</v>
+        <v>1.075823641658918</v>
       </c>
     </row>
     <row r="18">
@@ -2223,32 +2255,34 @@
         <v>-0.6068311046085225</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6097152202644555</v>
+        <v>0.5827375738137778</v>
       </c>
       <c r="X18" t="n">
-        <v>1.344313039769818</v>
+        <v>1.341011340625479</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5392578887204068</v>
+        <v>0.4636557060367985</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1731052652305627</v>
+        <v>0.1692295984067585</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1003450258662415</v>
+        <v>0.09887758711093253</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8776663762467199</v>
+        <v>0.8689131158623573</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.7437044326109541</v>
-      </c>
-      <c r="AD18" t="inlineStr"/>
+        <v>0.737744430932619</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.5020324569899608</v>
+      </c>
       <c r="AE18" t="n">
-        <v>0.3799803472577127</v>
+        <v>0.3687761363220225</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.8666132033309355</v>
+        <v>0.8025146860559803</v>
       </c>
     </row>
     <row r="19">
@@ -2321,32 +2355,34 @@
         <v>0.4479953871795845</v>
       </c>
       <c r="W19" t="n">
-        <v>3.208063439530801</v>
+        <v>3.201686703880821</v>
       </c>
       <c r="X19" t="n">
-        <v>2.91436372838701</v>
+        <v>2.936581701996354</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.926036576315097</v>
+        <v>2.973911676510303</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.778543924575275</v>
+        <v>1.823050683048108</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.683323090365928</v>
+        <v>1.686877553128787</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.973674362829557</v>
+        <v>2.966114728861243</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.842311326607721</v>
-      </c>
-      <c r="AD19" t="inlineStr"/>
+        <v>2.851052662402611</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.6157176981296515</v>
+      </c>
       <c r="AE19" t="n">
-        <v>2.582491504063506</v>
+        <v>2.589756313164968</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.537891859378797</v>
+        <v>2.553569635249079</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -855,34 +855,34 @@
         <v>-1.987390452446637</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.121384010245507</v>
+        <v>-5.121902984687507</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.469066990473364</v>
+        <v>-2.501496028824828</v>
       </c>
       <c r="Y4" t="n">
         <v>-5.161919148074234</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.694325169418027</v>
+        <v>-3.680337369047125</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.550327642556798</v>
+        <v>-2.553219040400591</v>
       </c>
       <c r="AB4" t="n">
         <v>-3.978447968100245</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.846468133935089</v>
+        <v>-2.826627950570331</v>
       </c>
       <c r="AD4" t="n">
         <v>-1.186984761976708</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3.34155198006079</v>
+        <v>-3.34125708902963</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2.910970594265658</v>
+        <v>-2.907543104105816</v>
       </c>
     </row>
     <row r="5">
@@ -1355,25 +1355,25 @@
         <v>-0.6174859176568872</v>
       </c>
       <c r="W9" t="n">
-        <v>-2.701462339988562</v>
+        <v>-2.70224268641485</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.665622545396872</v>
+        <v>-1.669107409001998</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.454994606148681</v>
+        <v>-2.541711461719501</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.458895514359248</v>
+        <v>-1.460398017966524</v>
       </c>
       <c r="AA9" t="n">
-        <v>-1.464749555216472</v>
+        <v>-1.453621477988713</v>
       </c>
       <c r="AB9" t="n">
         <v>-2.714154447382088</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.070960541815229</v>
+        <v>-2.060530538878146</v>
       </c>
       <c r="AD9" t="n">
         <v>-0.4119183452429304</v>
@@ -1382,7 +1382,7 @@
         <v>-2.357386712469199</v>
       </c>
       <c r="AF9" t="n">
-        <v>-1.725734785095956</v>
+        <v>-1.765796358392804</v>
       </c>
     </row>
     <row r="10">
@@ -1676,7 +1676,7 @@
         <v>-1.208936602100101</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.1557712110158144</v>
+        <v>-0.1661303238977951</v>
       </c>
       <c r="AE12" t="n">
         <v>-0.3265660561059912</v>
@@ -1776,7 +1776,7 @@
         <v>1.751402251731605</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.019401584598228</v>
+        <v>2.648175645574267</v>
       </c>
       <c r="AE13" t="n">
         <v>2.513364715079993</v>
@@ -1876,7 +1876,7 @@
         <v>-1.420739409218388</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.9654683830236555</v>
+        <v>-1.196741600853922</v>
       </c>
       <c r="AE14" t="n">
         <v>-1.796374958303987</v>
@@ -1955,34 +1955,34 @@
         <v>1.178611139067451</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5821543505464121</v>
+        <v>0.5826733249884127</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9036334355757883</v>
+        <v>0.9360624739272519</v>
       </c>
       <c r="Y15" t="n">
         <v>0.6153783857391522</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5884747458861008</v>
+        <v>0.5744869455151985</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.5504682766613814</v>
+        <v>0.5533596745051754</v>
       </c>
       <c r="AB15" t="n">
         <v>1.233146006300559</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.8448257944200047</v>
+        <v>0.8249856110552464</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4196413731379282</v>
+        <v>0.3965140513549014</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.4026003751378084</v>
+        <v>0.4023054841066479</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.181096553711183</v>
+        <v>1.177669063551341</v>
       </c>
     </row>
     <row r="16">
@@ -2055,34 +2055,34 @@
         <v>0.8741879091141732</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3328501343000003</v>
+        <v>0.3336304807262893</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1327311063485522</v>
+        <v>0.1362159699536785</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.7454644157817253</v>
+        <v>0.8321812713525458</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.1947102943731006</v>
+        <v>0.1962127979803765</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1706679519956585</v>
+        <v>0.159539874767899</v>
       </c>
       <c r="AB16" t="n">
         <v>0.9182717785852912</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6369210692074914</v>
+        <v>0.6264910662704074</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.02628229999105549</v>
+        <v>-0.04796416416264303</v>
       </c>
       <c r="AE16" t="n">
         <v>0.4116965248389085</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.4584302842952783</v>
+        <v>0.4984918575921266</v>
       </c>
     </row>
     <row r="17">
@@ -2276,7 +2276,7 @@
         <v>0.737744430932619</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.5020324569899608</v>
+        <v>0.1334407660729727</v>
       </c>
       <c r="AE18" t="n">
         <v>0.3687761363220225</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.913082276900228</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C19" t="n">
         <v>-0.2278352655724001</v>
@@ -2376,7 +2376,7 @@
         <v>2.851052662402611</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.6157176981296515</v>
+        <v>0.5781358002322331</v>
       </c>
       <c r="AE19" t="n">
         <v>2.589756313164968</v>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,201 +588,1801 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.801759837338154</v>
+        <v>1.838867317192179</v>
       </c>
       <c r="C2" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.701882774888518</v>
+        <v>0.5970368507485735</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1725813139151229</v>
+        <v>0.2601412609441115</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0804977455365629</v>
+        <v>0.8847031215219247</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4203075761885751</v>
+        <v>0.3576100872831192</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5848369966612617</v>
+        <v>-0.09173787254647825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01983568824927495</v>
+        <v>-0.2973014208429523</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.2454855784600608</v>
+        <v>-0.5199481661119107</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.2533541086340185</v>
+        <v>-0.6303852000429876</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5544451476881849</v>
+        <v>-0.3792840581218424</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3129449525684847</v>
+        <v>0.884522883947828</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3744126709902423</v>
+        <v>0.1482092388053634</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07242583385288097</v>
+        <v>-0.235893435477449</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8233685326350043</v>
+        <v>-0.2726391622953514</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1181596920350653</v>
+        <v>0.4086128638199454</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.9758125331653642</v>
+        <v>1.089247274442196</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4268499202315963</v>
+        <v>0.3449170117617177</v>
       </c>
       <c r="T2" t="n">
-        <v>1.595870764053879</v>
+        <v>1.280488154136713</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7924976507745651</v>
+        <v>0.9090309147252592</v>
       </c>
       <c r="V2" t="n">
-        <v>1.087284170081467</v>
+        <v>0.4586502002279492</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7133523979151684</v>
+        <v>0.3847994795985078</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3794445863499405</v>
+        <v>0.2184403731427309</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.311408118098955</v>
+        <v>0.6809145067399064</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9167734679184268</v>
+        <v>0.1986138257408913</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5140871595335484</v>
+        <v>0.0444756303459333</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5555861816493747</v>
+        <v>0.6747498855183129</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1791387584780763</v>
+        <v>0.2726475726888897</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4308436696265817</v>
+        <v>0.1470693664093991</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.2921439556687713</v>
+        <v>0.1606652956456772</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.7348956062791751</v>
+        <v>0.2329119529989892</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.875974797046204</v>
+        <v>1.838867317192179</v>
       </c>
       <c r="C3" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.197233479580629</v>
+        <v>1.719831781384025</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1476165499809362</v>
+        <v>0.6332257886272336</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.377810738894745</v>
+        <v>1.974446035942798</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6046044363271387</v>
+        <v>0.2961921389675706</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.270287644714799</v>
+        <v>0.693961975565736</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6660773445126804</v>
+        <v>-0.0370096426257471</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.617798516719311</v>
+        <v>1.126827359799189</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6892236198884039</v>
+        <v>-0.1187001474165297</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7530860616658001</v>
+        <v>-0.3871064076503342</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7125331007885728</v>
+        <v>-0.6116664070157473</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2837282965783398</v>
+        <v>-0.7344004720509747</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2799390453817828</v>
+        <v>1.944364254787034</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4175916547742467</v>
+        <v>0.09339195180603209</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9948405614193128</v>
+        <v>0.1454247696982551</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2781285250000318</v>
+        <v>0.8022360246395838</v>
       </c>
       <c r="S3" t="n">
-        <v>1.127968470470271</v>
+        <v>0.116938007004183</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.062456877255524</v>
+        <v>-0.7199729480070733</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.368208850533195</v>
+        <v>-0.3016560865322989</v>
       </c>
       <c r="V3" t="n">
-        <v>1.939669213950645</v>
+        <v>0.2348991262122902</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3556962072980042</v>
+        <v>0.5597271337833217</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8505910789294349</v>
+        <v>0.02219448810023416</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.4383105607241616</v>
+        <v>0.7701367821297659</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.5685383790613868</v>
+        <v>0.1750800223181159</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.4297449905685842</v>
+        <v>0.05403918069871457</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.704684375962837</v>
+        <v>0.4429211104900418</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.208936602100101</v>
+        <v>0.3956403345963115</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.2889942208701244</v>
+        <v>0.2354178005600061</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.3265660561059912</v>
+        <v>0.3397243038127616</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.297824576179278</v>
+        <v>0.4598928496696034</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3276177980100343</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.02556659296935735</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4176704439129793</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.09278820036423563</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.877437720658692</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.8896896057510738</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0.5199481661119107</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.7919699535039743</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1230468224687414</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1784560275380509</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.08159718515582839</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1825398586137147</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.6878014533381942</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.7704964932372687</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.2843678999957407</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5317035483699143</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.535672258282618</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.06601366349786</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1.043678439591476</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.3889228593540983</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1934046319938447</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.3884076154839165</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.5758609873739651</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.06245546075189036</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7144711201412915</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3698678424903083</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.1285484260003767</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.4644802257345393</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.04050394908388528</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.13470952636927</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.5225486685190066</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.3918528639425269</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2062404354970907</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.47966182367795</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.151057772662208</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.675752535102889</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.490735293802029</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.6093419085209569</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.4267441350989009</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.01776063374169065</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.5662355097599475</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5805395884000599</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.1430119412842074</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.7284906409743452</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.2862398164611</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.7281752942117634</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.5893636088599814</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.9655148781001565</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.165965440960421</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.851745508843042</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.409566355050921</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.7192803515328684</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.7212129282791081</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.246762189120679</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.255072576611924</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.08188079454534068</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.9419523383324091</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.903095130238806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.9220386436405671</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.3417869361357209</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.325918219160418</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.5060798109042798</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.4845877966025851</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.2643909661258342</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02897700919178917</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.285261736235937</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.7148245694068689</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.6116664070157473</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1065767052744038</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.4247907130875461</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.08296371493704791</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.6575317239229904</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.2896545996094824</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7912871192075428</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.2551733297413196</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.4351064166290058</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.6610916481468788</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.03993793799848386</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1367733858281446</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0.1201452996168724</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.2390548904864425</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-0.2229317319283217</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0.01516618295826995</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.6827226357367364</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.02731476971351204</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-0.08861570527927921</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.5074987607509247</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8559918830149522</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2379503596692792</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.357053731001014</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.1657220139889491</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3011120515096288</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4177530043744275</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-0.2454855784600608</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1506077750184482</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.1294790264402012</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3970005307125058</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.2431365763856548</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.5442127048077799</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1976743204958853</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.01272590734173736</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.5766658494120944</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1096205678171668</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.05469308243585117</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.044112028610673</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8741879091141732</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5112180707561453</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.3801230526644901</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.9621571577248372</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.8214696394519959</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.5602647890926571</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5012761797191251</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3615689916685059</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6093060611531963</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.3417981881318547</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.7370807830044591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3328498082461139</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.6580072793020848</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.9834275889138576</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.745954642524413</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.03921210213889102</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.2075456352508126</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.02897700919178917</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.3880080698515076</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.376803674081342</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.3258774413260755</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1.042481220180073</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.1037566057644509</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.3028810492154094</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.5700187692921851</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2677295666738505</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.823741718233679</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.9296100109360949</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-1.934345961290862</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.02180286524499585</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.567898416390733</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.602559485619333</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5719772031593666</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.519104610907877</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5453747325103779</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.222690723063681</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.122805690880799</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5520556150429806</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.4003910391748984</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.222111973991286</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.644486430142631</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.739996989709506</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.721698320117111</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.912891674315391</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.47966182367795</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.123112930625081</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3034395968436392</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.093185503540871</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.286096518173622</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.035822924607066</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.169594061431566</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.437839740887205</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.261354481132387</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.532746894540035</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.335422272897418</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.916250303738827</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.9814227332815603</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.5019980502799765</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.300380431048762</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.698932064852869</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.090151793604805</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.816838405077633</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.085216875669884</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.144555396034591</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.305237256176626</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.094313055365788</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.309785144353842</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.973046255771747</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.917648522847003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.875974797046204</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9933174145022621</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9318122906019893</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8535676096813284</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.080002146042188</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4320620261949978</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5558059507851947</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5779021844954891</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9928070960878336</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3945083589191623</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.649167265144569</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.285686245128614</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1825398586137143</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.274057969681877</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1827109887860822</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.492347066519373</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.1699493837178709</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4359103132064481</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.5992044351981544</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.09541793721551574</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.357142690990356</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.677496238471739</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.535385180351502</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.629992994937862</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.050078501054946</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.035212435834773</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.951634227308728</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5154029398957731</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.802674761709738</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.571224305531918</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.8942472735638395</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9258682991890875</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.138976468220128</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9270056497918491</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4757120177567876</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4506634590915454</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3034395968436392</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1506077750184482</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.8598484008940118</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.2754440944396629</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.2336998687853039</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.11680563356411</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5635869709400423</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.6033136486690245</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.00862218837982639</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.5656969464935833</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.563951202226469</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.7889866616393522</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4479953871795845</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.4941994941984714</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1.434242353774323</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.4480079274858257</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.236466810182744</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.3299569318155216</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-1.174243745520958</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.6373272896200992</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.5145372317407575</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.3285231086997686</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-1.023816132788621</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5089745032477533</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.1226517860467493</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.113030208352965</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.0979063627238648</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.1790378556700574</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.410992082592996</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.02897700919178917</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.3880080698515074</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1.243143527790144</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1952671431668551</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.32954721264769</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.6450187626092118</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.939003498223511</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.5890444146503802</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.1074995129292015</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.7525032112953391</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.565039741918488</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.0362028190738403</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.1912933957222985</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.7785528866285323</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1.336012417492405</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.005732697626002</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.05498649962754438</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.2918554033254037</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.5155609015976681</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.4787641540597219</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.1677187608585301</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.6302318946344064</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.9539858622779057</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.875974797046204</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.738324560844974</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-2.117455304216517</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-2.960532590791728</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.722740120393239</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-2.688912370472963</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2.926718530189825</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-2.441186279674861</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-2.523235169157403</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.170141239782045</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.6789108695309641</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.6219654207111551</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1.226919658324942</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.9623428855017186</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-1.731942110810492</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-2.646578504238539</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.859623787124919</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.926260172791655</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.863917837450493</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-2.200486713413931</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-5.073172623930094</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-2.559609061043044</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-5.215573427760327</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-3.674892403644734</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-2.548197138882423</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-3.992064150920365</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-2.856732581269992</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-1.389452074550437</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-3.263905906283202</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-2.861624910331761</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.47242831552069</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2.210613860542357</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.91897558755273</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.623021555969934</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.6467163366892323</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.723058475612637</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.4023213428325464</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1.844719104840706</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-2.268834938790664</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.7825794159085901</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-2.002126537525549</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.554115617614274</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.808813255250242</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.184460634155693</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.104932932382118</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.530936196059341</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.085172648073023</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.8377352729992493</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-2.089787357067284</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-5.432489791214243</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-2.078833219519646</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-4.106513522481005</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-3.889973967545558</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-3.202165914013528</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-3.711827193463421</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-2.395410390755872</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.6941353399620744</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-3.362152330721807</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-2.250593423301921</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.711969071785737</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.440142436233331</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.110107908962539</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.738298360822546</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.894336743514952</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8814912299338156</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.597334652916646</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.5074407722447937</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.177894907662872</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.041426629816667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8060495269651106</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.267949531256207</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.014726679180885</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.180697334512175</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.532936163025943</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.418971785364132</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.1255186993829765</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.7583433302984984</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.1709702479221019</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.341657521399765</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.479650316827748</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.574952318186171</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.5382290704210492</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.456017347010961</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8865522617884214</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.593564550718944</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.2791738673977146</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.8739235406021784</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.760458875674151</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.04141516863236985</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.276784436900236</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7238363103455101</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6966883436085421</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.3972878134790058</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.3968099877362612</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.5199481661119107</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5545696586709149</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.109002965212209</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.5276108288717262</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5563931008911245</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.3807451031832114</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1455331361509601</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.8664174552515002</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1793384209013073</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.235625222716883</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.8626745851939278</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.9849348249975332</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.4043896566895928</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-1.0082816189431</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-1.709703957359756</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-1.366666969266417</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1.088419331936846</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.76544828655015</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.7088620684190088</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.117450576337691</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.7286198286921232</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.5516538113030719</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-1.508847323775445</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.4266879389484561</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.776079715583968</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.962670581020127</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6506248823718815</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.693961975565736</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.312319000776086</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5779021844954891</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.362493425975848</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9780636361483129</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.2502274209964566</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.7118212260733729</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.5221898998556146</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.000648559407754</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8521482212328538</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.5528343407833286</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.071289370377816</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.8096711199530962</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.6699005952202586</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6610916481468788</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.677938499841016</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.373726594848874</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.874908715462506</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.835082310653172</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.276931490827487</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.159693773327737</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.080589012325936</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.4227904057914206</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.509193832449089</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.287615247732502</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.4266879389484561</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.320960454887707</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2049111130022373</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.1439698239605259</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.8337877290969024</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.111087210211685</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.7944107537637608</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.33058579837393</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.6384418990223328</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.5483005713717437</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.227403569255366</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.16982502062095</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.8347211295336585</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-1.4666023067971</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1.31117893918472</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.670771708651187</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.5609625522845781</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.140869696145199</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.6174859176568872</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-2.596346471369992</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-1.629480945443393</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-2.346504431772074</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.396850456938756</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1.479732994264998</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-2.769459137992379</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-2.086700364429376</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.4742709125649522</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-2.374608704781138</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-1.746702076055219</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4E8uaJWa</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-1.527467282708703</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.5183432944036076</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.533488298097727</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.044357589036246</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.03921210213889102</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8599498413917023</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.2454855784600608</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.066254711297373</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.105580687293493</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.001939313435606664</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3839650245170682</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-1.535238927655273</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.04895348145561681</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.6154424975848742</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1.397836925236233</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.5408788789974798</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.9312888537265279</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.8225863373918942</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.6504368350985142</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.3941016562901304</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.07014270770662917</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.1763408760501587</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.02978189620998948</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.04060396365010781</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.1026987868018969</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.1800958275306563</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.172190921168615</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.1142847503227543</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.1753692411803931</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,307 +588,307 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.801759837338154</v>
+        <v>1.875974797046204</v>
       </c>
       <c r="C2" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8942472735638395</v>
+        <v>0.453935536059741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9258682991890875</v>
+        <v>0.5541707028356425</v>
       </c>
       <c r="F2" t="n">
-        <v>1.138976468220128</v>
+        <v>0.957352649149983</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9270056497918491</v>
+        <v>-0.1292551071765924</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4757120177567876</v>
+        <v>-0.2881628345745316</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4506634590915454</v>
+        <v>0.7588249896245581</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3034395968436392</v>
+        <v>-0.2062766373669394</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1506077750184482</v>
+        <v>0.5545696586709149</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8598484008940118</v>
+        <v>-1.338738394603227</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2754440944396629</v>
+        <v>-0.8302109101902021</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2336998687853039</v>
+        <v>-1.004264689400372</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.11680563356411</v>
+        <v>0.02838022394854765</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5635869709400423</v>
+        <v>-0.8347211295336593</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.6033136486690245</v>
+        <v>-0.5398948308083772</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00862218837982639</v>
+        <v>0.2807282645815775</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5656969464935833</v>
+        <v>-0.461532084506756</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.563951202226469</v>
+        <v>-1.029839360184243</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7889866616393522</v>
+        <v>-2.387601637948503</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4479953871795845</v>
+        <v>0.02180286524499585</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.4506157354175616</v>
+        <v>-0.912769726648322</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.427735003828283</v>
+        <v>-1.595710004009791</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.372050293030662</v>
+        <v>-1.136415445397327</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.2049948423938947</v>
+        <v>-0.811931804499487</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.321649597972967</v>
+        <v>-0.5528812598407761</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1.157345090056702</v>
+        <v>-0.6320886804644952</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.6064511698142885</v>
+        <v>-0.5900197762983331</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.8339317403826911</v>
+        <v>-0.7547413126702738</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.3269732704182956</v>
+        <v>-0.4729627524425609</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.038425889082193</v>
+        <v>-1.260560954033321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.838867317192179</v>
+        <v>1.950189756754252</v>
       </c>
       <c r="C3" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5089745032477533</v>
+        <v>0.8942472735638398</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1226517860467493</v>
+        <v>1.382168706652832</v>
       </c>
       <c r="F3" t="n">
-        <v>1.113030208352965</v>
+        <v>1.424385326758929</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0979063627238648</v>
+        <v>1.120216278867846</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1790378556700574</v>
+        <v>-0.06991287676558335</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.410992082592996</v>
+        <v>1.046043503519405</v>
       </c>
       <c r="J3" t="n">
         <v>0.02897700919178917</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3880080698515074</v>
+        <v>0.7834813927406461</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.243143527790144</v>
+        <v>0.6288833714098863</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1952671431668551</v>
+        <v>0.4306227619701142</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.32954721264769</v>
+        <v>0.1894147719924155</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6450187626092118</v>
+        <v>1.444131970873538</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.939003498223511</v>
+        <v>-0.1819135015351797</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5890444146503802</v>
+        <v>1.511307559371967</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.1074995129292015</v>
+        <v>1.509538506792035</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7525032112953391</v>
+        <v>1.691149211973674</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.565039741918488</v>
+        <v>-1.304929743131003</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0362028190738403</v>
+        <v>-1.069600206710438</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1912933957222985</v>
+        <v>1.247106365806938</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.801227251792218</v>
+        <v>0.271701963064886</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.316380015640374</v>
+        <v>-0.7151649790516715</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.108241899328083</v>
+        <v>0.2444896612480306</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0796377307967233</v>
+        <v>-0.09002129050630389</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.2837985716542099</v>
+        <v>-0.2824133984048806</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.5761042859228428</v>
+        <v>-0.3485195159294145</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.454373298706427</v>
+        <v>-0.05086312447213875</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.153677172633121</v>
+        <v>0.253310500850178</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.6120310014236678</v>
+        <v>-0.04379727498724993</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.9143361774510999</v>
+        <v>-0.3871059287913065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.875974797046204</v>
+        <v>1.913082276900228</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.738324560844974</v>
+        <v>0.5640134704357659</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.117455304216517</v>
+        <v>-0.02556659296935714</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.960532590791728</v>
+        <v>1.606009145829074</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.722740120393239</v>
+        <v>1.061997182027065</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.688912370472963</v>
+        <v>0.03921210213889102</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.926718530189825</v>
+        <v>-0.7191536131260086</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.441186279674861</v>
+        <v>0.4994843023092463</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.523235169157403</v>
+        <v>-0.3880080698515076</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.170141239782045</v>
+        <v>-0.01744152859481979</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6789108695309641</v>
+        <v>0.6827894964021773</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6219654207111551</v>
+        <v>0.4454014781648269</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.226919658324942</v>
+        <v>0.5002974729235449</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9623428855017186</v>
+        <v>0.03082253059211991</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.731942110810492</v>
+        <v>-0.5474258154293294</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.646578504238539</v>
+        <v>-0.03990628380902091</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.859623787124919</v>
+        <v>-0.5737460494652928</v>
       </c>
       <c r="T4" t="n">
-        <v>1.926260172791655</v>
+        <v>-0.3326399327856114</v>
       </c>
       <c r="U4" t="n">
-        <v>1.863917837450493</v>
+        <v>1.942816401255195</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.200486713413931</v>
+        <v>-0.6174859176568872</v>
       </c>
       <c r="W4" t="n">
-        <v>-5.243281876225726</v>
+        <v>-0.03196684585592533</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.674149975205692</v>
+        <v>-0.18555587581581</v>
       </c>
       <c r="Y4" t="n">
-        <v>-5.374948908249713</v>
+        <v>-0.2946729839693709</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.711199651929419</v>
+        <v>-0.1943489811020196</v>
       </c>
       <c r="AA4" t="n">
-        <v>-2.563795469355522</v>
+        <v>-0.2746344907403739</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4.015892470855575</v>
+        <v>-0.9327996465856209</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.857593470401309</v>
+        <v>-0.3233345345332589</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.8335703759798313</v>
+        <v>-0.4042694653823982</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3.239414146903336</v>
+        <v>-0.1702330881597221</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2.851545927208666</v>
+        <v>-0.6142342381775221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -898,97 +898,97 @@
         <v>-0.2278352655724001</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.47242831552069</v>
+        <v>0.398896568871729</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.210613860542357</v>
+        <v>0.7913359602104156</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.91897558755273</v>
+        <v>0.1270723334007464</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.623021555969934</v>
+        <v>0.7337950207158538</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6467163366892323</v>
+        <v>1.348711848992581</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.723058475612637</v>
+        <v>2.009422268875038</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4023213428325464</v>
+        <v>1.205245241985432</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.844719104840706</v>
+        <v>2.035763232063293</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.268834938790664</v>
+        <v>1.842263207970027</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7825794159085901</v>
+        <v>-0.006466244378795444</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.002126537525549</v>
+        <v>0.3796434252031065</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.554115617614274</v>
+        <v>0.7456944423905436</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.808813255250242</v>
+        <v>0.1872460836269011</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.184460634155693</v>
+        <v>0.4541951391572858</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.104932932382118</v>
+        <v>-0.03643996436696058</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.530936196059341</v>
+        <v>0.5189196789442588</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.085172648073023</v>
+        <v>-1.007055065171216</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8377352729992493</v>
+        <v>-1.603659792576162</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.089787357067284</v>
+        <v>1.300380431048762</v>
       </c>
       <c r="W5" t="n">
-        <v>-5.651551875295325</v>
+        <v>2.622119166392113</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.061258573102836</v>
+        <v>1.25680165620034</v>
       </c>
       <c r="Y5" t="n">
-        <v>-4.383044956509704</v>
+        <v>2.355612550466498</v>
       </c>
       <c r="Z5" t="n">
-        <v>-4.004739391636894</v>
+        <v>1.853325485291611</v>
       </c>
       <c r="AA5" t="n">
-        <v>-3.195935969479625</v>
+        <v>1.366234773786936</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3.686164225518357</v>
+        <v>1.572423262966171</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.37309349558256</v>
+        <v>1.333582053265597</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.764549775033611</v>
+        <v>0.6421385983273146</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3.346598198328608</v>
+        <v>1.721945858586193</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2.253333565544738</v>
+        <v>1.576162631504331</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -998,297 +998,297 @@
         <v>-0.2278352655724001</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4266879389484561</v>
+        <v>1.279520043879926</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.320960454887707</v>
+        <v>0.3433571407247333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2049111130022373</v>
+        <v>0.9054601294156561</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1439698239605259</v>
+        <v>0.3569703169881656</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8337877290969024</v>
+        <v>0.9122119333746842</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.111087210211685</v>
+        <v>-0.0938549735007687</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7944107537637608</v>
+        <v>1.205245241985432</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.33058579837393</v>
+        <v>0.1506077750184482</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6384418990223328</v>
+        <v>-0.1932481802050859</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5483005713717437</v>
+        <v>0.1784560275380509</v>
       </c>
       <c r="N6" t="n">
-        <v>0.227403569255366</v>
+        <v>0.1913362735399982</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.16982502062095</v>
+        <v>0.4625440930055457</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8347211295336585</v>
+        <v>0.6148037952552978</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.4666023067971</v>
+        <v>0.05505295424683055</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.31117893918472</v>
+        <v>0.926330260665351</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.670771708651187</v>
+        <v>0.02318963121603802</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5609625522845781</v>
+        <v>-0.6242789089523595</v>
       </c>
       <c r="U6" t="n">
-        <v>1.140869696145199</v>
+        <v>0.5515270524599796</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6174859176568872</v>
+        <v>-1.469870961526065</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.624604614252421</v>
+        <v>0.2489877598880388</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.630529023877624</v>
+        <v>0.9906110075456348</v>
       </c>
       <c r="Y6" t="n">
-        <v>-2.528093600564576</v>
+        <v>0.001274658685556155</v>
       </c>
       <c r="Z6" t="n">
-        <v>-1.427678027868784</v>
+        <v>0.2529538584073018</v>
       </c>
       <c r="AA6" t="n">
-        <v>-1.433933341354985</v>
+        <v>0.2934851645081732</v>
       </c>
       <c r="AB6" t="n">
-        <v>-2.714154447382088</v>
+        <v>0.190137560602236</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2.033033258407658</v>
+        <v>1.175280796566846</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.123023262670525</v>
+        <v>0.1105715617205601</v>
       </c>
       <c r="AE6" t="n">
-        <v>-2.347391452076272</v>
+        <v>0.3056592400392281</v>
       </c>
       <c r="AF6" t="n">
-        <v>-1.860487349821715</v>
+        <v>1.083864860772317</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.838867317192179</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4266879389484561</v>
+        <v>-1.747623151460752</v>
       </c>
       <c r="E7" t="n">
-        <v>0.776079715583968</v>
+        <v>-2.58168103356413</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.962670581020127</v>
+        <v>-1.792950896769364</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6506248823718815</v>
+        <v>-2.234263889935592</v>
       </c>
       <c r="H7" t="n">
-        <v>0.693961975565736</v>
+        <v>-1.81591253923717</v>
       </c>
       <c r="I7" t="n">
-        <v>1.312319000776086</v>
+        <v>-2.720921336082133</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5779021844954891</v>
+        <v>-1.853052163278039</v>
       </c>
       <c r="K7" t="n">
-        <v>1.362493425975848</v>
+        <v>-2.952262508794078</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9780636361483129</v>
+        <v>-0.2918990610793617</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2502274209964566</v>
+        <v>-0.6116664070157473</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7118212260733729</v>
+        <v>-1.267944518435513</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5221898998556146</v>
+        <v>-1.349618143058441</v>
       </c>
       <c r="P7" t="n">
-        <v>1.000648559407754</v>
+        <v>-1.942529435362511</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8521482212328538</v>
+        <v>-1.196489104260805</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5528343407833286</v>
+        <v>-1.582418435525956</v>
       </c>
       <c r="S7" t="n">
-        <v>1.071289370377816</v>
+        <v>-1.226588315712381</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8096711199530962</v>
+        <v>1.580785162408411</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6699005952202586</v>
+        <v>1.116351291736351</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6610916481468788</v>
+        <v>-2.432032867105666</v>
       </c>
       <c r="W7" t="n">
-        <v>2.702087146670074</v>
+        <v>-5.314862043685517</v>
       </c>
       <c r="X7" t="n">
-        <v>1.36840739722343</v>
+        <v>-2.697616275532912</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.980317425595268</v>
+        <v>-4.070027617611146</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.832031950109931</v>
+        <v>-4.059278073998753</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.278467607692893</v>
+        <v>-3.478129382996768</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.131411458525233</v>
+        <v>-3.88848390303874</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.052772661058523</v>
+        <v>-3.097384204592905</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.996274262815201</v>
+        <v>-0.5260492691461481</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.498018135329423</v>
+        <v>-3.636678129008702</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.269323063994469</v>
+        <v>-2.949315242992639</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.875974797046204</v>
+        <v>1.838867317192179</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04141516863236985</v>
+        <v>-2.848402495220999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.276784436900236</v>
+        <v>-1.764778480384357</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7238363103455101</v>
+        <v>-2.467553653315619</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6966883436085421</v>
+        <v>-1.186795404734942</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3972878134790058</v>
+        <v>-2.361537433759541</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3968099877362612</v>
+        <v>-1.742369568876401</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5199481661119107</v>
+        <v>-1.382544870160582</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5545696586709149</v>
+        <v>-1.061277875938952</v>
       </c>
       <c r="L8" t="n">
-        <v>1.109002965212209</v>
+        <v>-0.215224011656369</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5276108288717262</v>
+        <v>-1.065566528993461</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5563931008911245</v>
+        <v>-0.2779371044140974</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3807451031832114</v>
+        <v>-0.6134272346574468</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1455331361509601</v>
+        <v>-0.417591654774246</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8664174552515002</v>
+        <v>-1.210152462073104</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1793384209013073</v>
+        <v>-3.21245515315492</v>
       </c>
       <c r="S8" t="n">
-        <v>1.235625222716883</v>
+        <v>-1.388007510382778</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8626745851939278</v>
+        <v>0.2796879956894941</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9849348249975332</v>
+        <v>1.207227504611448</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4043896566895928</v>
+        <v>-1.469870961526065</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.004479942851939</v>
+        <v>-5.321190562747734</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.781165279747439</v>
+        <v>-3.238693894561062</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.391025852188715</v>
+        <v>-5.366324253183043</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.071365252466644</v>
+        <v>-3.693146222402924</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.7575044773083424</v>
+        <v>-2.595230280295006</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.6846082427706709</v>
+        <v>-4.111692042839987</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.095265373120652</v>
+        <v>-3.151897149236649</v>
       </c>
       <c r="AD8" t="n">
-        <v>-1.106545045900118</v>
+        <v>-1.398940471299813</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.5414112475428839</v>
+        <v>-3.33534176347949</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.504364242954135</v>
+        <v>-2.968996285747202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1298,191 +1298,1091 @@
         <v>-0.2278352655724001</v>
       </c>
       <c r="D9" t="n">
-        <v>1.711969071785737</v>
+        <v>-0.75692174207653</v>
       </c>
       <c r="E9" t="n">
-        <v>1.440142436233331</v>
+        <v>-0.947875927204585</v>
       </c>
       <c r="F9" t="n">
-        <v>2.110107908962539</v>
+        <v>-0.7291542422156543</v>
       </c>
       <c r="G9" t="n">
-        <v>1.738298360822546</v>
+        <v>-0.4817685396960423</v>
       </c>
       <c r="H9" t="n">
-        <v>1.894336743514952</v>
+        <v>0.03921210213889102</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8814912299338156</v>
+        <v>0.3040623426243838</v>
       </c>
       <c r="J9" t="n">
-        <v>1.597334652916646</v>
+        <v>-0.2062766373669394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5074407722447937</v>
+        <v>0.1506077750184481</v>
       </c>
       <c r="L9" t="n">
-        <v>1.177894907662872</v>
+        <v>-0.896474786646151</v>
       </c>
       <c r="M9" t="n">
-        <v>1.041426629816667</v>
+        <v>0.4642449932277227</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8060495269651106</v>
+        <v>-0.1464209984906566</v>
       </c>
       <c r="O9" t="n">
-        <v>1.267949531256207</v>
+        <v>-2.029178981582436</v>
       </c>
       <c r="P9" t="n">
-        <v>1.014726679180885</v>
+        <v>-1.679408315921468</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.180697334512175</v>
+        <v>-1.737321385539743</v>
       </c>
       <c r="R9" t="n">
-        <v>1.532936163025943</v>
+        <v>-1.681208539624682</v>
       </c>
       <c r="S9" t="n">
-        <v>1.418971785364132</v>
+        <v>-1.658954520709878</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1255186993829765</v>
+        <v>0.1048185314645111</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7583433302984984</v>
+        <v>-1.284342740233658</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1709702479221019</v>
+        <v>0.2348991262122902</v>
       </c>
       <c r="W9" t="n">
-        <v>1.418523375299253</v>
+        <v>-2.822245557704643</v>
       </c>
       <c r="X9" t="n">
-        <v>1.490610658333529</v>
+        <v>-1.484379231169763</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.660130460352752</v>
+        <v>-2.29082217505221</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5709240594167944</v>
+        <v>-1.380450684836221</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4501238758078212</v>
+        <v>-1.352929239800561</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8922551435539909</v>
+        <v>-2.177221497895844</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.603666452553536</v>
+        <v>-1.814003196728918</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5067301942271382</v>
+        <v>-0.5934007107077303</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.8734107877103944</v>
+        <v>-2.275288605160334</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.785662114372691</v>
+        <v>-1.674712642827849</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.801759837338154</v>
+        <v>1.838867317192179</v>
       </c>
       <c r="C10" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.527467282708703</v>
+        <v>-0.4817269061364683</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5183432944036076</v>
+        <v>-0.05191828823322069</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.533488298097727</v>
+        <v>-0.5475304231455085</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.044357589036246</v>
+        <v>0.01661252007283495</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03921210213889102</v>
+        <v>0.148337081043365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8599498413917023</v>
+        <v>-0.3212362970008562</v>
       </c>
       <c r="J10" t="n">
+        <v>0.0289770091917891</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01595381380095945</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.3525729582268892</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.2250107475532503</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3527424035369481</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.160851243468443</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1151727855736728</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.6679215693645608</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-1.406502723841384</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.6994540988175783</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6015161627485028</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.064538776133564</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.6174859176568872</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.4318181779921329</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.3470252328451812</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.9126553593084963</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.09538733002574006</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01318805736910337</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.5119800223495198</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.4602159064123064</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.1085185133847196</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.3497529888893691</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.2772054136475303</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3438576016837164</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1744289047700715</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4384274518067099</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2095672410308494</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.06991287676558319</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.2817437513403147</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.5199481661119107</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.6303852000429876</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.3792840581218424</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.884522883947828</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1482092388053634</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07242583385288191</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.129772317190251</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4251413932248763</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.011255086995834</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.3646452053198286</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.135148335422034</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.9090309147252592</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4586502002279492</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.4105704471876935</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.2676083176504447</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.7623670621011185</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1867029400333505</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.03919285082682095</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.59358328922695</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.2326613796106228</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1910525765860482</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1408366028852332</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.2020073107414271</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.169442109503901</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4765025483737285</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.372492807024601</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1554426740777725</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3665870388523135</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.1417247258165768</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8523647721473392</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.2533541086340185</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.3871064076503342</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.6116664070157473</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.7344004720509747</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.988409864691368</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1142484255440033</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1814942223564979</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.7668795663305666</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1473194250836747</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.8300570681226471</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.3016560865322989</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2348991262122902</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5573487984058884</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.03427337639302779</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6384567806654614</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.1649480300305865</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.05071298618668091</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.4283323431827712</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.4039843369459772</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.2122009980676998</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.331486940009575</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.4373820608647149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.4817269061364686</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.1226517860467499</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4124811919395464</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.06335876679636862</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1.052037686905851</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.003380267501118</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.068873341415611</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1.061277875938952</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1230468224687414</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1784560275380509</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.08159718515582839</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.1605170536615476</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.6773732164692108</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.9805713274006674</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8024093406116869</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.719811873946506</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.371625334188822</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.06601366349786</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.043678439591476</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.185226886128079</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1873953631557115</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.2105184486327493</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.44455005022586</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.04543910023578279</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.6030659879766762</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.3323017713056646</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.275365620533698</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.4679177491500952</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.01587735424340384</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.7569217420765298</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2018901450976759</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.248079439558927</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.2130650158155182</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1483370810433649</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3429565163809776</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.5199481661119107</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01595381380095925</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.1294790264402012</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.3970005307125058</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.2431365763856548</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.6543267295686127</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.1455331361509601</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1529557543192063</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.09276765530044466</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.04536412077535541</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.2707841330330878</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.044112028610673</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8741879091141732</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.4782229598063661</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.3562799115958091</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.002665647824264</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.8096072022783086</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.5227431953631601</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.4770223540707872</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.320718146831599</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.6495723803290018</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.3319792330264145</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.8459147237942283</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.913082276900228</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.8669996764525548</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.3722994253886153</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.403756998761909</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.6161203016363044</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.50641279238348</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.3032851398824282</v>
+      </c>
+      <c r="J15" t="n">
         <v>-0.2454855784600608</v>
       </c>
-      <c r="K10" t="n">
-        <v>1.066254711297373</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.105580687293493</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.001939313435606664</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3839650245170682</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.535238927655273</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.04895348145561681</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.6154424975848742</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-1.397836925236233</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.5408788789974798</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.9312888537265279</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.8225863373918942</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.6504368350985142</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.3953697247813857</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.0742375974227783</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.1380663357051011</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>-0.02758433782330802</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.05383265228130058</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.06039136161081136</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-0.1522824863651017</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.3413920592847943</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.09681913455644041</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.1367066434589939</v>
+      <c r="K15" t="n">
+        <v>0.1506077750184482</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7148245694068689</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.6116664070157473</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1065767052744038</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.2799390453817818</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.2507398648704828</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5810327748785822</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.3241444780579849</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7141104260082114</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.05061589280194062</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.4351064166290058</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6610916481468788</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.03916150111666923</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1719599781998769</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0.1475243098223218</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.2348512531480965</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.2329755349646584</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.0414259641113578</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.75384532243151</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.01941637633671944</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.09713230175376023</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.557480342673658</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.875974797046204</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2888186344957038</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.6219470647304813</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.040509360621618</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.756190967243672</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.03921210213889079</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.1955781971718605</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.02897700919178917</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.3880080698515076</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.376803674081342</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.3258774413260755</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1.042481220180073</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.5442127048077808</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.5114457865951156</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.5462367125944423</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2304666326716995</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.7763151409199796</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.184074611028956</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1.934345961290862</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.02180286524499585</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5469632261154911</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.587999021365973</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5823203847925364</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.5179388646471393</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5359831244764007</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.184759928064776</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.12439502466169</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.5363001270782937</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.403148461803931</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.31902282749033</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.838867317192179</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5640134704357657</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6821646512601229</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.07517981366641927</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3577928787959628</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.785211764610477</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.340527961962187</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.950215122754739</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.612565068236899</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.6093419085209569</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.4267441350989009</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.01776063374169065</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.09444863880504764</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.8814687094764916</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.02860957215672142</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.2114890961910174</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1318838342474953</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.8527728389401462</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.5893636088599814</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.158316257070566</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.212122255607362</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.930406445589337</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.403442102768123</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.7025710994946575</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.7301153900613159</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.292716806138582</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.250668797594048</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.07790578611388294</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.9189006148033765</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.84522841325447</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.950189756754252</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.655494223580234</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.849564564753992</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.669805800382785</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.986465258235059</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.785211764610477</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.281681485171195</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5779021844954891</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.22783946475836</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.286096518173622</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.035822924607066</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.169594061431566</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.0985238894522</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.574201587201946</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.578725537489006</v>
+      </c>
+      <c r="R18" t="n">
+        <v>3.175104998702118</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.906149468637073</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.079964809212903</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.5019980502799765</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.513476692016056</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.926268883789241</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.160400989988178</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.034081112427869</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.139579419257231</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.231676790258874</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.513193502883908</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.219003514720972</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.234414854614514</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.070750190537483</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.922677897849637</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.801759837338154</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.2278352655724001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.5640134704357661</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7817535255690108</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.594105011009692</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9805544234794675</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2574620599478393</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4849338499539983</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3034395968436392</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8648858329312191</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3945083589191623</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.649167265144569</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.285686245128614</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.08173380081228425</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.14797110572051</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.1859385536236332</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3985831256116349</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.1664190753969464</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.6213059504169612</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5992044351981544</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.09541793721551574</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.844209820267932</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.528650632907643</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.427194488337217</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.521346588940874</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.056143173446205</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.988661005608845</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.911467428118994</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.3568155905264471</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.782435582379123</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.496325639005619</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -588,407 +588,397 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.913082276900228</v>
+        <v>1.838867317192179</v>
       </c>
       <c r="C2" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4932490840511782</v>
+        <v>-0.09645413582038213</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2620433381962401</v>
+        <v>0.2405855291956655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6756503991636347</v>
+        <v>0.444914016773501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3387368635819874</v>
+        <v>-0.2775538615468439</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2413949864726141</v>
+        <v>-0.4518503029312428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.367524637856231</v>
+        <v>0.5314436661244709</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9120375770431252</v>
+        <v>-0.7944107537637608</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8490375846866244</v>
+        <v>0.1438750769575737</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3792840581218424</v>
+        <v>-1.338738394603227</v>
       </c>
       <c r="M2" t="n">
-        <v>0.884522883947828</v>
+        <v>-0.8302109101902021</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1482092388053634</v>
+        <v>-1.004264689400372</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02838022394854765</v>
+        <v>0.50737623165817</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1437759495571773</v>
+        <v>-0.5046674326302739</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4699026213667006</v>
+        <v>-0.5248328615664728</v>
       </c>
       <c r="R2" t="n">
-        <v>1.011255086995834</v>
+        <v>0.02409682874616747</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3646452053198286</v>
+        <v>-0.5348420517686974</v>
       </c>
       <c r="T2" t="n">
-        <v>1.067059268535735</v>
+        <v>-0.8594128334868001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9090309147252592</v>
+        <v>-2.387601637948503</v>
       </c>
       <c r="V2" t="n">
-        <v>0.233884382112446</v>
+        <v>-0.3830800305928634</v>
       </c>
       <c r="W2" t="n">
-        <v>0.4126692352915818</v>
+        <v>-0.9311281236618434</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3375299490269271</v>
+        <v>-1.602444389980451</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8053699639998959</v>
+        <v>-1.138364831533073</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1664859369253932</v>
+        <v>-0.826574289752071</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.01982265925674269</v>
+        <v>-0.5577118261205629</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.5410637269207743</v>
+        <v>-0.5543648122157195</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1718693624916289</v>
+        <v>-0.651416071365271</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.2432955445423495</v>
+        <v>-0.7698669941042622</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1225119588315343</v>
+        <v>-0.4606768454367023</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1951396124619582</v>
+        <v>-1.246988867639715</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.801759837338154</v>
+        <v>1.838867317192179</v>
       </c>
       <c r="C3" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.719831781384025</v>
+        <v>0.7291303719998028</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8097821468951197</v>
+        <v>1.273948436328604</v>
       </c>
       <c r="F3" t="n">
-        <v>1.498517497807967</v>
+        <v>0.9314063892828194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3022699567696303</v>
+        <v>0.9326264888117991</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7874976717695709</v>
+        <v>-0.4518503029312428</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1221572838243141</v>
+        <v>0.6897985164191746</v>
       </c>
       <c r="J3" t="n">
-        <v>1.205245241985432</v>
+        <v>-0.1768699315470983</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01595381380095925</v>
+        <v>0.6129197085318268</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3871064076503342</v>
+        <v>0.6288833714098863</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6116664070157473</v>
+        <v>0.4306227619701142</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7344004720509747</v>
+        <v>0.1894147719924155</v>
       </c>
       <c r="O3" t="n">
-        <v>2.161446189315533</v>
+        <v>1.085474861652541</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3473195195658246</v>
+        <v>-0.2749234427523678</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3427365667671963</v>
+        <v>1.456246435722241</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7668795663305666</v>
+        <v>1.08330501254152</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1473194250836747</v>
+        <v>1.504846535270637</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9988527189665259</v>
+        <v>-1.025762170550333</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3016560865322989</v>
+        <v>-1.069600206710438</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4266857610828552</v>
+        <v>1.188251208015971</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4684410436384729</v>
+        <v>0.3806351048406696</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.04788658339099207</v>
+        <v>-0.6392341349005228</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5706611363472049</v>
+        <v>0.2333187610447304</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1421948948479464</v>
+        <v>-0.07955301445709498</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07067015325888258</v>
+        <v>-0.2652171901760009</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.5041939331805805</v>
+        <v>-0.372480461021963</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5092776999298572</v>
+        <v>-0.03272726077922969</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.07795740960000577</v>
+        <v>0.2596601896432859</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.35932876427656</v>
+        <v>-0.0297466955041496</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3751912375562724</v>
+        <v>-0.4134956953281171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.838867317192179</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C4" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7333336132816678</v>
+        <v>-0.09645413582038213</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2811780370288348</v>
+        <v>-0.3286110885037893</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2086177215546892</v>
+        <v>0.7951885249802102</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1353329249786516</v>
+        <v>0.7179926944304982</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.176751948510964</v>
+        <v>0.3665870388523134</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.105701863076157</v>
+        <v>-0.440611491838402</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.382544870160582</v>
+        <v>0.6465178314084516</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.263258817765186</v>
+        <v>-0.2398887125122697</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1230468224687414</v>
+        <v>-0.01744152859481979</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1784560275380509</v>
+        <v>0.6827894964021773</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08159718515582839</v>
+        <v>0.4454014781648269</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3870373331695451</v>
+        <v>-0.1367908131927002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7733129956638739</v>
+        <v>-0.3164377571450901</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.013747296494019</v>
+        <v>-0.7146136740144627</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8024093406116869</v>
+        <v>-0.5307618762293783</v>
       </c>
       <c r="S4" t="n">
-        <v>0.719811873946506</v>
+        <v>-0.7672599000768061</v>
       </c>
       <c r="T4" t="n">
-        <v>1.518404161009587</v>
+        <v>-0.3016532915678939</v>
       </c>
       <c r="U4" t="n">
-        <v>1.06601366349786</v>
+        <v>1.942816401255195</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.192845822268582</v>
+        <v>-0.1806385826739339</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1358019461140828</v>
+        <v>-0.07678403828208691</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1540540102277333</v>
+        <v>-0.1805728072874238</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.2215080791179914</v>
+        <v>-0.4624104987004007</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.3661662853462351</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.04083667868504036</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.5612890634149459</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.36562359887089</v>
-      </c>
+        <v>-0.2228953513760704</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-0.01291181708524318</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.5886819131117771</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.08518706930092218</v>
-      </c>
+        <v>-0.3805226617658976</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.987297236608277</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C5" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5918048405124928</v>
+        <v>0.3163381180897104</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2811780370288344</v>
+        <v>0.7149160439452109</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.081282054698589</v>
+        <v>-0.1777962200384266</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5291755185521059</v>
+        <v>0.499191253556357</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6155377712879541</v>
+        <v>0.9394931781008028</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3894506940508819</v>
+        <v>1.759302813024942</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2062766373669394</v>
+        <v>1.058211712886227</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1438750769575737</v>
+        <v>1.934772761150176</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7148245694068689</v>
+        <v>1.842263207970027</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6116664070157473</v>
+        <v>-0.006466244378795444</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1065767052744038</v>
+        <v>0.3796434252031065</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.08487991580545017</v>
+        <v>0.01186312023442371</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1579285567365127</v>
+        <v>-0.2074626818641928</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6002962408037541</v>
+        <v>0.2952913636551995</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.3241444780579849</v>
+        <v>-0.07320770987738884</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7141104260082114</v>
+        <v>0.4699543025330261</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4652660785706008</v>
+        <v>-0.8300570681226468</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4351064166290058</v>
+        <v>-1.603659792576162</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4266857610828552</v>
+        <v>1.236451552758574</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.05174317798748246</v>
+        <v>2.413654790271915</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1168598470677457</v>
+        <v>1.255481858854156</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1475243098223218</v>
+        <v>2.222193135168014</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.2370763394486358</v>
+        <v>1.726142104132111</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2238507339771009</v>
+        <v>1.390961487379234</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.06529849243234705</v>
+        <v>1.657162449433347</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.7002053073265113</v>
+        <v>1.415433871769566</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.1218771051814593</v>
+        <v>0.7144114788992731</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.08947878808146213</v>
+        <v>1.627012369374736</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.4934858814332395</v>
+        <v>1.473879885222306</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -998,297 +988,297 @@
         <v>-0.2278352655724001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6426405664186405</v>
+        <v>-1.741726119262037</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6821646512601229</v>
+        <v>-2.549764384020942</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06405998800906346</v>
+        <v>-1.865229763542177</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2835155475518464</v>
+        <v>-2.263437415385478</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816390330011755</v>
+        <v>-2.205644606753149</v>
       </c>
       <c r="I6" t="n">
-        <v>1.388996086181943</v>
+        <v>-2.909993849644706</v>
       </c>
       <c r="J6" t="n">
-        <v>2.107050887127225</v>
+        <v>-2.205932633116132</v>
       </c>
       <c r="K6" t="n">
-        <v>1.733753633332639</v>
+        <v>-3.114541694503767</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6093419085209569</v>
+        <v>-0.2918990610793617</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4267441350989009</v>
+        <v>-0.6116664070157473</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01776063374169065</v>
+        <v>-1.267944518435513</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1479325936888811</v>
+        <v>-1.408607799180316</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8256776422274212</v>
+        <v>-1.953996962918891</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.02811063306739601</v>
+        <v>-1.287099478852396</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2114890961910174</v>
+        <v>-1.566943795159615</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1318838342474953</v>
+        <v>-1.249394107465558</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.011783234662641</v>
+        <v>1.625152398697416</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5893636088599814</v>
+        <v>1.116351291736351</v>
       </c>
       <c r="V6" t="n">
-        <v>1.16897107011893</v>
+        <v>-2.560059079228309</v>
       </c>
       <c r="W6" t="n">
-        <v>1.205544317614436</v>
+        <v>-5.607508463901694</v>
       </c>
       <c r="X6" t="n">
-        <v>1.926422395332392</v>
+        <v>-2.822800380810278</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.423485110239097</v>
+        <v>-4.445831509203892</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7115119437204184</v>
+        <v>-4.155006761637404</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6999078915353633</v>
+        <v>-3.373401564709736</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.292716806138582</v>
+        <v>-3.709141534027309</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.183453223110622</v>
+        <v>-2.977875635585828</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.08952107049151913</v>
+        <v>-0.2911107838011604</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.8803900179434873</v>
+        <v>-3.379073154115272</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.838106355779476</v>
+        <v>-2.850033501651119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.987297236608277</v>
+        <v>1.875974797046204</v>
       </c>
       <c r="C7" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D7" t="n">
-        <v>2.710533190768246</v>
+        <v>-1.210993221377632</v>
       </c>
       <c r="E7" t="n">
-        <v>1.971891908031506</v>
+        <v>-1.229839066527926</v>
       </c>
       <c r="F7" t="n">
-        <v>2.499301806969994</v>
+        <v>-0.9561840160533359</v>
       </c>
       <c r="G7" t="n">
-        <v>1.987041051500517</v>
+        <v>-0.6713964551202977</v>
       </c>
       <c r="H7" t="n">
-        <v>2.096997418623261</v>
+        <v>-0.2881628345745316</v>
       </c>
       <c r="I7" t="n">
-        <v>2.475553982050216</v>
+        <v>0.07099648603679438</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9699915954267033</v>
+        <v>-0.3827168722859858</v>
       </c>
       <c r="K7" t="n">
-        <v>1.423087708523719</v>
+        <v>0.01595381380095925</v>
       </c>
       <c r="L7" t="n">
-        <v>2.286096518173622</v>
+        <v>-0.896474786646151</v>
       </c>
       <c r="M7" t="n">
-        <v>1.035822924607066</v>
+        <v>0.4642449932277227</v>
       </c>
       <c r="N7" t="n">
-        <v>1.169594061431566</v>
+        <v>-0.1464209984906566</v>
       </c>
       <c r="O7" t="n">
-        <v>2.010432669643534</v>
+        <v>-2.812561614880931</v>
       </c>
       <c r="P7" t="n">
-        <v>1.605486297808902</v>
+        <v>-2.218548162048008</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.511660137601369</v>
+        <v>-1.860076434861261</v>
       </c>
       <c r="R7" t="n">
-        <v>3.175104998702118</v>
+        <v>-1.532775789230733</v>
       </c>
       <c r="S7" t="n">
-        <v>2.906149468637073</v>
+        <v>-1.609397298491902</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.029839360184243</v>
+        <v>0.2304199556573773</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5019980502799765</v>
+        <v>-1.284342740233658</v>
       </c>
       <c r="V7" t="n">
-        <v>1.843775896515363</v>
+        <v>0.2242443131639254</v>
       </c>
       <c r="W7" t="n">
-        <v>4.826958220364722</v>
+        <v>-2.856826082550917</v>
       </c>
       <c r="X7" t="n">
-        <v>2.103094966215985</v>
+        <v>-1.405876993055359</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.872663991390525</v>
+        <v>-2.265798631498563</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.217932262413745</v>
+        <v>-1.337817707005098</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.276286928420267</v>
+        <v>-1.332670432539768</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.644492408649348</v>
+        <v>-2.09562386984313</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.261915526804974</v>
+        <v>-1.824970502847608</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.245359033672554</v>
+        <v>-0.9183533480222216</v>
       </c>
       <c r="AE7" t="n">
-        <v>3.132006857802704</v>
+        <v>-2.212604440190583</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.946714841827744</v>
+        <v>-1.614047974692625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.838867317192179</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C8" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9178354023587021</v>
+        <v>-3.274954490928094</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2574615112913571</v>
+        <v>-2.249649673239449</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6587286797190669</v>
+        <v>-2.396201438680918</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.557542290660569</v>
+        <v>-1.382501137961256</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3198191907503957</v>
+        <v>-2.334256189033422</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.03132510953824517</v>
+        <v>-1.924274627676471</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4994843023092462</v>
+        <v>-1.617798516719311</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1119674493556551</v>
+        <v>-1.263258817765186</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.376803674081342</v>
+        <v>-0.215224011656369</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3258774413260755</v>
+        <v>-1.065566528993461</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.042481220180073</v>
+        <v>-0.2779371044140974</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.915454274001444</v>
+        <v>-1.193885450896693</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7226175831920684</v>
+        <v>-0.7919653583708195</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5587222923607568</v>
+        <v>-1.561849443871562</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2304666326716995</v>
+        <v>-3.443955773035392</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7763151409199796</v>
+        <v>-1.623818607982882</v>
       </c>
       <c r="T8" t="n">
-        <v>1.04871191518314</v>
+        <v>0.7722784580040332</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.934345961290862</v>
+        <v>1.207227504611448</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02180286524499585</v>
+        <v>-1.597728718106441</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5983713626576859</v>
+        <v>-5.174865028011506</v>
       </c>
       <c r="X8" t="n">
-        <v>1.761458465079876</v>
+        <v>-3.201613141881857</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6909237919408191</v>
+        <v>-5.223555123577362</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5267579885327227</v>
+        <v>-3.783464260359266</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5022646428544124</v>
+        <v>-2.669092846573592</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.085556310375333</v>
+        <v>-4.275450955864105</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.075920344344576</v>
+        <v>-3.216396106793455</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.30161975916392</v>
+        <v>-1.325779666766542</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.3826364951584256</v>
+        <v>-3.45626216949103</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.315207439557294</v>
+        <v>-2.992317844487865</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1298,181 +1288,191 @@
         <v>-0.2278352655724001</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7333336132816675</v>
+        <v>0.6465719212177844</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1457194262457563</v>
+        <v>0.1220029005082791</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.08128205469859</v>
+        <v>0.6200512708768556</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2119134292846013</v>
+        <v>0.2803898126822166</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.05432359406494423</v>
+        <v>0.6939619755657359</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2244788793993531</v>
+        <v>-0.08248590732576483</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4415302839256678</v>
+        <v>1.058211712886227</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01595381380095925</v>
+        <v>0.1438750769575738</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1294790264402012</v>
+        <v>-0.1932481802050859</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3970005307125058</v>
+        <v>0.1784560275380509</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2431365763856548</v>
+        <v>0.1913362735399982</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3869069551494487</v>
+        <v>0.3917565056592959</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2284376192593933</v>
+        <v>0.5751764951531546</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07162112041292462</v>
+        <v>0.03773168961864067</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.09276765530044466</v>
+        <v>0.8745830632803048</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04536412077535541</v>
+        <v>0.05710239594243171</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3955461358307378</v>
+        <v>-0.2612891141921837</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.044112028610673</v>
+        <v>0.5515270524599796</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8315686569207142</v>
+        <v>-1.192845822268582</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4712693188203715</v>
+        <v>0.2410453522037886</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3036659602580023</v>
+        <v>0.9465697989968399</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.996232089870617</v>
+        <v>0.001274658685556155</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.8208208713227289</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+        <v>0.269934113224608</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.3040557261785181</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1907343738102606</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.220369112293997</v>
+      </c>
       <c r="AD9" t="n">
-        <v>0.6953624125199497</v>
-      </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
+        <v>0.08992216727142914</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.3038062496526942</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.006965283415226</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.838867317192179</v>
+        <v>1.801759837338154</v>
       </c>
       <c r="C10" t="n">
         <v>-0.2278352655724001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3517203112820036</v>
+        <v>-0.591804840512493</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6802005497497728</v>
+        <v>-0.1863119340789256</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3420556294429593</v>
+        <v>-0.5475304231455085</v>
       </c>
       <c r="G10" t="n">
-        <v>0.860485434030832</v>
+        <v>-0.06969249271640911</v>
       </c>
       <c r="H10" t="n">
-        <v>0.413354886954231</v>
+        <v>-0.3700065687528872</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5536874912494792</v>
+        <v>-0.5940938852009607</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2642306557505177</v>
+        <v>-0.5885638130248733</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8210897144140197</v>
+        <v>-0.3678099756688841</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3945083589191623</v>
+        <v>-0.3525729582268892</v>
       </c>
       <c r="M10" t="n">
-        <v>0.649167265144569</v>
+        <v>-0.2250107475532503</v>
       </c>
       <c r="N10" t="n">
-        <v>1.285686245128614</v>
+        <v>0.3527424035369481</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4435370250264486</v>
+        <v>-1.177368347182568</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9224691687191507</v>
+        <v>-0.2074626818641928</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2309841324433644</v>
+        <v>-0.6265011539493247</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3985831256116349</v>
+        <v>-1.675390074846937</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1664190753969464</v>
+        <v>-0.8739105144519562</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7227167762203985</v>
+        <v>0.6780953774607095</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5992044351981544</v>
+        <v>1.064538776133564</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2732829247716165</v>
+        <v>-0.9904043743496523</v>
       </c>
       <c r="W10" t="n">
-        <v>4.28708609581073</v>
+        <v>-0.3416061907722422</v>
       </c>
       <c r="X10" t="n">
-        <v>1.587270683797775</v>
+        <v>-0.2806245422873125</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.92991341381953</v>
+        <v>-0.8586961764495017</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.691769345226951</v>
+        <v>0.1337061541958824</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.984283142277137</v>
+        <v>-0.004377480984218512</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.852720219336547</v>
+        <v>-0.5614823623262373</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.941448042622123</v>
+        <v>-0.5023829182865174</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.07145285034852951</v>
+        <v>-0.09158600993643221</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.570915511749179</v>
+        <v>-0.3718088001857767</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.487220735983606</v>
+        <v>-0.3121682412520538</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/data_preparation/df_selected.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_selected.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_team_away</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -441,12 +441,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_shots_on_goal</t>
+          <t>dif_mean_last_360_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -456,1023 +456,1057 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goal_attempts</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_goals</t>
+          <t>dif_mean_last_360_matches_points</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_goals</t>
+          <t>dif_mean_last_360_matches_goal_ratio</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_points</t>
+          <t>dif_mean_last_360_matches_attacks</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_points</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_attacks</t>
+          <t>dif_mean_last_360_matches_dead_balls</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_total_passes</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_dangerous_attacks</t>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_yellow_cards</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_dead_balls</t>
+          <t>dif_mean_last_360_matches_PPDA</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_ball_possession</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_60_matches_total_passes</t>
+          <t>dif_sum_value_player_miss</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_total_passes</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_240_matches_yellow_cards</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_240_matches_KGP</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_240_matches_clean_sheet</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
           <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xMovyDqH</t>
+          <t>6w5RRTN0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.838867317192179</v>
+        <v>0.07832037754204221</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09645413582038213</v>
+        <v>-1.163640689214296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2405855291956655</v>
+        <v>-0.3061523359515487</v>
       </c>
       <c r="F2" t="n">
-        <v>0.444914016773501</v>
+        <v>-1.1866931214736</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2775538615468439</v>
+        <v>-0.04673028695522184</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4518503029312428</v>
+        <v>0.1775406457950858</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5314436661244709</v>
+        <v>-0.2601663087005531</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.7944107537637608</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.1438750769575737</v>
-      </c>
+        <v>1.026644303337151</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-1.338738394603227</v>
+        <v>1.416790413719748</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8302109101902021</v>
+        <v>-1.539807363267552</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.004264689400372</v>
+        <v>-1.152474781003747</v>
       </c>
       <c r="O2" t="n">
-        <v>0.50737623165817</v>
+        <v>0.4042804844410054</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5046674326302739</v>
+        <v>-0.450081010894782</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5248328615664728</v>
+        <v>-0.7201795327605661</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02409682874616747</v>
+        <v>-0.1047135340717079</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5348420517686974</v>
+        <v>-0.5634510635798788</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8594128334868001</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-2.387601637948503</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.3830800305928634</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-0.9311281236618434</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-1.602444389980451</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-1.138364831533073</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.826574289752071</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.5577118261205629</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-0.5543648122157195</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.651416071365271</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-0.7698669941042622</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.4606768454367023</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1.246988867639715</v>
+        <v>0.4085881247268545</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UkaNveph</t>
+          <t>fwAoyY0E</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.838867317192179</v>
+        <v>-0.9092463963223026</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7291303719998028</v>
+        <v>1.297326231947809</v>
       </c>
       <c r="E3" t="n">
-        <v>1.273948436328604</v>
+        <v>1.825281610425591</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9314063892828194</v>
+        <v>1.376152505895362</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9326264888117991</v>
+        <v>1.644118017982295</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4518503029312428</v>
+        <v>2.6027536776341</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6897985164191746</v>
+        <v>-0.1383144710328494</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1768699315470983</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.6129197085318268</v>
-      </c>
+        <v>0.1188582777555262</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.6288833714098863</v>
+        <v>0.7725691791913468</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4306227619701142</v>
+        <v>1.894705845122534</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1894147719924155</v>
+        <v>-1.20331531757153</v>
       </c>
       <c r="O3" t="n">
-        <v>1.085474861652541</v>
+        <v>-1.840217226735242</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2749234427523678</v>
+        <v>-0.4247195242345063</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.456246435722241</v>
+        <v>-0.8135433711292612</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08330501254152</v>
+        <v>0.1920849617513184</v>
       </c>
       <c r="S3" t="n">
-        <v>1.504846535270637</v>
+        <v>0.2653329538608435</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.025762170550333</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-1.069600206710438</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.188251208015971</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.3806351048406696</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.6392341349005228</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.2333187610447304</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.07955301445709498</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.2652171901760009</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-0.372480461021963</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.03272726077922969</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.2596601896432859</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-0.0297466955041496</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.4134956953281171</v>
+        <v>1.024323758840337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UJQITUyi</t>
+          <t>pOGITkgl</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.801759837338154</v>
+        <v>2.476696828355451</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.09645413582038213</v>
+        <v>2.415947559748766</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3286110885037893</v>
+        <v>0.9940286229141547</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7951885249802102</v>
+        <v>0.6378842181759079</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7179926944304982</v>
+        <v>1.010049903630726</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3665870388523134</v>
+        <v>0.4425925131147</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.440611491838402</v>
+        <v>-1.597783865194464</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6465178314084516</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.2398887125122697</v>
-      </c>
+        <v>0.8913864653619402</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-0.01744152859481979</v>
+        <v>2.444708705784822</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6827894964021773</v>
+        <v>1.274458875349169</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4454014781648269</v>
+        <v>0.6269439988686393</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1367908131927002</v>
+        <v>-0.2552223019228086</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3164377571450901</v>
+        <v>-2.157972998318321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.7146136740144627</v>
+        <v>-0.7727638284350901</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.5307618762293783</v>
+        <v>0.7323742201628869</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7672599000768061</v>
+        <v>0.008597996506339488</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3016532915678939</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.942816401255195</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-0.1806385826739339</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.07678403828208691</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-0.1805728072874238</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.4624104987004007</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.2228953513760704</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>-0.3805226617658976</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>1.296719148524042</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>j5mWxZE4</t>
+          <t>2qNaDU87</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.801759837338154</v>
+        <v>0.360482312931855</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3163381180897104</v>
+        <v>1.744774763068192</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7149160439452109</v>
+        <v>1.905747025528349</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1777962200384266</v>
+        <v>0.7855378757197989</v>
       </c>
       <c r="G5" t="n">
-        <v>0.499191253556357</v>
+        <v>1.010049903630726</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9394931781008028</v>
+        <v>1.022147947497954</v>
       </c>
       <c r="I5" t="n">
-        <v>1.759302813024942</v>
+        <v>-2.167289721400472</v>
       </c>
       <c r="J5" t="n">
-        <v>1.058211712886227</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.934772761150176</v>
-      </c>
+        <v>2.606379420304951</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1.842263207970027</v>
+        <v>1.58136295486804</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.006466244378795444</v>
+        <v>1.10971763613152</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3796434252031065</v>
+        <v>0.6777845354364217</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01186312023442371</v>
+        <v>0.9772173792946071</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2074626818641928</v>
+        <v>-2.06295336961122</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2952913636551995</v>
+        <v>-0.5871578404978671</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.07320770987738884</v>
+        <v>0.3298680527604106</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4699543025330261</v>
+        <v>-1.230099737229164</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8300570681226468</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-1.603659792576162</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.236451552758574</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.413654790271915</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.255481858854156</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.222193135168014</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.726142104132111</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.390961487379234</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.657162449433347</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.415433871769566</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.7144114788992731</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.627012369374736</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.473879885222306</v>
+        <v>2.762857365949159</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>biQrHC9r</t>
+          <t>E38ZP7hD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.838867317192179</v>
+        <v>0.4310227967793082</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.741726119262037</v>
+        <v>-0.2687436269735305</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.549764384020942</v>
+        <v>-0.2569823344340688</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.865229763542177</v>
+        <v>0.4269504216846357</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.263437415385478</v>
+        <v>-0.6807984013067908</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.205644606753149</v>
+        <v>-0.8657977857202217</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.909993849644706</v>
+        <v>0.02430268063542598</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.205932633116132</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-3.114541694503767</v>
-      </c>
+        <v>0.5107285267663267</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>-0.2918990610793617</v>
+        <v>0.7539303102868615</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6116664070157473</v>
+        <v>-0.01993657564665163</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.267944518435513</v>
+        <v>-0.6949099518937049</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.408607799180316</v>
+        <v>0.7605077052342458</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.953996962918891</v>
+        <v>0.9987946614272118</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.287099478852396</v>
+        <v>-0.4235457507544685</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.566943795159615</v>
+        <v>-0.516751547814125</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.249394107465558</v>
+        <v>-0.196758624982476</v>
       </c>
       <c r="T6" t="n">
-        <v>1.625152398697416</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.116351291736351</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-2.560059079228309</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-5.607508463901694</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.822800380810278</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-4.445831509203892</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-4.155006761637404</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-3.373401564709736</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-3.709141534027309</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-2.977875635585828</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-0.2911107838011604</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-3.379073154115272</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-2.850033501651119</v>
+        <v>-1.321131956501107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nee3ysec</t>
+          <t>SrjMmBpK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.875974797046204</v>
+        <v>3.746425537609609</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.210993221377632</v>
+        <v>-0.2687436269735305</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.229839066527926</v>
+        <v>-0.1633355432631315</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9561840160533359</v>
+        <v>-0.2585844169120003</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6713964551202977</v>
+        <v>0.3759817892791575</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2881628345745316</v>
+        <v>-0.5145520679121891</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07099648603679438</v>
+        <v>-0.4952084381675927</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3827168722859858</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.01595381380095925</v>
-      </c>
+        <v>0.9549228910480022</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>-0.896474786646151</v>
+        <v>0.4731823474130791</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4642449932277227</v>
+        <v>0.8925932378999629</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1464209984906566</v>
+        <v>0.5252629257330742</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.812561614880931</v>
+        <v>-0.2067845919288486</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.218548162048008</v>
+        <v>0.02639744722832494</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.860076434861261</v>
+        <v>-0.5389799191409005</v>
       </c>
       <c r="R7" t="n">
-        <v>-1.532775789230733</v>
+        <v>0.6105279727697803</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.609397298491902</v>
+        <v>0.6607489887717588</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2304199556573773</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-1.284342740233658</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.2242443131639254</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-2.856826082550917</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.405876993055359</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-2.265798631498563</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-1.337817707005098</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-1.332670432539768</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-2.09562386984313</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1.824970502847608</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.9183533480222216</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-2.212604440190583</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1.614047974692625</v>
+        <v>0.1544279746716089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>6HTjFjve</t>
+          <t>EuQnZBVQ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.801759837338154</v>
+        <v>2.406156344507998</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.274954490928094</v>
+        <v>3.310844621989532</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.249649673239449</v>
+        <v>1.919375978171977</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.396201438680918</v>
+        <v>2.430821488351725</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.382501137961256</v>
+        <v>1.432761979865106</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.334256189033422</v>
+        <v>1.861844741632782</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.924274627676471</v>
+        <v>-1.430440262659445</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.617798516719311</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-1.263258817765186</v>
-      </c>
+        <v>1.238469763325409</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>-0.215224011656369</v>
+        <v>1.167887939362376</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.065566528993461</v>
+        <v>2.887708337733991</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2779371044140974</v>
+        <v>-1.610039610113789</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.193885450896693</v>
+        <v>-1.899737551605659</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7919653583708195</v>
+        <v>-0.1253260275276555</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.561849443871562</v>
+        <v>0.9435075046143674</v>
       </c>
       <c r="R8" t="n">
-        <v>-3.443955773035392</v>
+        <v>1.174722496605328</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.623818607982882</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.7722784580040332</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.207227504611448</v>
-      </c>
-      <c r="V8" t="n">
-        <v>-1.597728718106441</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-5.174865028011506</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-3.201613141881857</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-5.223555123577362</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>-3.783464260359266</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-2.669092846573592</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-4.275450955864105</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-3.216396106793455</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-1.325779666766542</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-3.45626216949103</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-2.992317844487865</v>
-      </c>
+        <v>-0.8275890381374049</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YmumZjET</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.987297236608277</v>
+        <v>3.464263602219796</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2278352655724001</v>
+        <v>-0.3232752051465956</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6465719212177844</v>
+        <v>-0.2687436269735305</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1220029005082791</v>
+        <v>-0.5343076663759432</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6200512708768556</v>
+        <v>0.3214835234389993</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2803898126822166</v>
+        <v>-1.10351047754117</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6939619755657359</v>
+        <v>-0.3389292090081727</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08248590732576483</v>
+        <v>0.04831677239572466</v>
       </c>
       <c r="J9" t="n">
-        <v>1.058211712886227</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.1438750769575738</v>
-      </c>
+        <v>-0.7312217235559321</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>-0.1932481802050859</v>
+        <v>-0.4576689765862227</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1784560275380509</v>
+        <v>0.5418538253720628</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1913362735399982</v>
+        <v>-0.9999531713003996</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3917565056592959</v>
+        <v>-0.7613330222419976</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5751764951531546</v>
+        <v>-0.7848706056668219</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03773168961864067</v>
+        <v>0.3737833533617947</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8745830632803048</v>
+        <v>-0.936909282512788</v>
       </c>
       <c r="S9" t="n">
-        <v>0.05710239594243171</v>
+        <v>0.2904574975159649</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2612891141921837</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.5515270524599796</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1.192845822268582</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.2410453522037886</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.9465697989968399</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.001274658685556155</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.269934113224608</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.3040557261785181</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.1907343738102606</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.220369112293997</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.08992216727142914</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.3038062496526942</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.006965283415226</v>
+        <v>-0.6368296381461261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.8387059124748494</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4024291697070437</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.315732893760198</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9120981536145625</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3759817892791575</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.607557477178008</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1.391825598313292</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.470701628269307</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1.260674558627507</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8785484778744946</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.304996390707095</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.559531905241064</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.478956920845772</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6303951908451407</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.6503196487603272</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2867082321640382</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.02630258730166279</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.547237312202904</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.594926972196919</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7299240144317071</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.435213968912918</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9255074883838504</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9041513391718177</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.5818615409772313</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1837028063233609</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.656294672783299</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.3296804724245376</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.447349893096885</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.6253760696432552</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.136474034617017</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.1572149070866385</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.006743505141357207</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2364139480787132</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-1.050327364017209</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4024291697070437</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.933977484426919</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.02617620835121761</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.644118017982295</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.731716291079723</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.2695694000129745</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.164344983043535</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.9330956712303503</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.3888962173967804</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.5423883421903575</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-1.537603364499332</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.2521823969207924</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.1509560976299146</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.530073762802276</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.9272660352136211</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.402754363906341</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-1.473570267101928</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.953434813695828</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1.952264686366768</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.5222516625260909</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1.52622255377555</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-2.475673992340371</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.127753043976391</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.033977463746024</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>-1.838619861396139</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.6971217617394803</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2202197063263795</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.87886328306261</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.7140306302772266</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7419988901217245</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.8578302610258713</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.059078378477827</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-2.932598484049539</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.041020699135077</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1345090676374156</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.7049213200659507</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.08945634729859939</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.004459079331783872</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.719445403300208</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.5094643309106239</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2000229470387997</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0.2444576748861855</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1.131750146311391</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.02381486919897654</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.121019632583405</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2287676228963024</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.26908645478653</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-2.938950045246293</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.0002890080964952268</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.794902507412475</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.182101666829984</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.416496576351368</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1.195827656940967</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.821603848912331</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.695307384269301</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.6120689711457349</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>-0.201707906076023</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>-0.1302510333695733</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-2.815223408823551</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1.854074185639145</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.3009032810806654</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.198487452951293</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.2295116370403616</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.7997213014868244</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.5322940444315616</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-3.167972386665438</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-1.403029783254475</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.834813485894871</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.7841586823786967</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.007399394456018</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.4694423631896011</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.427790934213074</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>-0.6687442382979711</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>-0.4846225284160658</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.09545820942746258</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.8982720981648348</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.2062276766084231</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.177031659772082</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.5272806114104369</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.18467130348692</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4967944137381755</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.210262904082627</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>v3DAZKP9</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1.801759837338154</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.2278352655724001</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.591804840512493</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-0.1863119340789256</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.5475304231455085</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.06969249271640911</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.3700065687528872</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.5940938852009607</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.5885638130248733</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.3678099756688841</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.3525729582268892</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.2250107475532503</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3527424035369481</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.177368347182568</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.2074626818641928</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.6265011539493247</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-1.675390074846937</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.8739105144519562</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.6780953774607095</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.064538776133564</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.9904043743496523</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.3416061907722422</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.2806245422873125</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-0.8586961764495017</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.1337061541958824</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.004377480984218512</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.5614823623262373</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-0.5023829182865174</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.09158600993643221</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.3718088001857767</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.3121682412520538</v>
+      <c r="B17" t="n">
+        <v>2.476696828355451</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.3232752051465956</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.6261534352672352</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.1578269084883707</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.7331854590173636</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1646257511619678</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08915150957036708</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.8756402841692911</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.9203360258920938</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0.111107757327156</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.8140348992487801</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6269439988686391</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.125148011282485</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.03035454700074238</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.9354022497814848</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.07657189249664439</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.8861254836407785</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.5946515496782523</v>
       </c>
     </row>
   </sheetData>
